--- a/research/traditional_assets/database/data/portugal/portugal_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtls_eson" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0916</v>
+        <v>-0.0169</v>
+      </c>
+      <c r="E2">
+        <v>0.235</v>
       </c>
       <c r="G2">
-        <v>0.03618233618233618</v>
+        <v>0.1024860476915271</v>
       </c>
       <c r="H2">
-        <v>0.03618233618233618</v>
+        <v>0.1024860476915271</v>
       </c>
       <c r="I2">
-        <v>-0.1531339031339031</v>
+        <v>0.2090309487569762</v>
       </c>
       <c r="J2">
-        <v>-0.1531339031339031</v>
+        <v>0.2085071917521901</v>
       </c>
       <c r="K2">
-        <v>-25.5</v>
+        <v>35.7</v>
       </c>
       <c r="L2">
-        <v>-0.1816239316239316</v>
+        <v>0.1811263318112633</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>69.3</v>
+        <v>87.2</v>
       </c>
       <c r="V2">
-        <v>0.9203187250996016</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="W2">
-        <v>-0.2442528735632184</v>
+        <v>0.4224852071005917</v>
       </c>
       <c r="X2">
-        <v>0.07789712575991252</v>
+        <v>0.1120837426099213</v>
       </c>
       <c r="Y2">
-        <v>-0.3221499993231309</v>
+        <v>0.3104014644906705</v>
       </c>
       <c r="Z2">
-        <v>3.483870967741936</v>
+        <v>7.3271375464684</v>
       </c>
       <c r="AA2">
-        <v>-0.533498759305211</v>
+        <v>1.527760873396158</v>
       </c>
       <c r="AB2">
-        <v>0.07211298660311551</v>
+        <v>0.1083653129524731</v>
       </c>
       <c r="AC2">
-        <v>-0.6056117459083264</v>
+        <v>1.419395560443685</v>
       </c>
       <c r="AD2">
-        <v>11.7</v>
+        <v>6.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.7</v>
+        <v>6.1</v>
       </c>
       <c r="AG2">
-        <v>-57.59999999999999</v>
+        <v>-81.10000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1344827586206896</v>
+        <v>0.07402912621359224</v>
       </c>
       <c r="AI2">
-        <v>0.1060743427017226</v>
+        <v>0.04903536977491962</v>
       </c>
       <c r="AJ2">
-        <v>-3.254237288135593</v>
+        <v>16.8958333333333</v>
       </c>
       <c r="AK2">
-        <v>-1.404878048780488</v>
+        <v>-2.180107526881721</v>
       </c>
       <c r="AL2">
-        <v>0.396</v>
+        <v>0.341</v>
       </c>
       <c r="AM2">
-        <v>0.355</v>
+        <v>0.292</v>
       </c>
       <c r="AN2">
-        <v>-1.618257261410788</v>
+        <v>0.1352549889135255</v>
       </c>
       <c r="AO2">
-        <v>-54.29292929292929</v>
+        <v>120.8211143695015</v>
       </c>
       <c r="AP2">
-        <v>7.96680497925311</v>
+        <v>-1.798226164079823</v>
       </c>
       <c r="AQ2">
-        <v>-60.56338028169014</v>
+        <v>141.0958904109589</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0916</v>
+        <v>-0.0169</v>
+      </c>
+      <c r="E3">
+        <v>0.235</v>
       </c>
       <c r="G3">
-        <v>0.03618233618233618</v>
+        <v>0.1024860476915271</v>
       </c>
       <c r="H3">
-        <v>0.03618233618233618</v>
+        <v>0.1024860476915271</v>
       </c>
       <c r="I3">
-        <v>-0.1531339031339031</v>
+        <v>0.2090309487569762</v>
       </c>
       <c r="J3">
-        <v>-0.1531339031339031</v>
+        <v>0.2085071917521901</v>
       </c>
       <c r="K3">
-        <v>-25.5</v>
+        <v>35.7</v>
       </c>
       <c r="L3">
-        <v>-0.1816239316239316</v>
+        <v>0.1811263318112633</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>69.3</v>
+        <v>87.2</v>
       </c>
       <c r="V3">
-        <v>0.9203187250996016</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="W3">
-        <v>-0.2442528735632184</v>
+        <v>0.4224852071005917</v>
       </c>
       <c r="X3">
-        <v>0.07789712575991252</v>
+        <v>0.1120837426099213</v>
       </c>
       <c r="Y3">
-        <v>-0.3221499993231309</v>
+        <v>0.3104014644906705</v>
       </c>
       <c r="Z3">
-        <v>3.483870967741936</v>
+        <v>7.3271375464684</v>
       </c>
       <c r="AA3">
-        <v>-0.533498759305211</v>
+        <v>1.527760873396158</v>
       </c>
       <c r="AB3">
-        <v>0.07211298660311551</v>
+        <v>0.1083653129524731</v>
       </c>
       <c r="AC3">
-        <v>-0.6056117459083264</v>
+        <v>1.419395560443685</v>
       </c>
       <c r="AD3">
-        <v>11.7</v>
+        <v>6.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11.7</v>
+        <v>6.1</v>
       </c>
       <c r="AG3">
-        <v>-57.59999999999999</v>
+        <v>-81.10000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1344827586206896</v>
+        <v>0.07402912621359224</v>
       </c>
       <c r="AI3">
-        <v>0.1060743427017226</v>
+        <v>0.04903536977491962</v>
       </c>
       <c r="AJ3">
-        <v>-3.254237288135593</v>
+        <v>16.8958333333333</v>
       </c>
       <c r="AK3">
-        <v>-1.404878048780488</v>
+        <v>-2.180107526881721</v>
       </c>
       <c r="AL3">
-        <v>0.396</v>
+        <v>0.341</v>
       </c>
       <c r="AM3">
-        <v>0.355</v>
+        <v>0.292</v>
       </c>
       <c r="AN3">
-        <v>-1.618257261410788</v>
+        <v>0.1352549889135255</v>
       </c>
       <c r="AO3">
-        <v>-54.29292929292929</v>
+        <v>120.8211143695015</v>
       </c>
       <c r="AP3">
-        <v>7.96680497925311</v>
+        <v>-1.798226164079823</v>
       </c>
       <c r="AQ3">
-        <v>-60.56338028169014</v>
+        <v>141.0958904109589</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Estoril Sol, SGPS, S.A. (ENXTLS:ESON)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTLS:ESON</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0740291262135922</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>76.3</v>
+      </c>
+      <c r="H2">
+        <v>82.39761018028631</v>
+      </c>
+      <c r="I2">
+        <v>-4.80000000000001</v>
+      </c>
+      <c r="J2">
+        <v>-4.80238981971373</v>
+      </c>
+      <c r="K2">
+        <v>6.1</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.108365312952473</v>
+      </c>
+      <c r="N2">
+        <v>0.107730208226642</v>
+      </c>
+      <c r="O2">
+        <v>0.0618544633027523</v>
+      </c>
+      <c r="P2">
+        <v>0.036103</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.112083742609921</v>
+      </c>
+      <c r="T2">
+        <v>0.107730208226642</v>
+      </c>
+      <c r="U2">
+        <v>0.79651543615509</v>
+      </c>
+      <c r="V2">
+        <v>0.749197201378634</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>76.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.09200542674185173</v>
+      </c>
+      <c r="AC2">
+        <v>0.07829678899082569</v>
+      </c>
+      <c r="AD2">
+        <v>0.21</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>45.1</v>
+      </c>
+      <c r="AH2">
+        <v>4.33</v>
+      </c>
+      <c r="AI2">
+        <v>0.04999999999999893</v>
+      </c>
+      <c r="AJ2">
+        <v>6.1</v>
+      </c>
+      <c r="AK2">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="AL2">
+        <v>0.341</v>
+      </c>
+      <c r="AM2">
+        <v>6.1</v>
+      </c>
+      <c r="AN2">
+        <v>87.2</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1077302082266422</v>
+      </c>
+      <c r="C2">
+        <v>82.39761018028626</v>
+      </c>
+      <c r="D2">
+        <v>-4.802389819713735</v>
+      </c>
+      <c r="E2">
+        <v>-6.1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>87.2</v>
+      </c>
+      <c r="H2">
+        <v>76.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>45.1</v>
+      </c>
+      <c r="K2">
+        <v>4.33</v>
+      </c>
+      <c r="L2">
+        <v>40.77</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>40.77</v>
+      </c>
+      <c r="O2">
+        <v>8.5617</v>
+      </c>
+      <c r="P2">
+        <v>32.2083</v>
+      </c>
+      <c r="Q2">
+        <v>36.5383</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1077302082266422</v>
+      </c>
+      <c r="T2">
+        <v>0.7491972013786339</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.21</v>
+      </c>
+      <c r="W2">
+        <v>0.036103</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1075584847893663</v>
+      </c>
+      <c r="C3">
+        <v>81.57296359769312</v>
+      </c>
+      <c r="D3">
+        <v>-4.80303640230689</v>
+      </c>
+      <c r="E3">
+        <v>-5.276</v>
+      </c>
+      <c r="F3">
+        <v>0.824</v>
+      </c>
+      <c r="G3">
+        <v>87.2</v>
+      </c>
+      <c r="H3">
+        <v>76.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>45.1</v>
+      </c>
+      <c r="K3">
+        <v>4.33</v>
+      </c>
+      <c r="L3">
+        <v>40.77</v>
+      </c>
+      <c r="M3">
+        <v>0.0376568</v>
+      </c>
+      <c r="N3">
+        <v>40.7323432</v>
+      </c>
+      <c r="O3">
+        <v>8.553792071999998</v>
+      </c>
+      <c r="P3">
+        <v>32.178551128</v>
+      </c>
+      <c r="Q3">
+        <v>36.508551128</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1082802573629963</v>
+      </c>
+      <c r="T3">
+        <v>0.7551756436926654</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.21</v>
+      </c>
+      <c r="W3">
+        <v>0.036103</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>1082.672983365554</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1073867613520904</v>
+      </c>
+      <c r="C4">
+        <v>80.74831684096776</v>
+      </c>
+      <c r="D4">
+        <v>-4.80368315903224</v>
+      </c>
+      <c r="E4">
+        <v>-4.452</v>
+      </c>
+      <c r="F4">
+        <v>1.648</v>
+      </c>
+      <c r="G4">
+        <v>87.2</v>
+      </c>
+      <c r="H4">
+        <v>76.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>45.1</v>
+      </c>
+      <c r="K4">
+        <v>4.33</v>
+      </c>
+      <c r="L4">
+        <v>40.77</v>
+      </c>
+      <c r="M4">
+        <v>0.07531360000000001</v>
+      </c>
+      <c r="N4">
+        <v>40.6946864</v>
+      </c>
+      <c r="O4">
+        <v>8.545884143999999</v>
+      </c>
+      <c r="P4">
+        <v>32.148802256</v>
+      </c>
+      <c r="Q4">
+        <v>36.478802256</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1088415319919289</v>
+      </c>
+      <c r="T4">
+        <v>0.761276095033514</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.21</v>
+      </c>
+      <c r="W4">
+        <v>0.036103</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>541.336491682777</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1072150379148144</v>
+      </c>
+      <c r="C5">
+        <v>79.92366991003986</v>
+      </c>
+      <c r="D5">
+        <v>-4.804330089960141</v>
+      </c>
+      <c r="E5">
+        <v>-3.628</v>
+      </c>
+      <c r="F5">
+        <v>2.472</v>
+      </c>
+      <c r="G5">
+        <v>87.2</v>
+      </c>
+      <c r="H5">
+        <v>76.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>45.1</v>
+      </c>
+      <c r="K5">
+        <v>4.33</v>
+      </c>
+      <c r="L5">
+        <v>40.77</v>
+      </c>
+      <c r="M5">
+        <v>0.1129704</v>
+      </c>
+      <c r="N5">
+        <v>40.6570296</v>
+      </c>
+      <c r="O5">
+        <v>8.537976215999999</v>
+      </c>
+      <c r="P5">
+        <v>32.119053384</v>
+      </c>
+      <c r="Q5">
+        <v>36.449053384</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1094143792936231</v>
+      </c>
+      <c r="T5">
+        <v>0.7675023288762355</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.21</v>
+      </c>
+      <c r="W5">
+        <v>0.036103</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>360.8909944551848</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1070433144775384</v>
+      </c>
+      <c r="C6">
+        <v>79.09902280483901</v>
+      </c>
+      <c r="D6">
+        <v>-4.804977195160983</v>
+      </c>
+      <c r="E6">
+        <v>-2.804</v>
+      </c>
+      <c r="F6">
+        <v>3.296</v>
+      </c>
+      <c r="G6">
+        <v>87.2</v>
+      </c>
+      <c r="H6">
+        <v>76.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>45.1</v>
+      </c>
+      <c r="K6">
+        <v>4.33</v>
+      </c>
+      <c r="L6">
+        <v>40.77</v>
+      </c>
+      <c r="M6">
+        <v>0.1506272</v>
+      </c>
+      <c r="N6">
+        <v>40.6193728</v>
+      </c>
+      <c r="O6">
+        <v>8.530068287999999</v>
+      </c>
+      <c r="P6">
+        <v>32.089304512</v>
+      </c>
+      <c r="Q6">
+        <v>36.419304512</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1099991609141025</v>
+      </c>
+      <c r="T6">
+        <v>0.7738582759240139</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.21</v>
+      </c>
+      <c r="W6">
+        <v>0.036103</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>270.6682458413885</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1068715910402625</v>
+      </c>
+      <c r="C7">
+        <v>78.2743755252948</v>
+      </c>
+      <c r="D7">
+        <v>-4.805624474705197</v>
+      </c>
+      <c r="E7">
+        <v>-1.98</v>
+      </c>
+      <c r="F7">
+        <v>4.12</v>
+      </c>
+      <c r="G7">
+        <v>87.2</v>
+      </c>
+      <c r="H7">
+        <v>76.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>45.1</v>
+      </c>
+      <c r="K7">
+        <v>4.33</v>
+      </c>
+      <c r="L7">
+        <v>40.77</v>
+      </c>
+      <c r="M7">
+        <v>0.188284</v>
+      </c>
+      <c r="N7">
+        <v>40.581716</v>
+      </c>
+      <c r="O7">
+        <v>8.522160359999999</v>
+      </c>
+      <c r="P7">
+        <v>32.05955564</v>
+      </c>
+      <c r="Q7">
+        <v>36.38955564</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1105962537265921</v>
+      </c>
+      <c r="T7">
+        <v>0.7803480323833245</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.21</v>
+      </c>
+      <c r="W7">
+        <v>0.036103</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>216.5345966731108</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1066998676029866</v>
+      </c>
+      <c r="C8">
+        <v>77.44972807133675</v>
+      </c>
+      <c r="D8">
+        <v>-4.806271928663247</v>
+      </c>
+      <c r="E8">
+        <v>-1.156000000000001</v>
+      </c>
+      <c r="F8">
+        <v>4.943999999999999</v>
+      </c>
+      <c r="G8">
+        <v>87.2</v>
+      </c>
+      <c r="H8">
+        <v>76.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>45.1</v>
+      </c>
+      <c r="K8">
+        <v>4.33</v>
+      </c>
+      <c r="L8">
+        <v>40.77</v>
+      </c>
+      <c r="M8">
+        <v>0.2259408</v>
+      </c>
+      <c r="N8">
+        <v>40.54405920000001</v>
+      </c>
+      <c r="O8">
+        <v>8.514252431999999</v>
+      </c>
+      <c r="P8">
+        <v>32.02980676800001</v>
+      </c>
+      <c r="Q8">
+        <v>36.35980676800001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1112060506414751</v>
+      </c>
+      <c r="T8">
+        <v>0.7869758687673012</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.21</v>
+      </c>
+      <c r="W8">
+        <v>0.036103</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>180.4454972275924</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1065281441657106</v>
+      </c>
+      <c r="C9">
+        <v>76.62508044289436</v>
+      </c>
+      <c r="D9">
+        <v>-4.80691955710564</v>
+      </c>
+      <c r="E9">
+        <v>-0.3319999999999999</v>
+      </c>
+      <c r="F9">
+        <v>5.768</v>
+      </c>
+      <c r="G9">
+        <v>87.2</v>
+      </c>
+      <c r="H9">
+        <v>76.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>45.1</v>
+      </c>
+      <c r="K9">
+        <v>4.33</v>
+      </c>
+      <c r="L9">
+        <v>40.77</v>
+      </c>
+      <c r="M9">
+        <v>0.2635976</v>
+      </c>
+      <c r="N9">
+        <v>40.50640240000001</v>
+      </c>
+      <c r="O9">
+        <v>8.506344503999999</v>
+      </c>
+      <c r="P9">
+        <v>32.00005789600001</v>
+      </c>
+      <c r="Q9">
+        <v>36.33005789600001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.111828961468506</v>
+      </c>
+      <c r="T9">
+        <v>0.7937462392670624</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.21</v>
+      </c>
+      <c r="W9">
+        <v>0.036103</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>154.667569052222</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1063564207284347</v>
+      </c>
+      <c r="C10">
+        <v>75.80043263989708</v>
+      </c>
+      <c r="D10">
+        <v>-4.807567360102918</v>
+      </c>
+      <c r="E10">
+        <v>0.492</v>
+      </c>
+      <c r="F10">
+        <v>6.592</v>
+      </c>
+      <c r="G10">
+        <v>87.2</v>
+      </c>
+      <c r="H10">
+        <v>76.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>45.1</v>
+      </c>
+      <c r="K10">
+        <v>4.33</v>
+      </c>
+      <c r="L10">
+        <v>40.77</v>
+      </c>
+      <c r="M10">
+        <v>0.3012544</v>
+      </c>
+      <c r="N10">
+        <v>40.46874560000001</v>
+      </c>
+      <c r="O10">
+        <v>8.498436576</v>
+      </c>
+      <c r="P10">
+        <v>31.97030902400001</v>
+      </c>
+      <c r="Q10">
+        <v>36.30030902400001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1124654138352551</v>
+      </c>
+      <c r="T10">
+        <v>0.8006637917342097</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.21</v>
+      </c>
+      <c r="W10">
+        <v>0.036103</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>135.3341229206943</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1061846972911587</v>
+      </c>
+      <c r="C11">
+        <v>74.97578466227435</v>
+      </c>
+      <c r="D11">
+        <v>-4.808215337725662</v>
+      </c>
+      <c r="E11">
+        <v>1.315999999999999</v>
+      </c>
+      <c r="F11">
+        <v>7.415999999999999</v>
+      </c>
+      <c r="G11">
+        <v>87.2</v>
+      </c>
+      <c r="H11">
+        <v>76.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>45.1</v>
+      </c>
+      <c r="K11">
+        <v>4.33</v>
+      </c>
+      <c r="L11">
+        <v>40.77</v>
+      </c>
+      <c r="M11">
+        <v>0.3389112</v>
+      </c>
+      <c r="N11">
+        <v>40.4310888</v>
+      </c>
+      <c r="O11">
+        <v>8.490528648</v>
+      </c>
+      <c r="P11">
+        <v>31.940560152</v>
+      </c>
+      <c r="Q11">
+        <v>36.270560152</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1131158541661085</v>
+      </c>
+      <c r="T11">
+        <v>0.8077333783215139</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.21</v>
+      </c>
+      <c r="W11">
+        <v>0.036103</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>120.2969981517283</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1060129738538828</v>
+      </c>
+      <c r="C12">
+        <v>74.15113650995552</v>
+      </c>
+      <c r="D12">
+        <v>-4.808863490044492</v>
+      </c>
+      <c r="E12">
+        <v>2.140000000000001</v>
+      </c>
+      <c r="F12">
+        <v>8.24</v>
+      </c>
+      <c r="G12">
+        <v>87.2</v>
+      </c>
+      <c r="H12">
+        <v>76.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>45.1</v>
+      </c>
+      <c r="K12">
+        <v>4.33</v>
+      </c>
+      <c r="L12">
+        <v>40.77</v>
+      </c>
+      <c r="M12">
+        <v>0.3765680000000001</v>
+      </c>
+      <c r="N12">
+        <v>40.393432</v>
+      </c>
+      <c r="O12">
+        <v>8.48262072</v>
+      </c>
+      <c r="P12">
+        <v>31.91081128</v>
+      </c>
+      <c r="Q12">
+        <v>36.24081128</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1137807487265364</v>
+      </c>
+      <c r="T12">
+        <v>0.8149600668329806</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.21</v>
+      </c>
+      <c r="W12">
+        <v>0.036103</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>108.2672983365554</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1058412504166068</v>
+      </c>
+      <c r="C13">
+        <v>73.32648818286995</v>
+      </c>
+      <c r="D13">
+        <v>-4.809511817130065</v>
+      </c>
+      <c r="E13">
+        <v>2.963999999999999</v>
+      </c>
+      <c r="F13">
+        <v>9.063999999999998</v>
+      </c>
+      <c r="G13">
+        <v>87.2</v>
+      </c>
+      <c r="H13">
+        <v>76.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>45.1</v>
+      </c>
+      <c r="K13">
+        <v>4.33</v>
+      </c>
+      <c r="L13">
+        <v>40.77</v>
+      </c>
+      <c r="M13">
+        <v>0.4142247999999999</v>
+      </c>
+      <c r="N13">
+        <v>40.3557752</v>
+      </c>
+      <c r="O13">
+        <v>8.474712792</v>
+      </c>
+      <c r="P13">
+        <v>31.88106240800001</v>
+      </c>
+      <c r="Q13">
+        <v>36.211062408</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1144605847377605</v>
+      </c>
+      <c r="T13">
+        <v>0.8223491528390869</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.21</v>
+      </c>
+      <c r="W13">
+        <v>0.036103</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>98.42481666959586</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1056695269793309</v>
+      </c>
+      <c r="C14">
+        <v>72.50183968094692</v>
+      </c>
+      <c r="D14">
+        <v>-4.810160319053075</v>
+      </c>
+      <c r="E14">
+        <v>3.787999999999998</v>
+      </c>
+      <c r="F14">
+        <v>9.887999999999998</v>
+      </c>
+      <c r="G14">
+        <v>87.2</v>
+      </c>
+      <c r="H14">
+        <v>76.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>45.1</v>
+      </c>
+      <c r="K14">
+        <v>4.33</v>
+      </c>
+      <c r="L14">
+        <v>40.77</v>
+      </c>
+      <c r="M14">
+        <v>0.4518815999999999</v>
+      </c>
+      <c r="N14">
+        <v>40.3181184</v>
+      </c>
+      <c r="O14">
+        <v>8.466804863999998</v>
+      </c>
+      <c r="P14">
+        <v>31.85131353600001</v>
+      </c>
+      <c r="Q14">
+        <v>36.181313536</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1151558715674214</v>
+      </c>
+      <c r="T14">
+        <v>0.8299061726180594</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.21</v>
+      </c>
+      <c r="W14">
+        <v>0.036103</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>90.2227486137962</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1054978035420549</v>
+      </c>
+      <c r="C15">
+        <v>71.67719100411574</v>
+      </c>
+      <c r="D15">
+        <v>-4.810808995884257</v>
+      </c>
+      <c r="E15">
+        <v>4.612</v>
+      </c>
+      <c r="F15">
+        <v>10.712</v>
+      </c>
+      <c r="G15">
+        <v>87.2</v>
+      </c>
+      <c r="H15">
+        <v>76.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>45.1</v>
+      </c>
+      <c r="K15">
+        <v>4.33</v>
+      </c>
+      <c r="L15">
+        <v>40.77</v>
+      </c>
+      <c r="M15">
+        <v>0.4895384</v>
+      </c>
+      <c r="N15">
+        <v>40.2804616</v>
+      </c>
+      <c r="O15">
+        <v>8.458896935999999</v>
+      </c>
+      <c r="P15">
+        <v>31.821564664</v>
+      </c>
+      <c r="Q15">
+        <v>36.15156466400001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.115867142002362</v>
+      </c>
+      <c r="T15">
+        <v>0.837636916989652</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.21</v>
+      </c>
+      <c r="W15">
+        <v>0.036103</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>83.28253718196571</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.105326080104779</v>
+      </c>
+      <c r="C16">
+        <v>70.85254215230562</v>
+      </c>
+      <c r="D16">
+        <v>-4.811457847694381</v>
+      </c>
+      <c r="E16">
+        <v>5.436</v>
+      </c>
+      <c r="F16">
+        <v>11.536</v>
+      </c>
+      <c r="G16">
+        <v>87.2</v>
+      </c>
+      <c r="H16">
+        <v>76.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>45.1</v>
+      </c>
+      <c r="K16">
+        <v>4.33</v>
+      </c>
+      <c r="L16">
+        <v>40.77</v>
+      </c>
+      <c r="M16">
+        <v>0.5271952000000001</v>
+      </c>
+      <c r="N16">
+        <v>40.2428048</v>
+      </c>
+      <c r="O16">
+        <v>8.450989007999999</v>
+      </c>
+      <c r="P16">
+        <v>31.791815792</v>
+      </c>
+      <c r="Q16">
+        <v>36.121815792</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1165949536102081</v>
+      </c>
+      <c r="T16">
+        <v>0.8455474461140722</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.21</v>
+      </c>
+      <c r="W16">
+        <v>0.036103</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>77.333784526111</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.105154356667503</v>
+      </c>
+      <c r="C17">
+        <v>70.02789312544574</v>
+      </c>
+      <c r="D17">
+        <v>-4.812106874554257</v>
+      </c>
+      <c r="E17">
+        <v>6.259999999999998</v>
+      </c>
+      <c r="F17">
+        <v>12.36</v>
+      </c>
+      <c r="G17">
+        <v>87.2</v>
+      </c>
+      <c r="H17">
+        <v>76.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>45.1</v>
+      </c>
+      <c r="K17">
+        <v>4.33</v>
+      </c>
+      <c r="L17">
+        <v>40.77</v>
+      </c>
+      <c r="M17">
+        <v>0.5648519999999999</v>
+      </c>
+      <c r="N17">
+        <v>40.205148</v>
+      </c>
+      <c r="O17">
+        <v>8.443081079999999</v>
+      </c>
+      <c r="P17">
+        <v>31.76206692</v>
+      </c>
+      <c r="Q17">
+        <v>36.09206692</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1173398901970624</v>
+      </c>
+      <c r="T17">
+        <v>0.8536441053355376</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.21</v>
+      </c>
+      <c r="W17">
+        <v>0.036103</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>72.17819889103696</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1049826332302271</v>
+      </c>
+      <c r="C18">
+        <v>69.20324392346527</v>
+      </c>
+      <c r="D18">
+        <v>-4.812756076534735</v>
+      </c>
+      <c r="E18">
+        <v>7.084</v>
+      </c>
+      <c r="F18">
+        <v>13.184</v>
+      </c>
+      <c r="G18">
+        <v>87.2</v>
+      </c>
+      <c r="H18">
+        <v>76.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>45.1</v>
+      </c>
+      <c r="K18">
+        <v>4.33</v>
+      </c>
+      <c r="L18">
+        <v>40.77</v>
+      </c>
+      <c r="M18">
+        <v>0.6025088000000001</v>
+      </c>
+      <c r="N18">
+        <v>40.1674912</v>
+      </c>
+      <c r="O18">
+        <v>8.435173151999999</v>
+      </c>
+      <c r="P18">
+        <v>31.732318048</v>
+      </c>
+      <c r="Q18">
+        <v>36.062318048</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1181025633693179</v>
+      </c>
+      <c r="T18">
+        <v>0.8619335421575139</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.21</v>
+      </c>
+      <c r="W18">
+        <v>0.036103</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>67.66706146034713</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1048109097929511</v>
+      </c>
+      <c r="C19">
+        <v>68.37859454629331</v>
+      </c>
+      <c r="D19">
+        <v>-4.8134054537067</v>
+      </c>
+      <c r="E19">
+        <v>7.907999999999999</v>
+      </c>
+      <c r="F19">
+        <v>14.008</v>
+      </c>
+      <c r="G19">
+        <v>87.2</v>
+      </c>
+      <c r="H19">
+        <v>76.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>45.1</v>
+      </c>
+      <c r="K19">
+        <v>4.33</v>
+      </c>
+      <c r="L19">
+        <v>40.77</v>
+      </c>
+      <c r="M19">
+        <v>0.6401656</v>
+      </c>
+      <c r="N19">
+        <v>40.1298344</v>
+      </c>
+      <c r="O19">
+        <v>8.427265223999999</v>
+      </c>
+      <c r="P19">
+        <v>31.702569176</v>
+      </c>
+      <c r="Q19">
+        <v>36.032569176</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1188836142083748</v>
+      </c>
+      <c r="T19">
+        <v>0.8704227244450803</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.21</v>
+      </c>
+      <c r="W19">
+        <v>0.036103</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>63.68664608032672</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1046391863556752</v>
+      </c>
+      <c r="C20">
+        <v>67.55394499385893</v>
+      </c>
+      <c r="D20">
+        <v>-4.814055006141075</v>
+      </c>
+      <c r="E20">
+        <v>8.731999999999998</v>
+      </c>
+      <c r="F20">
+        <v>14.832</v>
+      </c>
+      <c r="G20">
+        <v>87.2</v>
+      </c>
+      <c r="H20">
+        <v>76.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>45.1</v>
+      </c>
+      <c r="K20">
+        <v>4.33</v>
+      </c>
+      <c r="L20">
+        <v>40.77</v>
+      </c>
+      <c r="M20">
+        <v>0.6778223999999999</v>
+      </c>
+      <c r="N20">
+        <v>40.09217760000001</v>
+      </c>
+      <c r="O20">
+        <v>8.419357295999999</v>
+      </c>
+      <c r="P20">
+        <v>31.67282030400001</v>
+      </c>
+      <c r="Q20">
+        <v>36.002820304</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1196837150678965</v>
+      </c>
+      <c r="T20">
+        <v>0.8791189599591726</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.21</v>
+      </c>
+      <c r="W20">
+        <v>0.036103</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>60.14849907586414</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1044674629183992</v>
+      </c>
+      <c r="C21">
+        <v>66.72929526609119</v>
+      </c>
+      <c r="D21">
+        <v>-4.814704733908825</v>
+      </c>
+      <c r="E21">
+        <v>9.555999999999999</v>
+      </c>
+      <c r="F21">
+        <v>15.656</v>
+      </c>
+      <c r="G21">
+        <v>87.2</v>
+      </c>
+      <c r="H21">
+        <v>76.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>45.1</v>
+      </c>
+      <c r="K21">
+        <v>4.33</v>
+      </c>
+      <c r="L21">
+        <v>40.77</v>
+      </c>
+      <c r="M21">
+        <v>0.7154792</v>
+      </c>
+      <c r="N21">
+        <v>40.05452080000001</v>
+      </c>
+      <c r="O21">
+        <v>8.411449368</v>
+      </c>
+      <c r="P21">
+        <v>31.64307143200001</v>
+      </c>
+      <c r="Q21">
+        <v>35.973071432</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1205035715041966</v>
+      </c>
+      <c r="T21">
+        <v>0.8880299173378104</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.21</v>
+      </c>
+      <c r="W21">
+        <v>0.036103</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>56.98278859818707</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1042957394811233</v>
+      </c>
+      <c r="C22">
+        <v>65.90464536291906</v>
+      </c>
+      <c r="D22">
+        <v>-4.815354637080948</v>
+      </c>
+      <c r="E22">
+        <v>10.38</v>
+      </c>
+      <c r="F22">
+        <v>16.48</v>
+      </c>
+      <c r="G22">
+        <v>87.2</v>
+      </c>
+      <c r="H22">
+        <v>76.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>45.1</v>
+      </c>
+      <c r="K22">
+        <v>4.33</v>
+      </c>
+      <c r="L22">
+        <v>40.77</v>
+      </c>
+      <c r="M22">
+        <v>0.7531360000000001</v>
+      </c>
+      <c r="N22">
+        <v>40.01686400000001</v>
+      </c>
+      <c r="O22">
+        <v>8.40354144</v>
+      </c>
+      <c r="P22">
+        <v>31.61332256000001</v>
+      </c>
+      <c r="Q22">
+        <v>35.94332256000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1213439243514041</v>
+      </c>
+      <c r="T22">
+        <v>0.897163648650914</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.21</v>
+      </c>
+      <c r="W22">
+        <v>0.036103</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>54.13364916827771</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1041240160438473</v>
+      </c>
+      <c r="C23">
+        <v>65.07999528427152</v>
+      </c>
+      <c r="D23">
+        <v>-4.816004715728488</v>
+      </c>
+      <c r="E23">
+        <v>11.204</v>
+      </c>
+      <c r="F23">
+        <v>17.304</v>
+      </c>
+      <c r="G23">
+        <v>87.2</v>
+      </c>
+      <c r="H23">
+        <v>76.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>45.1</v>
+      </c>
+      <c r="K23">
+        <v>4.33</v>
+      </c>
+      <c r="L23">
+        <v>40.77</v>
+      </c>
+      <c r="M23">
+        <v>0.7907928</v>
+      </c>
+      <c r="N23">
+        <v>39.9792072</v>
+      </c>
+      <c r="O23">
+        <v>8.395633512</v>
+      </c>
+      <c r="P23">
+        <v>31.583573688</v>
+      </c>
+      <c r="Q23">
+        <v>35.91357368800001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1222055519542371</v>
+      </c>
+      <c r="T23">
+        <v>0.906528613668147</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.21</v>
+      </c>
+      <c r="W23">
+        <v>0.036103</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>51.55585635074068</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1039522926065714</v>
+      </c>
+      <c r="C24">
+        <v>64.25534503007748</v>
+      </c>
+      <c r="D24">
+        <v>-4.816654969922519</v>
+      </c>
+      <c r="E24">
+        <v>12.028</v>
+      </c>
+      <c r="F24">
+        <v>18.128</v>
+      </c>
+      <c r="G24">
+        <v>87.2</v>
+      </c>
+      <c r="H24">
+        <v>76.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>45.1</v>
+      </c>
+      <c r="K24">
+        <v>4.33</v>
+      </c>
+      <c r="L24">
+        <v>40.77</v>
+      </c>
+      <c r="M24">
+        <v>0.8284495999999999</v>
+      </c>
+      <c r="N24">
+        <v>39.9415504</v>
+      </c>
+      <c r="O24">
+        <v>8.387725584</v>
+      </c>
+      <c r="P24">
+        <v>31.553824816</v>
+      </c>
+      <c r="Q24">
+        <v>35.883824816</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1230892725725274</v>
+      </c>
+      <c r="T24">
+        <v>0.9161337059935141</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.21</v>
+      </c>
+      <c r="W24">
+        <v>0.036103</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>49.21240833479793</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1037805691692954</v>
+      </c>
+      <c r="C25">
+        <v>63.43069460026585</v>
+      </c>
+      <c r="D25">
+        <v>-4.817305399734157</v>
+      </c>
+      <c r="E25">
+        <v>12.852</v>
+      </c>
+      <c r="F25">
+        <v>18.952</v>
+      </c>
+      <c r="G25">
+        <v>87.2</v>
+      </c>
+      <c r="H25">
+        <v>76.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>45.1</v>
+      </c>
+      <c r="K25">
+        <v>4.33</v>
+      </c>
+      <c r="L25">
+        <v>40.77</v>
+      </c>
+      <c r="M25">
+        <v>0.8661064000000001</v>
+      </c>
+      <c r="N25">
+        <v>39.9038936</v>
+      </c>
+      <c r="O25">
+        <v>8.379817656</v>
+      </c>
+      <c r="P25">
+        <v>31.524075944</v>
+      </c>
+      <c r="Q25">
+        <v>35.854075944</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1239959469731109</v>
+      </c>
+      <c r="T25">
+        <v>0.9259882812364232</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.21</v>
+      </c>
+      <c r="W25">
+        <v>0.036103</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>47.07273840719801</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1036088457320195</v>
+      </c>
+      <c r="C26">
+        <v>62.60604399476544</v>
+      </c>
+      <c r="D26">
+        <v>-4.817956005234559</v>
+      </c>
+      <c r="E26">
+        <v>13.676</v>
+      </c>
+      <c r="F26">
+        <v>19.776</v>
+      </c>
+      <c r="G26">
+        <v>87.2</v>
+      </c>
+      <c r="H26">
+        <v>76.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>45.1</v>
+      </c>
+      <c r="K26">
+        <v>4.33</v>
+      </c>
+      <c r="L26">
+        <v>40.77</v>
+      </c>
+      <c r="M26">
+        <v>0.9037631999999999</v>
+      </c>
+      <c r="N26">
+        <v>39.8662368</v>
+      </c>
+      <c r="O26">
+        <v>8.371909727999999</v>
+      </c>
+      <c r="P26">
+        <v>31.494327072</v>
+      </c>
+      <c r="Q26">
+        <v>35.824327072</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1249264812263414</v>
+      </c>
+      <c r="T26">
+        <v>0.9361021874067773</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.21</v>
+      </c>
+      <c r="W26">
+        <v>0.036103</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>45.1113743068981</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1034371222947435</v>
+      </c>
+      <c r="C27">
+        <v>61.7813932135051</v>
+      </c>
+      <c r="D27">
+        <v>-4.818606786494917</v>
+      </c>
+      <c r="E27">
+        <v>14.5</v>
+      </c>
+      <c r="F27">
+        <v>20.6</v>
+      </c>
+      <c r="G27">
+        <v>87.2</v>
+      </c>
+      <c r="H27">
+        <v>76.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>45.1</v>
+      </c>
+      <c r="K27">
+        <v>4.33</v>
+      </c>
+      <c r="L27">
+        <v>40.77</v>
+      </c>
+      <c r="M27">
+        <v>0.94142</v>
+      </c>
+      <c r="N27">
+        <v>39.82858</v>
+      </c>
+      <c r="O27">
+        <v>8.364001799999999</v>
+      </c>
+      <c r="P27">
+        <v>31.46457820000001</v>
+      </c>
+      <c r="Q27">
+        <v>35.7945782</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1258818297263247</v>
+      </c>
+      <c r="T27">
+        <v>0.9464857977416741</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.21</v>
+      </c>
+      <c r="W27">
+        <v>0.036103</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>43.30691933462217</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1032653988574676</v>
+      </c>
+      <c r="C28">
+        <v>60.95674225641354</v>
+      </c>
+      <c r="D28">
+        <v>-4.819257743586462</v>
+      </c>
+      <c r="E28">
+        <v>15.324</v>
+      </c>
+      <c r="F28">
+        <v>21.424</v>
+      </c>
+      <c r="G28">
+        <v>87.2</v>
+      </c>
+      <c r="H28">
+        <v>76.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>45.1</v>
+      </c>
+      <c r="K28">
+        <v>4.33</v>
+      </c>
+      <c r="L28">
+        <v>40.77</v>
+      </c>
+      <c r="M28">
+        <v>0.9790768000000001</v>
+      </c>
+      <c r="N28">
+        <v>39.7909232</v>
+      </c>
+      <c r="O28">
+        <v>8.356093871999999</v>
+      </c>
+      <c r="P28">
+        <v>31.434829328</v>
+      </c>
+      <c r="Q28">
+        <v>35.764829328</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1268629984560373</v>
+      </c>
+      <c r="T28">
+        <v>0.9571500461937303</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.21</v>
+      </c>
+      <c r="W28">
+        <v>0.036103</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>41.64126859098285</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1030936754201916</v>
+      </c>
+      <c r="C29">
+        <v>60.13209112341953</v>
+      </c>
+      <c r="D29">
+        <v>-4.819908876580465</v>
+      </c>
+      <c r="E29">
+        <v>16.148</v>
+      </c>
+      <c r="F29">
+        <v>22.248</v>
+      </c>
+      <c r="G29">
+        <v>87.2</v>
+      </c>
+      <c r="H29">
+        <v>76.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>45.1</v>
+      </c>
+      <c r="K29">
+        <v>4.33</v>
+      </c>
+      <c r="L29">
+        <v>40.77</v>
+      </c>
+      <c r="M29">
+        <v>1.0167336</v>
+      </c>
+      <c r="N29">
+        <v>39.7532664</v>
+      </c>
+      <c r="O29">
+        <v>8.348185943999999</v>
+      </c>
+      <c r="P29">
+        <v>31.405080456</v>
+      </c>
+      <c r="Q29">
+        <v>35.735080456</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1278710485208104</v>
+      </c>
+      <c r="T29">
+        <v>0.9681064658362539</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.21</v>
+      </c>
+      <c r="W29">
+        <v>0.036103</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>40.09899938390942</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1029219519829157</v>
+      </c>
+      <c r="C30">
+        <v>59.30743981445177</v>
+      </c>
+      <c r="D30">
+        <v>-4.820560185548234</v>
+      </c>
+      <c r="E30">
+        <v>16.972</v>
+      </c>
+      <c r="F30">
+        <v>23.072</v>
+      </c>
+      <c r="G30">
+        <v>87.2</v>
+      </c>
+      <c r="H30">
+        <v>76.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>45.1</v>
+      </c>
+      <c r="K30">
+        <v>4.33</v>
+      </c>
+      <c r="L30">
+        <v>40.77</v>
+      </c>
+      <c r="M30">
+        <v>1.0543904</v>
+      </c>
+      <c r="N30">
+        <v>39.7156096</v>
+      </c>
+      <c r="O30">
+        <v>8.340278015999999</v>
+      </c>
+      <c r="P30">
+        <v>31.375331584</v>
+      </c>
+      <c r="Q30">
+        <v>35.705331584</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1289070999762718</v>
+      </c>
+      <c r="T30">
+        <v>0.9793672304688475</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.21</v>
+      </c>
+      <c r="W30">
+        <v>0.036103</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>38.6668922630555</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1027502285456397</v>
+      </c>
+      <c r="C31">
+        <v>58.48278832943889</v>
+      </c>
+      <c r="D31">
+        <v>-4.821211670561116</v>
+      </c>
+      <c r="E31">
+        <v>17.796</v>
+      </c>
+      <c r="F31">
+        <v>23.896</v>
+      </c>
+      <c r="G31">
+        <v>87.2</v>
+      </c>
+      <c r="H31">
+        <v>76.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>45.1</v>
+      </c>
+      <c r="K31">
+        <v>4.33</v>
+      </c>
+      <c r="L31">
+        <v>40.77</v>
+      </c>
+      <c r="M31">
+        <v>1.0920472</v>
+      </c>
+      <c r="N31">
+        <v>39.6779528</v>
+      </c>
+      <c r="O31">
+        <v>8.332370087999999</v>
+      </c>
+      <c r="P31">
+        <v>31.345582712</v>
+      </c>
+      <c r="Q31">
+        <v>35.675582712</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1299723359797743</v>
+      </c>
+      <c r="T31">
+        <v>0.990945199738979</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.21</v>
+      </c>
+      <c r="W31">
+        <v>0.036103</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>37.33355115053635</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1025785051083638</v>
+      </c>
+      <c r="C32">
+        <v>57.65813666830951</v>
+      </c>
+      <c r="D32">
+        <v>-4.821863331690496</v>
+      </c>
+      <c r="E32">
+        <v>18.62</v>
+      </c>
+      <c r="F32">
+        <v>24.72</v>
+      </c>
+      <c r="G32">
+        <v>87.2</v>
+      </c>
+      <c r="H32">
+        <v>76.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>45.1</v>
+      </c>
+      <c r="K32">
+        <v>4.33</v>
+      </c>
+      <c r="L32">
+        <v>40.77</v>
+      </c>
+      <c r="M32">
+        <v>1.129704</v>
+      </c>
+      <c r="N32">
+        <v>39.64029600000001</v>
+      </c>
+      <c r="O32">
+        <v>8.324462159999999</v>
+      </c>
+      <c r="P32">
+        <v>31.31583384000001</v>
+      </c>
+      <c r="Q32">
+        <v>35.64583384000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1310680072976625</v>
+      </c>
+      <c r="T32">
+        <v>1.002853968131114</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.21</v>
+      </c>
+      <c r="W32">
+        <v>0.036103</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>36.08909944551849</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1024067816710878</v>
+      </c>
+      <c r="C33">
+        <v>56.83348483099221</v>
+      </c>
+      <c r="D33">
+        <v>-4.822515169007799</v>
+      </c>
+      <c r="E33">
+        <v>19.444</v>
+      </c>
+      <c r="F33">
+        <v>25.544</v>
+      </c>
+      <c r="G33">
+        <v>87.2</v>
+      </c>
+      <c r="H33">
+        <v>76.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>45.1</v>
+      </c>
+      <c r="K33">
+        <v>4.33</v>
+      </c>
+      <c r="L33">
+        <v>40.77</v>
+      </c>
+      <c r="M33">
+        <v>1.1673608</v>
+      </c>
+      <c r="N33">
+        <v>39.60263920000001</v>
+      </c>
+      <c r="O33">
+        <v>8.316554232</v>
+      </c>
+      <c r="P33">
+        <v>31.286084968</v>
+      </c>
+      <c r="Q33">
+        <v>35.616084968</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1321954372044751</v>
+      </c>
+      <c r="T33">
+        <v>1.015107918215775</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.21</v>
+      </c>
+      <c r="W33">
+        <v>0.036103</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>34.92493494727594</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1022350582338119</v>
+      </c>
+      <c r="C34">
+        <v>56.00883281741552</v>
+      </c>
+      <c r="D34">
+        <v>-4.823167182584488</v>
+      </c>
+      <c r="E34">
+        <v>20.268</v>
+      </c>
+      <c r="F34">
+        <v>26.368</v>
+      </c>
+      <c r="G34">
+        <v>87.2</v>
+      </c>
+      <c r="H34">
+        <v>76.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>45.1</v>
+      </c>
+      <c r="K34">
+        <v>4.33</v>
+      </c>
+      <c r="L34">
+        <v>40.77</v>
+      </c>
+      <c r="M34">
+        <v>1.2050176</v>
+      </c>
+      <c r="N34">
+        <v>39.56498240000001</v>
+      </c>
+      <c r="O34">
+        <v>8.308646304</v>
+      </c>
+      <c r="P34">
+        <v>31.25633609600001</v>
+      </c>
+      <c r="Q34">
+        <v>35.586336096</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1333560268144293</v>
+      </c>
+      <c r="T34">
+        <v>1.027722278597044</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.21</v>
+      </c>
+      <c r="W34">
+        <v>0.036103</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>33.83353073017357</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1020633347965359</v>
+      </c>
+      <c r="C35">
+        <v>55.18418062750793</v>
+      </c>
+      <c r="D35">
+        <v>-4.823819372492064</v>
+      </c>
+      <c r="E35">
+        <v>21.092</v>
+      </c>
+      <c r="F35">
+        <v>27.192</v>
+      </c>
+      <c r="G35">
+        <v>87.2</v>
+      </c>
+      <c r="H35">
+        <v>76.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>45.1</v>
+      </c>
+      <c r="K35">
+        <v>4.33</v>
+      </c>
+      <c r="L35">
+        <v>40.77</v>
+      </c>
+      <c r="M35">
+        <v>1.2426744</v>
+      </c>
+      <c r="N35">
+        <v>39.5273256</v>
+      </c>
+      <c r="O35">
+        <v>8.300738376</v>
+      </c>
+      <c r="P35">
+        <v>31.22658722400001</v>
+      </c>
+      <c r="Q35">
+        <v>35.556587224</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1345512608903521</v>
+      </c>
+      <c r="T35">
+        <v>1.040713187049395</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.21</v>
+      </c>
+      <c r="W35">
+        <v>0.036103</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>32.80827222319861</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.10189161135926</v>
+      </c>
+      <c r="C36">
+        <v>54.35952826119793</v>
+      </c>
+      <c r="D36">
+        <v>-4.824471738802067</v>
+      </c>
+      <c r="E36">
+        <v>21.916</v>
+      </c>
+      <c r="F36">
+        <v>28.016</v>
+      </c>
+      <c r="G36">
+        <v>87.2</v>
+      </c>
+      <c r="H36">
+        <v>76.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>45.1</v>
+      </c>
+      <c r="K36">
+        <v>4.33</v>
+      </c>
+      <c r="L36">
+        <v>40.77</v>
+      </c>
+      <c r="M36">
+        <v>1.2803312</v>
+      </c>
+      <c r="N36">
+        <v>39.4896688</v>
+      </c>
+      <c r="O36">
+        <v>8.292830448</v>
+      </c>
+      <c r="P36">
+        <v>31.196838352</v>
+      </c>
+      <c r="Q36">
+        <v>35.52683835200001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.135782714180697</v>
+      </c>
+      <c r="T36">
+        <v>1.054097759394242</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.21</v>
+      </c>
+      <c r="W36">
+        <v>0.036103</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>31.84332304016336</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.101719887921984</v>
+      </c>
+      <c r="C37">
+        <v>53.53487571841393</v>
+      </c>
+      <c r="D37">
+        <v>-4.825124281586078</v>
+      </c>
+      <c r="E37">
+        <v>22.74</v>
+      </c>
+      <c r="F37">
+        <v>28.84</v>
+      </c>
+      <c r="G37">
+        <v>87.2</v>
+      </c>
+      <c r="H37">
+        <v>76.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>45.1</v>
+      </c>
+      <c r="K37">
+        <v>4.33</v>
+      </c>
+      <c r="L37">
+        <v>40.77</v>
+      </c>
+      <c r="M37">
+        <v>1.317988</v>
+      </c>
+      <c r="N37">
+        <v>39.452012</v>
+      </c>
+      <c r="O37">
+        <v>8.284922519999999</v>
+      </c>
+      <c r="P37">
+        <v>31.16708948</v>
+      </c>
+      <c r="Q37">
+        <v>35.49708948000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1370520583415139</v>
+      </c>
+      <c r="T37">
+        <v>1.067894164734314</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.21</v>
+      </c>
+      <c r="W37">
+        <v>0.036103</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>30.9335138104444</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1015481644847081</v>
+      </c>
+      <c r="C38">
+        <v>52.7102229990843</v>
+      </c>
+      <c r="D38">
+        <v>-4.825777000915712</v>
+      </c>
+      <c r="E38">
+        <v>23.56399999999999</v>
+      </c>
+      <c r="F38">
+        <v>29.66399999999999</v>
+      </c>
+      <c r="G38">
+        <v>87.2</v>
+      </c>
+      <c r="H38">
+        <v>76.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>45.1</v>
+      </c>
+      <c r="K38">
+        <v>4.33</v>
+      </c>
+      <c r="L38">
+        <v>40.77</v>
+      </c>
+      <c r="M38">
+        <v>1.3556448</v>
+      </c>
+      <c r="N38">
+        <v>39.4143552</v>
+      </c>
+      <c r="O38">
+        <v>8.277014591999999</v>
+      </c>
+      <c r="P38">
+        <v>31.137340608</v>
+      </c>
+      <c r="Q38">
+        <v>35.467340608</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1383610695073564</v>
+      </c>
+      <c r="T38">
+        <v>1.082121707741264</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.21</v>
+      </c>
+      <c r="W38">
+        <v>0.036103</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>30.07424953793207</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1013764410474321</v>
+      </c>
+      <c r="C39">
+        <v>51.88557010313738</v>
+      </c>
+      <c r="D39">
+        <v>-4.826429896862626</v>
+      </c>
+      <c r="E39">
+        <v>24.388</v>
+      </c>
+      <c r="F39">
+        <v>30.488</v>
+      </c>
+      <c r="G39">
+        <v>87.2</v>
+      </c>
+      <c r="H39">
+        <v>76.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>45.1</v>
+      </c>
+      <c r="K39">
+        <v>4.33</v>
+      </c>
+      <c r="L39">
+        <v>40.77</v>
+      </c>
+      <c r="M39">
+        <v>1.3933016</v>
+      </c>
+      <c r="N39">
+        <v>39.3766984</v>
+      </c>
+      <c r="O39">
+        <v>8.269106663999999</v>
+      </c>
+      <c r="P39">
+        <v>31.107591736</v>
+      </c>
+      <c r="Q39">
+        <v>35.437591736</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1397116365832256</v>
+      </c>
+      <c r="T39">
+        <v>1.096800918780181</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.21</v>
+      </c>
+      <c r="W39">
+        <v>0.036103</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>29.26143198285282</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1012047176101562</v>
+      </c>
+      <c r="C40">
+        <v>51.06091703050149</v>
+      </c>
+      <c r="D40">
+        <v>-4.827082969498516</v>
+      </c>
+      <c r="E40">
+        <v>25.212</v>
+      </c>
+      <c r="F40">
+        <v>31.312</v>
+      </c>
+      <c r="G40">
+        <v>87.2</v>
+      </c>
+      <c r="H40">
+        <v>76.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>45.1</v>
+      </c>
+      <c r="K40">
+        <v>4.33</v>
+      </c>
+      <c r="L40">
+        <v>40.77</v>
+      </c>
+      <c r="M40">
+        <v>1.4309584</v>
+      </c>
+      <c r="N40">
+        <v>39.3390416</v>
+      </c>
+      <c r="O40">
+        <v>8.261198735999999</v>
+      </c>
+      <c r="P40">
+        <v>31.077842864</v>
+      </c>
+      <c r="Q40">
+        <v>35.407842864</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1411057703389616</v>
+      </c>
+      <c r="T40">
+        <v>1.111953652755837</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.21</v>
+      </c>
+      <c r="W40">
+        <v>0.036103</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>28.49139429909353</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1010329941728803</v>
+      </c>
+      <c r="C41">
+        <v>50.2362637811049</v>
+      </c>
+      <c r="D41">
+        <v>-4.827736218895114</v>
+      </c>
+      <c r="E41">
+        <v>26.03599999999999</v>
+      </c>
+      <c r="F41">
+        <v>32.136</v>
+      </c>
+      <c r="G41">
+        <v>87.2</v>
+      </c>
+      <c r="H41">
+        <v>76.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>45.1</v>
+      </c>
+      <c r="K41">
+        <v>4.33</v>
+      </c>
+      <c r="L41">
+        <v>40.77</v>
+      </c>
+      <c r="M41">
+        <v>1.4686152</v>
+      </c>
+      <c r="N41">
+        <v>39.3013848</v>
+      </c>
+      <c r="O41">
+        <v>8.253290807999999</v>
+      </c>
+      <c r="P41">
+        <v>31.048093992</v>
+      </c>
+      <c r="Q41">
+        <v>35.378093992</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1425456133981644</v>
+      </c>
+      <c r="T41">
+        <v>1.127603197681514</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0.21</v>
+      </c>
+      <c r="W41">
+        <v>0.036103</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>27.7608457273219</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1008612707356043</v>
+      </c>
+      <c r="C42">
+        <v>49.41161035487581</v>
+      </c>
+      <c r="D42">
+        <v>-4.828389645124196</v>
+      </c>
+      <c r="E42">
+        <v>26.86</v>
+      </c>
+      <c r="F42">
+        <v>32.96</v>
+      </c>
+      <c r="G42">
+        <v>87.2</v>
+      </c>
+      <c r="H42">
+        <v>76.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>45.1</v>
+      </c>
+      <c r="K42">
+        <v>4.33</v>
+      </c>
+      <c r="L42">
+        <v>40.77</v>
+      </c>
+      <c r="M42">
+        <v>1.506272</v>
+      </c>
+      <c r="N42">
+        <v>39.263728</v>
+      </c>
+      <c r="O42">
+        <v>8.245382879999999</v>
+      </c>
+      <c r="P42">
+        <v>31.01834512</v>
+      </c>
+      <c r="Q42">
+        <v>35.34834512</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1440334512260072</v>
+      </c>
+      <c r="T42">
+        <v>1.143774394104714</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0.21</v>
+      </c>
+      <c r="W42">
+        <v>0.036103</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>27.06682458413885</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1006895472983283</v>
+      </c>
+      <c r="C43">
+        <v>48.58695675174243</v>
+      </c>
+      <c r="D43">
+        <v>-4.829043248257572</v>
+      </c>
+      <c r="E43">
+        <v>27.684</v>
+      </c>
+      <c r="F43">
+        <v>33.784</v>
+      </c>
+      <c r="G43">
+        <v>87.2</v>
+      </c>
+      <c r="H43">
+        <v>76.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>45.1</v>
+      </c>
+      <c r="K43">
+        <v>4.33</v>
+      </c>
+      <c r="L43">
+        <v>40.77</v>
+      </c>
+      <c r="M43">
+        <v>1.5439288</v>
+      </c>
+      <c r="N43">
+        <v>39.2260712</v>
+      </c>
+      <c r="O43">
+        <v>8.237474951999998</v>
+      </c>
+      <c r="P43">
+        <v>30.988596248</v>
+      </c>
+      <c r="Q43">
+        <v>35.318596248</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1455717242344548</v>
+      </c>
+      <c r="T43">
+        <v>1.160493766677853</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0.21</v>
+      </c>
+      <c r="W43">
+        <v>0.036103</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>26.40665813086717</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1005178238610524</v>
+      </c>
+      <c r="C44">
+        <v>47.76230297163291</v>
+      </c>
+      <c r="D44">
+        <v>-4.829697028367093</v>
+      </c>
+      <c r="E44">
+        <v>28.508</v>
+      </c>
+      <c r="F44">
+        <v>34.608</v>
+      </c>
+      <c r="G44">
+        <v>87.2</v>
+      </c>
+      <c r="H44">
+        <v>76.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>45.1</v>
+      </c>
+      <c r="K44">
+        <v>4.33</v>
+      </c>
+      <c r="L44">
+        <v>40.77</v>
+      </c>
+      <c r="M44">
+        <v>1.5815856</v>
+      </c>
+      <c r="N44">
+        <v>39.18841440000001</v>
+      </c>
+      <c r="O44">
+        <v>8.229567024</v>
+      </c>
+      <c r="P44">
+        <v>30.95884737600001</v>
+      </c>
+      <c r="Q44">
+        <v>35.28884737600001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1471630411397455</v>
+      </c>
+      <c r="T44">
+        <v>1.177789669339721</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0.21</v>
+      </c>
+      <c r="W44">
+        <v>0.036103</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>25.77792817537034</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1003461004237765</v>
+      </c>
+      <c r="C45">
+        <v>46.93764901447536</v>
+      </c>
+      <c r="D45">
+        <v>-4.830350985524648</v>
+      </c>
+      <c r="E45">
+        <v>29.33199999999999</v>
+      </c>
+      <c r="F45">
+        <v>35.432</v>
+      </c>
+      <c r="G45">
+        <v>87.2</v>
+      </c>
+      <c r="H45">
+        <v>76.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>45.1</v>
+      </c>
+      <c r="K45">
+        <v>4.33</v>
+      </c>
+      <c r="L45">
+        <v>40.77</v>
+      </c>
+      <c r="M45">
+        <v>1.6192424</v>
+      </c>
+      <c r="N45">
+        <v>39.15075760000001</v>
+      </c>
+      <c r="O45">
+        <v>8.221659096</v>
+      </c>
+      <c r="P45">
+        <v>30.92909850400001</v>
+      </c>
+      <c r="Q45">
+        <v>35.25909850400001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1488101937259236</v>
+      </c>
+      <c r="T45">
+        <v>1.195692445779199</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0.21</v>
+      </c>
+      <c r="W45">
+        <v>0.036103</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>25.17844147361754</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1001743769865005</v>
+      </c>
+      <c r="C46">
+        <v>46.11299488019785</v>
+      </c>
+      <c r="D46">
+        <v>-4.831005119802164</v>
+      </c>
+      <c r="E46">
+        <v>30.15599999999999</v>
+      </c>
+      <c r="F46">
+        <v>36.25599999999999</v>
+      </c>
+      <c r="G46">
+        <v>87.2</v>
+      </c>
+      <c r="H46">
+        <v>76.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>45.1</v>
+      </c>
+      <c r="K46">
+        <v>4.33</v>
+      </c>
+      <c r="L46">
+        <v>40.77</v>
+      </c>
+      <c r="M46">
+        <v>1.6568992</v>
+      </c>
+      <c r="N46">
+        <v>39.11310080000001</v>
+      </c>
+      <c r="O46">
+        <v>8.213751168</v>
+      </c>
+      <c r="P46">
+        <v>30.899349632</v>
+      </c>
+      <c r="Q46">
+        <v>35.229349632</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1505161731901795</v>
+      </c>
+      <c r="T46">
+        <v>1.214234607091514</v>
+      </c>
+      <c r="U46">
+        <v>0.0457</v>
+      </c>
+      <c r="V46">
+        <v>0.21</v>
+      </c>
+      <c r="W46">
+        <v>0.036103</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>24.60620416739896</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1000026535492246</v>
+      </c>
+      <c r="C47">
+        <v>45.2883405687284</v>
+      </c>
+      <c r="D47">
+        <v>-4.831659431271611</v>
+      </c>
+      <c r="E47">
+        <v>30.98</v>
+      </c>
+      <c r="F47">
+        <v>37.08</v>
+      </c>
+      <c r="G47">
+        <v>87.2</v>
+      </c>
+      <c r="H47">
+        <v>76.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>45.1</v>
+      </c>
+      <c r="K47">
+        <v>4.33</v>
+      </c>
+      <c r="L47">
+        <v>40.77</v>
+      </c>
+      <c r="M47">
+        <v>1.694556</v>
+      </c>
+      <c r="N47">
+        <v>39.075444</v>
+      </c>
+      <c r="O47">
+        <v>8.20584324</v>
+      </c>
+      <c r="P47">
+        <v>30.86960076</v>
+      </c>
+      <c r="Q47">
+        <v>35.19960076</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1522841882713174</v>
+      </c>
+      <c r="T47">
+        <v>1.233451028815187</v>
+      </c>
+      <c r="U47">
+        <v>0.0457</v>
+      </c>
+      <c r="V47">
+        <v>0.21</v>
+      </c>
+      <c r="W47">
+        <v>0.036103</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>24.05939963034565</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.09983093011194862</v>
+      </c>
+      <c r="C48">
+        <v>44.46368607999501</v>
+      </c>
+      <c r="D48">
+        <v>-4.832313920004994</v>
+      </c>
+      <c r="E48">
+        <v>31.80399999999999</v>
+      </c>
+      <c r="F48">
+        <v>37.904</v>
+      </c>
+      <c r="G48">
+        <v>87.2</v>
+      </c>
+      <c r="H48">
+        <v>76.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>45.1</v>
+      </c>
+      <c r="K48">
+        <v>4.33</v>
+      </c>
+      <c r="L48">
+        <v>40.77</v>
+      </c>
+      <c r="M48">
+        <v>1.7322128</v>
+      </c>
+      <c r="N48">
+        <v>39.0377872</v>
+      </c>
+      <c r="O48">
+        <v>8.197935312</v>
+      </c>
+      <c r="P48">
+        <v>30.83985188800001</v>
+      </c>
+      <c r="Q48">
+        <v>35.169851888</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1541176853924974</v>
+      </c>
+      <c r="T48">
+        <v>1.253379169861959</v>
+      </c>
+      <c r="U48">
+        <v>0.0457</v>
+      </c>
+      <c r="V48">
+        <v>0.21</v>
+      </c>
+      <c r="W48">
+        <v>0.036103</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>23.536369203599</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.09965920667467267</v>
+      </c>
+      <c r="C49">
+        <v>43.63903141392564</v>
+      </c>
+      <c r="D49">
+        <v>-4.83296858607436</v>
+      </c>
+      <c r="E49">
+        <v>32.628</v>
+      </c>
+      <c r="F49">
+        <v>38.728</v>
+      </c>
+      <c r="G49">
+        <v>87.2</v>
+      </c>
+      <c r="H49">
+        <v>76.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>45.1</v>
+      </c>
+      <c r="K49">
+        <v>4.33</v>
+      </c>
+      <c r="L49">
+        <v>40.77</v>
+      </c>
+      <c r="M49">
+        <v>1.7698696</v>
+      </c>
+      <c r="N49">
+        <v>39.0001304</v>
+      </c>
+      <c r="O49">
+        <v>8.190027383999999</v>
+      </c>
+      <c r="P49">
+        <v>30.81010301600001</v>
+      </c>
+      <c r="Q49">
+        <v>35.140103016</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.156020371084288</v>
+      </c>
+      <c r="T49">
+        <v>1.274059316231251</v>
+      </c>
+      <c r="U49">
+        <v>0.0457</v>
+      </c>
+      <c r="V49">
+        <v>0.21</v>
+      </c>
+      <c r="W49">
+        <v>0.036103</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>23.03559539075647</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.0994874832373967</v>
+      </c>
+      <c r="C50">
+        <v>42.81437657044822</v>
+      </c>
+      <c r="D50">
+        <v>-4.83362342955179</v>
+      </c>
+      <c r="E50">
+        <v>33.45199999999999</v>
+      </c>
+      <c r="F50">
+        <v>39.55199999999999</v>
+      </c>
+      <c r="G50">
+        <v>87.2</v>
+      </c>
+      <c r="H50">
+        <v>76.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>45.1</v>
+      </c>
+      <c r="K50">
+        <v>4.33</v>
+      </c>
+      <c r="L50">
+        <v>40.77</v>
+      </c>
+      <c r="M50">
+        <v>1.8075264</v>
+      </c>
+      <c r="N50">
+        <v>38.9624736</v>
+      </c>
+      <c r="O50">
+        <v>8.182119455999999</v>
+      </c>
+      <c r="P50">
+        <v>30.780354144</v>
+      </c>
+      <c r="Q50">
+        <v>35.11035414400001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1579962369949937</v>
+      </c>
+      <c r="T50">
+        <v>1.295534852845515</v>
+      </c>
+      <c r="U50">
+        <v>0.0457</v>
+      </c>
+      <c r="V50">
+        <v>0.21</v>
+      </c>
+      <c r="W50">
+        <v>0.036103</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>22.55568715344905</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.09931575980012075</v>
+      </c>
+      <c r="C51">
+        <v>41.98972154949059</v>
+      </c>
+      <c r="D51">
+        <v>-4.834278450509411</v>
+      </c>
+      <c r="E51">
+        <v>34.276</v>
+      </c>
+      <c r="F51">
+        <v>40.376</v>
+      </c>
+      <c r="G51">
+        <v>87.2</v>
+      </c>
+      <c r="H51">
+        <v>76.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>45.1</v>
+      </c>
+      <c r="K51">
+        <v>4.33</v>
+      </c>
+      <c r="L51">
+        <v>40.77</v>
+      </c>
+      <c r="M51">
+        <v>1.8451832</v>
+      </c>
+      <c r="N51">
+        <v>38.9248168</v>
+      </c>
+      <c r="O51">
+        <v>8.174211527999999</v>
+      </c>
+      <c r="P51">
+        <v>30.750605272</v>
+      </c>
+      <c r="Q51">
+        <v>35.080605272</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.160049587843374</v>
+      </c>
+      <c r="T51">
+        <v>1.31785256736622</v>
+      </c>
+      <c r="U51">
+        <v>0.0457</v>
+      </c>
+      <c r="V51">
+        <v>0.21</v>
+      </c>
+      <c r="W51">
+        <v>0.036103</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>22.09536700746029</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.0991440363628448</v>
+      </c>
+      <c r="C52">
+        <v>41.16506635098062</v>
+      </c>
+      <c r="D52">
+        <v>-4.834933649019385</v>
+      </c>
+      <c r="E52">
+        <v>35.09999999999999</v>
+      </c>
+      <c r="F52">
+        <v>41.2</v>
+      </c>
+      <c r="G52">
+        <v>87.2</v>
+      </c>
+      <c r="H52">
+        <v>76.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>45.1</v>
+      </c>
+      <c r="K52">
+        <v>4.33</v>
+      </c>
+      <c r="L52">
+        <v>40.77</v>
+      </c>
+      <c r="M52">
+        <v>1.88284</v>
+      </c>
+      <c r="N52">
+        <v>38.88716</v>
+      </c>
+      <c r="O52">
+        <v>8.166303599999999</v>
+      </c>
+      <c r="P52">
+        <v>30.7208564</v>
+      </c>
+      <c r="Q52">
+        <v>35.0508564</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1621850727256896</v>
+      </c>
+      <c r="T52">
+        <v>1.341062990467755</v>
+      </c>
+      <c r="U52">
+        <v>0.0457</v>
+      </c>
+      <c r="V52">
+        <v>0.21</v>
+      </c>
+      <c r="W52">
+        <v>0.036103</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>21.65345966731108</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.09897231292556888</v>
+      </c>
+      <c r="C53">
+        <v>40.3404109748461</v>
+      </c>
+      <c r="D53">
+        <v>-4.835589025153912</v>
+      </c>
+      <c r="E53">
+        <v>35.92399999999999</v>
+      </c>
+      <c r="F53">
+        <v>42.02399999999999</v>
+      </c>
+      <c r="G53">
+        <v>87.2</v>
+      </c>
+      <c r="H53">
+        <v>76.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>45.1</v>
+      </c>
+      <c r="K53">
+        <v>4.33</v>
+      </c>
+      <c r="L53">
+        <v>40.77</v>
+      </c>
+      <c r="M53">
+        <v>1.9204968</v>
+      </c>
+      <c r="N53">
+        <v>38.8495032</v>
+      </c>
+      <c r="O53">
+        <v>8.158395671999999</v>
+      </c>
+      <c r="P53">
+        <v>30.691107528</v>
+      </c>
+      <c r="Q53">
+        <v>35.021107528</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.164407720256263</v>
+      </c>
+      <c r="T53">
+        <v>1.365220777777515</v>
+      </c>
+      <c r="U53">
+        <v>0.0457</v>
+      </c>
+      <c r="V53">
+        <v>0.21</v>
+      </c>
+      <c r="W53">
+        <v>0.036103</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>21.22888202677557</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.0988005894882929</v>
+      </c>
+      <c r="C54">
+        <v>39.51575542101477</v>
+      </c>
+      <c r="D54">
+        <v>-4.836244578985234</v>
+      </c>
+      <c r="E54">
+        <v>36.748</v>
+      </c>
+      <c r="F54">
+        <v>42.848</v>
+      </c>
+      <c r="G54">
+        <v>87.2</v>
+      </c>
+      <c r="H54">
+        <v>76.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>45.1</v>
+      </c>
+      <c r="K54">
+        <v>4.33</v>
+      </c>
+      <c r="L54">
+        <v>40.77</v>
+      </c>
+      <c r="M54">
+        <v>1.9581536</v>
+      </c>
+      <c r="N54">
+        <v>38.8118464</v>
+      </c>
+      <c r="O54">
+        <v>8.150487743999999</v>
+      </c>
+      <c r="P54">
+        <v>30.661358656</v>
+      </c>
+      <c r="Q54">
+        <v>34.991358656</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1667229781006102</v>
+      </c>
+      <c r="T54">
+        <v>1.390385139558515</v>
+      </c>
+      <c r="U54">
+        <v>0.0457</v>
+      </c>
+      <c r="V54">
+        <v>0.21</v>
+      </c>
+      <c r="W54">
+        <v>0.036103</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>20.82063429549142</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.09862886605101696</v>
+      </c>
+      <c r="C55">
+        <v>38.69109968941437</v>
+      </c>
+      <c r="D55">
+        <v>-4.836900310585632</v>
+      </c>
+      <c r="E55">
+        <v>37.572</v>
+      </c>
+      <c r="F55">
+        <v>43.672</v>
+      </c>
+      <c r="G55">
+        <v>87.2</v>
+      </c>
+      <c r="H55">
+        <v>76.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>45.1</v>
+      </c>
+      <c r="K55">
+        <v>4.33</v>
+      </c>
+      <c r="L55">
+        <v>40.77</v>
+      </c>
+      <c r="M55">
+        <v>1.9958104</v>
+      </c>
+      <c r="N55">
+        <v>38.7741896</v>
+      </c>
+      <c r="O55">
+        <v>8.142579815999998</v>
+      </c>
+      <c r="P55">
+        <v>30.631609784</v>
+      </c>
+      <c r="Q55">
+        <v>34.961609784</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1691367575553552</v>
+      </c>
+      <c r="T55">
+        <v>1.416620325245089</v>
+      </c>
+      <c r="U55">
+        <v>0.0457</v>
+      </c>
+      <c r="V55">
+        <v>0.21</v>
+      </c>
+      <c r="W55">
+        <v>0.036103</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>20.42779213897272</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.09845714261374101</v>
+      </c>
+      <c r="C56">
+        <v>37.86644377997258</v>
+      </c>
+      <c r="D56">
+        <v>-4.837556220027424</v>
+      </c>
+      <c r="E56">
+        <v>38.39599999999999</v>
+      </c>
+      <c r="F56">
+        <v>44.496</v>
+      </c>
+      <c r="G56">
+        <v>87.2</v>
+      </c>
+      <c r="H56">
+        <v>76.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>45.1</v>
+      </c>
+      <c r="K56">
+        <v>4.33</v>
+      </c>
+      <c r="L56">
+        <v>40.77</v>
+      </c>
+      <c r="M56">
+        <v>2.0334672</v>
+      </c>
+      <c r="N56">
+        <v>38.73653280000001</v>
+      </c>
+      <c r="O56">
+        <v>8.134671888</v>
+      </c>
+      <c r="P56">
+        <v>30.60186091200001</v>
+      </c>
+      <c r="Q56">
+        <v>34.931860912</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1716554839429152</v>
+      </c>
+      <c r="T56">
+        <v>1.443996171178906</v>
+      </c>
+      <c r="U56">
+        <v>0.0457</v>
+      </c>
+      <c r="V56">
+        <v>0.21</v>
+      </c>
+      <c r="W56">
+        <v>0.036103</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>20.04949969195471</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.09828541917646506</v>
+      </c>
+      <c r="C57">
+        <v>37.04178769261703</v>
+      </c>
+      <c r="D57">
+        <v>-4.838212307382968</v>
+      </c>
+      <c r="E57">
+        <v>39.22</v>
+      </c>
+      <c r="F57">
+        <v>45.32</v>
+      </c>
+      <c r="G57">
+        <v>87.2</v>
+      </c>
+      <c r="H57">
+        <v>76.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>45.1</v>
+      </c>
+      <c r="K57">
+        <v>4.33</v>
+      </c>
+      <c r="L57">
+        <v>40.77</v>
+      </c>
+      <c r="M57">
+        <v>2.071124</v>
+      </c>
+      <c r="N57">
+        <v>38.69887600000001</v>
+      </c>
+      <c r="O57">
+        <v>8.12676396</v>
+      </c>
+      <c r="P57">
+        <v>30.57211204000001</v>
+      </c>
+      <c r="Q57">
+        <v>34.90211204000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1742861537254779</v>
+      </c>
+      <c r="T57">
+        <v>1.472588721376448</v>
+      </c>
+      <c r="U57">
+        <v>0.0457</v>
+      </c>
+      <c r="V57">
+        <v>0.21</v>
+      </c>
+      <c r="W57">
+        <v>0.036103</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>19.68496333391917</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.09811369573918911</v>
+      </c>
+      <c r="C58">
+        <v>36.21713142727534</v>
+      </c>
+      <c r="D58">
+        <v>-4.838868572724665</v>
+      </c>
+      <c r="E58">
+        <v>40.044</v>
+      </c>
+      <c r="F58">
+        <v>46.144</v>
+      </c>
+      <c r="G58">
+        <v>87.2</v>
+      </c>
+      <c r="H58">
+        <v>76.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>45.1</v>
+      </c>
+      <c r="K58">
+        <v>4.33</v>
+      </c>
+      <c r="L58">
+        <v>40.77</v>
+      </c>
+      <c r="M58">
+        <v>2.1087808</v>
+      </c>
+      <c r="N58">
+        <v>38.66121920000001</v>
+      </c>
+      <c r="O58">
+        <v>8.118856032</v>
+      </c>
+      <c r="P58">
+        <v>30.542363168</v>
+      </c>
+      <c r="Q58">
+        <v>34.87236316800001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.177036399407248</v>
+      </c>
+      <c r="T58">
+        <v>1.502480932946606</v>
+      </c>
+      <c r="U58">
+        <v>0.0457</v>
+      </c>
+      <c r="V58">
+        <v>0.21</v>
+      </c>
+      <c r="W58">
+        <v>0.036103</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>19.33344613152775</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.09794197230191316</v>
+      </c>
+      <c r="C59">
+        <v>35.39247498387505</v>
+      </c>
+      <c r="D59">
+        <v>-4.839525016124948</v>
+      </c>
+      <c r="E59">
+        <v>40.868</v>
+      </c>
+      <c r="F59">
+        <v>46.968</v>
+      </c>
+      <c r="G59">
+        <v>87.2</v>
+      </c>
+      <c r="H59">
+        <v>76.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>45.1</v>
+      </c>
+      <c r="K59">
+        <v>4.33</v>
+      </c>
+      <c r="L59">
+        <v>40.77</v>
+      </c>
+      <c r="M59">
+        <v>2.146437600000001</v>
+      </c>
+      <c r="N59">
+        <v>38.6235624</v>
+      </c>
+      <c r="O59">
+        <v>8.110948104</v>
+      </c>
+      <c r="P59">
+        <v>30.512614296</v>
+      </c>
+      <c r="Q59">
+        <v>34.842614296</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1799145634928213</v>
+      </c>
+      <c r="T59">
+        <v>1.533763479938631</v>
+      </c>
+      <c r="U59">
+        <v>0.0457</v>
+      </c>
+      <c r="V59">
+        <v>0.21</v>
+      </c>
+      <c r="W59">
+        <v>0.036103</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>18.99426286606235</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.09777024886463721</v>
+      </c>
+      <c r="C60">
+        <v>34.56781836234371</v>
+      </c>
+      <c r="D60">
+        <v>-4.840181637656296</v>
+      </c>
+      <c r="E60">
+        <v>41.69199999999999</v>
+      </c>
+      <c r="F60">
+        <v>47.79199999999999</v>
+      </c>
+      <c r="G60">
+        <v>87.2</v>
+      </c>
+      <c r="H60">
+        <v>76.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>45.1</v>
+      </c>
+      <c r="K60">
+        <v>4.33</v>
+      </c>
+      <c r="L60">
+        <v>40.77</v>
+      </c>
+      <c r="M60">
+        <v>2.1840944</v>
+      </c>
+      <c r="N60">
+        <v>38.5859056</v>
+      </c>
+      <c r="O60">
+        <v>8.103040175999999</v>
+      </c>
+      <c r="P60">
+        <v>30.482865424</v>
+      </c>
+      <c r="Q60">
+        <v>34.812865424</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.182929783011041</v>
+      </c>
+      <c r="T60">
+        <v>1.566535672025515</v>
+      </c>
+      <c r="U60">
+        <v>0.0457</v>
+      </c>
+      <c r="V60">
+        <v>0.21</v>
+      </c>
+      <c r="W60">
+        <v>0.036103</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>18.66677557526818</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.09759852542736128</v>
+      </c>
+      <c r="C61">
+        <v>33.74316156260878</v>
+      </c>
+      <c r="D61">
+        <v>-4.840838437391223</v>
+      </c>
+      <c r="E61">
+        <v>42.51599999999999</v>
+      </c>
+      <c r="F61">
+        <v>48.61599999999999</v>
+      </c>
+      <c r="G61">
+        <v>87.2</v>
+      </c>
+      <c r="H61">
+        <v>76.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>45.1</v>
+      </c>
+      <c r="K61">
+        <v>4.33</v>
+      </c>
+      <c r="L61">
+        <v>40.77</v>
+      </c>
+      <c r="M61">
+        <v>2.2217512</v>
+      </c>
+      <c r="N61">
+        <v>38.5482488</v>
+      </c>
+      <c r="O61">
+        <v>8.095132247999999</v>
+      </c>
+      <c r="P61">
+        <v>30.453116552</v>
+      </c>
+      <c r="Q61">
+        <v>34.783116552</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1860920864081982</v>
+      </c>
+      <c r="T61">
+        <v>1.600906507628832</v>
+      </c>
+      <c r="U61">
+        <v>0.0457</v>
+      </c>
+      <c r="V61">
+        <v>0.21</v>
+      </c>
+      <c r="W61">
+        <v>0.036103</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>18.35038954856872</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.09742680199008533</v>
+      </c>
+      <c r="C62">
+        <v>32.91850458459772</v>
+      </c>
+      <c r="D62">
+        <v>-4.841495415402287</v>
+      </c>
+      <c r="E62">
+        <v>43.33999999999999</v>
+      </c>
+      <c r="F62">
+        <v>49.43999999999999</v>
+      </c>
+      <c r="G62">
+        <v>87.2</v>
+      </c>
+      <c r="H62">
+        <v>76.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>45.1</v>
+      </c>
+      <c r="K62">
+        <v>4.33</v>
+      </c>
+      <c r="L62">
+        <v>40.77</v>
+      </c>
+      <c r="M62">
+        <v>2.259408</v>
+      </c>
+      <c r="N62">
+        <v>38.510592</v>
+      </c>
+      <c r="O62">
+        <v>8.087224319999999</v>
+      </c>
+      <c r="P62">
+        <v>30.42336768000001</v>
+      </c>
+      <c r="Q62">
+        <v>34.75336768</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1894125049752133</v>
+      </c>
+      <c r="T62">
+        <v>1.636995885012315</v>
+      </c>
+      <c r="U62">
+        <v>0.0457</v>
+      </c>
+      <c r="V62">
+        <v>0.21</v>
+      </c>
+      <c r="W62">
+        <v>0.036103</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>18.04454972275924</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.09725507855280938</v>
+      </c>
+      <c r="C63">
+        <v>32.09384742823792</v>
+      </c>
+      <c r="D63">
+        <v>-4.842152571762079</v>
+      </c>
+      <c r="E63">
+        <v>44.16399999999999</v>
+      </c>
+      <c r="F63">
+        <v>50.264</v>
+      </c>
+      <c r="G63">
+        <v>87.2</v>
+      </c>
+      <c r="H63">
+        <v>76.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>45.1</v>
+      </c>
+      <c r="K63">
+        <v>4.33</v>
+      </c>
+      <c r="L63">
+        <v>40.77</v>
+      </c>
+      <c r="M63">
+        <v>2.2970648</v>
+      </c>
+      <c r="N63">
+        <v>38.4729352</v>
+      </c>
+      <c r="O63">
+        <v>8.079316391999999</v>
+      </c>
+      <c r="P63">
+        <v>30.393618808</v>
+      </c>
+      <c r="Q63">
+        <v>34.723618808</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1929032014174599</v>
+      </c>
+      <c r="T63">
+        <v>1.674935999697515</v>
+      </c>
+      <c r="U63">
+        <v>0.0457</v>
+      </c>
+      <c r="V63">
+        <v>0.21</v>
+      </c>
+      <c r="W63">
+        <v>0.036103</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>17.7487374322222</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.09708335511553344</v>
+      </c>
+      <c r="C64">
+        <v>31.26919009345677</v>
+      </c>
+      <c r="D64">
+        <v>-4.842809906543235</v>
+      </c>
+      <c r="E64">
+        <v>44.98799999999999</v>
+      </c>
+      <c r="F64">
+        <v>51.08799999999999</v>
+      </c>
+      <c r="G64">
+        <v>87.2</v>
+      </c>
+      <c r="H64">
+        <v>76.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>45.1</v>
+      </c>
+      <c r="K64">
+        <v>4.33</v>
+      </c>
+      <c r="L64">
+        <v>40.77</v>
+      </c>
+      <c r="M64">
+        <v>2.3347216</v>
+      </c>
+      <c r="N64">
+        <v>38.4352784</v>
+      </c>
+      <c r="O64">
+        <v>8.071408463999999</v>
+      </c>
+      <c r="P64">
+        <v>30.363869936</v>
+      </c>
+      <c r="Q64">
+        <v>34.693869936</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.196577618725088</v>
+      </c>
+      <c r="T64">
+        <v>1.714872962524042</v>
+      </c>
+      <c r="U64">
+        <v>0.0457</v>
+      </c>
+      <c r="V64">
+        <v>0.21</v>
+      </c>
+      <c r="W64">
+        <v>0.036103</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>17.46246747363797</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.09691163167825748</v>
+      </c>
+      <c r="C65">
+        <v>30.44453258018159</v>
+      </c>
+      <c r="D65">
+        <v>-4.843467419818428</v>
+      </c>
+      <c r="E65">
+        <v>45.81199999999999</v>
+      </c>
+      <c r="F65">
+        <v>51.91199999999999</v>
+      </c>
+      <c r="G65">
+        <v>87.2</v>
+      </c>
+      <c r="H65">
+        <v>76.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>45.1</v>
+      </c>
+      <c r="K65">
+        <v>4.33</v>
+      </c>
+      <c r="L65">
+        <v>40.77</v>
+      </c>
+      <c r="M65">
+        <v>2.3723784</v>
+      </c>
+      <c r="N65">
+        <v>38.3976216</v>
+      </c>
+      <c r="O65">
+        <v>8.063500535999999</v>
+      </c>
+      <c r="P65">
+        <v>30.334121064</v>
+      </c>
+      <c r="Q65">
+        <v>34.664121064</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2004506531844797</v>
+      </c>
+      <c r="T65">
+        <v>1.756968680097948</v>
+      </c>
+      <c r="U65">
+        <v>0.0457</v>
+      </c>
+      <c r="V65">
+        <v>0.21</v>
+      </c>
+      <c r="W65">
+        <v>0.036103</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>17.18528545024689</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.09673990824098153</v>
+      </c>
+      <c r="C66">
+        <v>29.61987488833963</v>
+      </c>
+      <c r="D66">
+        <v>-4.84412511166037</v>
+      </c>
+      <c r="E66">
+        <v>46.636</v>
+      </c>
+      <c r="F66">
+        <v>52.736</v>
+      </c>
+      <c r="G66">
+        <v>87.2</v>
+      </c>
+      <c r="H66">
+        <v>76.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>45.1</v>
+      </c>
+      <c r="K66">
+        <v>4.33</v>
+      </c>
+      <c r="L66">
+        <v>40.77</v>
+      </c>
+      <c r="M66">
+        <v>2.4100352</v>
+      </c>
+      <c r="N66">
+        <v>38.3599648</v>
+      </c>
+      <c r="O66">
+        <v>8.055592608</v>
+      </c>
+      <c r="P66">
+        <v>30.304372192</v>
+      </c>
+      <c r="Q66">
+        <v>34.634372192</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2045388562249487</v>
+      </c>
+      <c r="T66">
+        <v>1.801403048648182</v>
+      </c>
+      <c r="U66">
+        <v>0.0457</v>
+      </c>
+      <c r="V66">
+        <v>0.21</v>
+      </c>
+      <c r="W66">
+        <v>0.036103</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>16.91676536508678</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.09656818480370558</v>
+      </c>
+      <c r="C67">
+        <v>28.7952170178582</v>
+      </c>
+      <c r="D67">
+        <v>-4.844782982141813</v>
+      </c>
+      <c r="E67">
+        <v>47.45999999999999</v>
+      </c>
+      <c r="F67">
+        <v>53.56</v>
+      </c>
+      <c r="G67">
+        <v>87.2</v>
+      </c>
+      <c r="H67">
+        <v>76.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>45.1</v>
+      </c>
+      <c r="K67">
+        <v>4.33</v>
+      </c>
+      <c r="L67">
+        <v>40.77</v>
+      </c>
+      <c r="M67">
+        <v>2.447692</v>
+      </c>
+      <c r="N67">
+        <v>38.32230800000001</v>
+      </c>
+      <c r="O67">
+        <v>8.04768468</v>
+      </c>
+      <c r="P67">
+        <v>30.27462332000001</v>
+      </c>
+      <c r="Q67">
+        <v>34.60462332000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2088606708677302</v>
+      </c>
+      <c r="T67">
+        <v>1.848376523972716</v>
+      </c>
+      <c r="U67">
+        <v>0.0457</v>
+      </c>
+      <c r="V67">
+        <v>0.21</v>
+      </c>
+      <c r="W67">
+        <v>0.036103</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>16.65650743639314</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.09639646136642963</v>
+      </c>
+      <c r="C68">
+        <v>27.97055896866445</v>
+      </c>
+      <c r="D68">
+        <v>-4.845441031335551</v>
+      </c>
+      <c r="E68">
+        <v>48.284</v>
+      </c>
+      <c r="F68">
+        <v>54.384</v>
+      </c>
+      <c r="G68">
+        <v>87.2</v>
+      </c>
+      <c r="H68">
+        <v>76.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>45.1</v>
+      </c>
+      <c r="K68">
+        <v>4.33</v>
+      </c>
+      <c r="L68">
+        <v>40.77</v>
+      </c>
+      <c r="M68">
+        <v>2.4853488</v>
+      </c>
+      <c r="N68">
+        <v>38.28465120000001</v>
+      </c>
+      <c r="O68">
+        <v>8.039776752</v>
+      </c>
+      <c r="P68">
+        <v>30.244874448</v>
+      </c>
+      <c r="Q68">
+        <v>34.574874448</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2134367099012636</v>
+      </c>
+      <c r="T68">
+        <v>1.898113144904574</v>
+      </c>
+      <c r="U68">
+        <v>0.0457</v>
+      </c>
+      <c r="V68">
+        <v>0.21</v>
+      </c>
+      <c r="W68">
+        <v>0.036103</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>16.40413611159931</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.09622473792915368</v>
+      </c>
+      <c r="C69">
+        <v>27.14590074068559</v>
+      </c>
+      <c r="D69">
+        <v>-4.846099259314414</v>
+      </c>
+      <c r="E69">
+        <v>49.108</v>
+      </c>
+      <c r="F69">
+        <v>55.208</v>
+      </c>
+      <c r="G69">
+        <v>87.2</v>
+      </c>
+      <c r="H69">
+        <v>76.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>45.1</v>
+      </c>
+      <c r="K69">
+        <v>4.33</v>
+      </c>
+      <c r="L69">
+        <v>40.77</v>
+      </c>
+      <c r="M69">
+        <v>2.5230056</v>
+      </c>
+      <c r="N69">
+        <v>38.24699440000001</v>
+      </c>
+      <c r="O69">
+        <v>8.031868824</v>
+      </c>
+      <c r="P69">
+        <v>30.21512557600001</v>
+      </c>
+      <c r="Q69">
+        <v>34.545125576</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2182900846337991</v>
+      </c>
+      <c r="T69">
+        <v>1.95086410649897</v>
+      </c>
+      <c r="U69">
+        <v>0.0457</v>
+      </c>
+      <c r="V69">
+        <v>0.21</v>
+      </c>
+      <c r="W69">
+        <v>0.036103</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>16.15929825918737</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.09605301449187774</v>
+      </c>
+      <c r="C70">
+        <v>26.32124233384873</v>
+      </c>
+      <c r="D70">
+        <v>-4.846757666151274</v>
+      </c>
+      <c r="E70">
+        <v>49.932</v>
+      </c>
+      <c r="F70">
+        <v>56.032</v>
+      </c>
+      <c r="G70">
+        <v>87.2</v>
+      </c>
+      <c r="H70">
+        <v>76.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>45.1</v>
+      </c>
+      <c r="K70">
+        <v>4.33</v>
+      </c>
+      <c r="L70">
+        <v>40.77</v>
+      </c>
+      <c r="M70">
+        <v>2.5606624</v>
+      </c>
+      <c r="N70">
+        <v>38.2093376</v>
+      </c>
+      <c r="O70">
+        <v>8.023960896</v>
+      </c>
+      <c r="P70">
+        <v>30.18537670400001</v>
+      </c>
+      <c r="Q70">
+        <v>34.515376704</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2234467952871179</v>
+      </c>
+      <c r="T70">
+        <v>2.006912003193016</v>
+      </c>
+      <c r="U70">
+        <v>0.0457</v>
+      </c>
+      <c r="V70">
+        <v>0.21</v>
+      </c>
+      <c r="W70">
+        <v>0.036103</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>15.92166152008168</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.09588129105460179</v>
+      </c>
+      <c r="C71">
+        <v>25.49658374808096</v>
+      </c>
+      <c r="D71">
+        <v>-4.84741625191904</v>
+      </c>
+      <c r="E71">
+        <v>50.756</v>
+      </c>
+      <c r="F71">
+        <v>56.856</v>
+      </c>
+      <c r="G71">
+        <v>87.2</v>
+      </c>
+      <c r="H71">
+        <v>76.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>45.1</v>
+      </c>
+      <c r="K71">
+        <v>4.33</v>
+      </c>
+      <c r="L71">
+        <v>40.77</v>
+      </c>
+      <c r="M71">
+        <v>2.5983192</v>
+      </c>
+      <c r="N71">
+        <v>38.1716808</v>
+      </c>
+      <c r="O71">
+        <v>8.016052968</v>
+      </c>
+      <c r="P71">
+        <v>30.155627832</v>
+      </c>
+      <c r="Q71">
+        <v>34.48562783200001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2289361969503284</v>
+      </c>
+      <c r="T71">
+        <v>2.066575893222161</v>
+      </c>
+      <c r="U71">
+        <v>0.0457</v>
+      </c>
+      <c r="V71">
+        <v>0.21</v>
+      </c>
+      <c r="W71">
+        <v>0.036103</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>15.69091280239934</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.09570956761732584</v>
+      </c>
+      <c r="C72">
+        <v>24.67192498330935</v>
+      </c>
+      <c r="D72">
+        <v>-4.848075016690664</v>
+      </c>
+      <c r="E72">
+        <v>51.58</v>
+      </c>
+      <c r="F72">
+        <v>57.68</v>
+      </c>
+      <c r="G72">
+        <v>87.2</v>
+      </c>
+      <c r="H72">
+        <v>76.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>45.1</v>
+      </c>
+      <c r="K72">
+        <v>4.33</v>
+      </c>
+      <c r="L72">
+        <v>40.77</v>
+      </c>
+      <c r="M72">
+        <v>2.635976</v>
+      </c>
+      <c r="N72">
+        <v>38.134024</v>
+      </c>
+      <c r="O72">
+        <v>8.008145039999999</v>
+      </c>
+      <c r="P72">
+        <v>30.12587896</v>
+      </c>
+      <c r="Q72">
+        <v>34.45587896000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2347915587244195</v>
+      </c>
+      <c r="T72">
+        <v>2.130217375919916</v>
+      </c>
+      <c r="U72">
+        <v>0.0457</v>
+      </c>
+      <c r="V72">
+        <v>0.21</v>
+      </c>
+      <c r="W72">
+        <v>0.036103</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>15.4667569052222</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.0955378441800499</v>
+      </c>
+      <c r="C73">
+        <v>23.84726603946088</v>
+      </c>
+      <c r="D73">
+        <v>-4.848733960539134</v>
+      </c>
+      <c r="E73">
+        <v>52.40399999999999</v>
+      </c>
+      <c r="F73">
+        <v>58.50399999999999</v>
+      </c>
+      <c r="G73">
+        <v>87.2</v>
+      </c>
+      <c r="H73">
+        <v>76.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>45.1</v>
+      </c>
+      <c r="K73">
+        <v>4.33</v>
+      </c>
+      <c r="L73">
+        <v>40.77</v>
+      </c>
+      <c r="M73">
+        <v>2.6736328</v>
+      </c>
+      <c r="N73">
+        <v>38.0963672</v>
+      </c>
+      <c r="O73">
+        <v>8.000237111999999</v>
+      </c>
+      <c r="P73">
+        <v>30.096130088</v>
+      </c>
+      <c r="Q73">
+        <v>34.426130088</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2410507385518962</v>
+      </c>
+      <c r="T73">
+        <v>2.198247926389929</v>
+      </c>
+      <c r="U73">
+        <v>0.0457</v>
+      </c>
+      <c r="V73">
+        <v>0.21</v>
+      </c>
+      <c r="W73">
+        <v>0.036103</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>15.24891525866978</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.09536612074277394</v>
+      </c>
+      <c r="C74">
+        <v>23.02260691646254</v>
+      </c>
+      <c r="D74">
+        <v>-4.849393083537481</v>
+      </c>
+      <c r="E74">
+        <v>53.22799999999999</v>
+      </c>
+      <c r="F74">
+        <v>59.32799999999999</v>
+      </c>
+      <c r="G74">
+        <v>87.2</v>
+      </c>
+      <c r="H74">
+        <v>76.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>45.1</v>
+      </c>
+      <c r="K74">
+        <v>4.33</v>
+      </c>
+      <c r="L74">
+        <v>40.77</v>
+      </c>
+      <c r="M74">
+        <v>2.7112896</v>
+      </c>
+      <c r="N74">
+        <v>38.0587104</v>
+      </c>
+      <c r="O74">
+        <v>7.992329183999999</v>
+      </c>
+      <c r="P74">
+        <v>30.066381216</v>
+      </c>
+      <c r="Q74">
+        <v>34.396381216</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.247757002652764</v>
+      </c>
+      <c r="T74">
+        <v>2.271137801893516</v>
+      </c>
+      <c r="U74">
+        <v>0.0457</v>
+      </c>
+      <c r="V74">
+        <v>0.21</v>
+      </c>
+      <c r="W74">
+        <v>0.036103</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>15.03712476896603</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.09519439730549799</v>
+      </c>
+      <c r="C75">
+        <v>22.19794761424124</v>
+      </c>
+      <c r="D75">
+        <v>-4.850052385758773</v>
+      </c>
+      <c r="E75">
+        <v>54.05199999999999</v>
+      </c>
+      <c r="F75">
+        <v>60.15199999999999</v>
+      </c>
+      <c r="G75">
+        <v>87.2</v>
+      </c>
+      <c r="H75">
+        <v>76.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>45.1</v>
+      </c>
+      <c r="K75">
+        <v>4.33</v>
+      </c>
+      <c r="L75">
+        <v>40.77</v>
+      </c>
+      <c r="M75">
+        <v>2.7489464</v>
+      </c>
+      <c r="N75">
+        <v>38.0210536</v>
+      </c>
+      <c r="O75">
+        <v>7.984421255999999</v>
+      </c>
+      <c r="P75">
+        <v>30.036632344</v>
+      </c>
+      <c r="Q75">
+        <v>34.366632344</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2549600270574</v>
+      </c>
+      <c r="T75">
+        <v>2.349426927434405</v>
+      </c>
+      <c r="U75">
+        <v>0.0457</v>
+      </c>
+      <c r="V75">
+        <v>0.21</v>
+      </c>
+      <c r="W75">
+        <v>0.036103</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>14.83113675843225</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.09502267386822202</v>
+      </c>
+      <c r="C76">
+        <v>21.37328813272389</v>
+      </c>
+      <c r="D76">
+        <v>-4.850711867276121</v>
+      </c>
+      <c r="E76">
+        <v>54.87599999999999</v>
+      </c>
+      <c r="F76">
+        <v>60.97599999999999</v>
+      </c>
+      <c r="G76">
+        <v>87.2</v>
+      </c>
+      <c r="H76">
+        <v>76.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>45.1</v>
+      </c>
+      <c r="K76">
+        <v>4.33</v>
+      </c>
+      <c r="L76">
+        <v>40.77</v>
+      </c>
+      <c r="M76">
+        <v>2.7866032</v>
+      </c>
+      <c r="N76">
+        <v>37.9833968</v>
+      </c>
+      <c r="O76">
+        <v>7.976513327999999</v>
+      </c>
+      <c r="P76">
+        <v>30.006883472</v>
+      </c>
+      <c r="Q76">
+        <v>34.336883472</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2627171302623924</v>
+      </c>
+      <c r="T76">
+        <v>2.433738293401516</v>
+      </c>
+      <c r="U76">
+        <v>0.0457</v>
+      </c>
+      <c r="V76">
+        <v>0.21</v>
+      </c>
+      <c r="W76">
+        <v>0.036103</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>14.63071599142641</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.09485095043094607</v>
+      </c>
+      <c r="C77">
+        <v>20.54862847183733</v>
+      </c>
+      <c r="D77">
+        <v>-4.851371528162671</v>
+      </c>
+      <c r="E77">
+        <v>55.7</v>
+      </c>
+      <c r="F77">
+        <v>61.8</v>
+      </c>
+      <c r="G77">
+        <v>87.2</v>
+      </c>
+      <c r="H77">
+        <v>76.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>45.1</v>
+      </c>
+      <c r="K77">
+        <v>4.33</v>
+      </c>
+      <c r="L77">
+        <v>40.77</v>
+      </c>
+      <c r="M77">
+        <v>2.82426</v>
+      </c>
+      <c r="N77">
+        <v>37.94574</v>
+      </c>
+      <c r="O77">
+        <v>7.968605399999999</v>
+      </c>
+      <c r="P77">
+        <v>29.9771346</v>
+      </c>
+      <c r="Q77">
+        <v>34.3071346</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2710948017237843</v>
+      </c>
+      <c r="T77">
+        <v>2.524794568645996</v>
+      </c>
+      <c r="U77">
+        <v>0.0457</v>
+      </c>
+      <c r="V77">
+        <v>0.21</v>
+      </c>
+      <c r="W77">
+        <v>0.036103</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>14.43563977820739</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.09467922699367015</v>
+      </c>
+      <c r="C78">
+        <v>19.7239686315084</v>
+      </c>
+      <c r="D78">
+        <v>-4.852031368491615</v>
+      </c>
+      <c r="E78">
+        <v>56.52399999999999</v>
+      </c>
+      <c r="F78">
+        <v>62.624</v>
+      </c>
+      <c r="G78">
+        <v>87.2</v>
+      </c>
+      <c r="H78">
+        <v>76.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>45.1</v>
+      </c>
+      <c r="K78">
+        <v>4.33</v>
+      </c>
+      <c r="L78">
+        <v>40.77</v>
+      </c>
+      <c r="M78">
+        <v>2.8619168</v>
+      </c>
+      <c r="N78">
+        <v>37.9080832</v>
+      </c>
+      <c r="O78">
+        <v>7.960697471999999</v>
+      </c>
+      <c r="P78">
+        <v>29.947385728</v>
+      </c>
+      <c r="Q78">
+        <v>34.277385728</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2801706124736256</v>
+      </c>
+      <c r="T78">
+        <v>2.623438866827517</v>
+      </c>
+      <c r="U78">
+        <v>0.0457</v>
+      </c>
+      <c r="V78">
+        <v>0.21</v>
+      </c>
+      <c r="W78">
+        <v>0.036103</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>14.24569714954677</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.0945075035563942</v>
+      </c>
+      <c r="C79">
+        <v>18.89930861166383</v>
+      </c>
+      <c r="D79">
+        <v>-4.852691388336178</v>
+      </c>
+      <c r="E79">
+        <v>57.34799999999999</v>
+      </c>
+      <c r="F79">
+        <v>63.44799999999999</v>
+      </c>
+      <c r="G79">
+        <v>87.2</v>
+      </c>
+      <c r="H79">
+        <v>76.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>45.1</v>
+      </c>
+      <c r="K79">
+        <v>4.33</v>
+      </c>
+      <c r="L79">
+        <v>40.77</v>
+      </c>
+      <c r="M79">
+        <v>2.8995736</v>
+      </c>
+      <c r="N79">
+        <v>37.8704264</v>
+      </c>
+      <c r="O79">
+        <v>7.952789543999999</v>
+      </c>
+      <c r="P79">
+        <v>29.917636856</v>
+      </c>
+      <c r="Q79">
+        <v>34.247636856</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2900356241582356</v>
+      </c>
+      <c r="T79">
+        <v>2.730660930068299</v>
+      </c>
+      <c r="U79">
+        <v>0.0457</v>
+      </c>
+      <c r="V79">
+        <v>0.21</v>
+      </c>
+      <c r="W79">
+        <v>0.036103</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>14.06068809565655</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.09433578011911825</v>
+      </c>
+      <c r="C80">
+        <v>18.07464841223037</v>
+      </c>
+      <c r="D80">
+        <v>-4.853351587769631</v>
+      </c>
+      <c r="E80">
+        <v>58.17199999999999</v>
+      </c>
+      <c r="F80">
+        <v>64.27199999999999</v>
+      </c>
+      <c r="G80">
+        <v>87.2</v>
+      </c>
+      <c r="H80">
+        <v>76.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>45.1</v>
+      </c>
+      <c r="K80">
+        <v>4.33</v>
+      </c>
+      <c r="L80">
+        <v>40.77</v>
+      </c>
+      <c r="M80">
+        <v>2.9372304</v>
+      </c>
+      <c r="N80">
+        <v>37.83276960000001</v>
+      </c>
+      <c r="O80">
+        <v>7.944881616</v>
+      </c>
+      <c r="P80">
+        <v>29.88788798400001</v>
+      </c>
+      <c r="Q80">
+        <v>34.21788798400001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3007974550869011</v>
+      </c>
+      <c r="T80">
+        <v>2.847630453603699</v>
+      </c>
+      <c r="U80">
+        <v>0.0457</v>
+      </c>
+      <c r="V80">
+        <v>0.21</v>
+      </c>
+      <c r="W80">
+        <v>0.036103</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>13.88042286366095</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.09416405668184229</v>
+      </c>
+      <c r="C81">
+        <v>17.24998803313473</v>
+      </c>
+      <c r="D81">
+        <v>-4.854011966865282</v>
+      </c>
+      <c r="E81">
+        <v>58.99599999999999</v>
+      </c>
+      <c r="F81">
+        <v>65.09599999999999</v>
+      </c>
+      <c r="G81">
+        <v>87.2</v>
+      </c>
+      <c r="H81">
+        <v>76.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>45.1</v>
+      </c>
+      <c r="K81">
+        <v>4.33</v>
+      </c>
+      <c r="L81">
+        <v>40.77</v>
+      </c>
+      <c r="M81">
+        <v>2.9748872</v>
+      </c>
+      <c r="N81">
+        <v>37.79511280000001</v>
+      </c>
+      <c r="O81">
+        <v>7.936973688</v>
+      </c>
+      <c r="P81">
+        <v>29.858139112</v>
+      </c>
+      <c r="Q81">
+        <v>34.188139112</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3125842222944871</v>
+      </c>
+      <c r="T81">
+        <v>2.975739931761517</v>
+      </c>
+      <c r="U81">
+        <v>0.0457</v>
+      </c>
+      <c r="V81">
+        <v>0.21</v>
+      </c>
+      <c r="W81">
+        <v>0.036103</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>13.70472130842474</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.09399233324456634</v>
+      </c>
+      <c r="C82">
+        <v>16.42532747430353</v>
+      </c>
+      <c r="D82">
+        <v>-4.854672525696477</v>
+      </c>
+      <c r="E82">
+        <v>59.82</v>
+      </c>
+      <c r="F82">
+        <v>65.92</v>
+      </c>
+      <c r="G82">
+        <v>87.2</v>
+      </c>
+      <c r="H82">
+        <v>76.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>45.1</v>
+      </c>
+      <c r="K82">
+        <v>4.33</v>
+      </c>
+      <c r="L82">
+        <v>40.77</v>
+      </c>
+      <c r="M82">
+        <v>3.012544000000001</v>
+      </c>
+      <c r="N82">
+        <v>37.757456</v>
+      </c>
+      <c r="O82">
+        <v>7.929065759999999</v>
+      </c>
+      <c r="P82">
+        <v>29.82839024</v>
+      </c>
+      <c r="Q82">
+        <v>34.15839024</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3255496662228318</v>
+      </c>
+      <c r="T82">
+        <v>3.116660357735118</v>
+      </c>
+      <c r="U82">
+        <v>0.0457</v>
+      </c>
+      <c r="V82">
+        <v>0.21</v>
+      </c>
+      <c r="W82">
+        <v>0.036103</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>13.53341229206943</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.0938206098072904</v>
+      </c>
+      <c r="C83">
+        <v>15.6006667356634</v>
+      </c>
+      <c r="D83">
+        <v>-4.855333264336606</v>
+      </c>
+      <c r="E83">
+        <v>60.644</v>
+      </c>
+      <c r="F83">
+        <v>66.744</v>
+      </c>
+      <c r="G83">
+        <v>87.2</v>
+      </c>
+      <c r="H83">
+        <v>76.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>45.1</v>
+      </c>
+      <c r="K83">
+        <v>4.33</v>
+      </c>
+      <c r="L83">
+        <v>40.77</v>
+      </c>
+      <c r="M83">
+        <v>3.0502008</v>
+      </c>
+      <c r="N83">
+        <v>37.7197992</v>
+      </c>
+      <c r="O83">
+        <v>7.921157832</v>
+      </c>
+      <c r="P83">
+        <v>29.79864136800001</v>
+      </c>
+      <c r="Q83">
+        <v>34.128641368</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3398798937225812</v>
+      </c>
+      <c r="T83">
+        <v>3.272414512758571</v>
+      </c>
+      <c r="U83">
+        <v>0.0457</v>
+      </c>
+      <c r="V83">
+        <v>0.21</v>
+      </c>
+      <c r="W83">
+        <v>0.036103</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>13.3663331279698</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.09364888637001445</v>
+      </c>
+      <c r="C84">
+        <v>14.77600581714091</v>
+      </c>
+      <c r="D84">
+        <v>-4.855994182859096</v>
+      </c>
+      <c r="E84">
+        <v>61.468</v>
+      </c>
+      <c r="F84">
+        <v>67.568</v>
+      </c>
+      <c r="G84">
+        <v>87.2</v>
+      </c>
+      <c r="H84">
+        <v>76.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>45.1</v>
+      </c>
+      <c r="K84">
+        <v>4.33</v>
+      </c>
+      <c r="L84">
+        <v>40.77</v>
+      </c>
+      <c r="M84">
+        <v>3.0878576</v>
+      </c>
+      <c r="N84">
+        <v>37.6821424</v>
+      </c>
+      <c r="O84">
+        <v>7.913249904</v>
+      </c>
+      <c r="P84">
+        <v>29.768892496</v>
+      </c>
+      <c r="Q84">
+        <v>34.098892496</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3558023687223026</v>
+      </c>
+      <c r="T84">
+        <v>3.445474685006852</v>
+      </c>
+      <c r="U84">
+        <v>0.0457</v>
+      </c>
+      <c r="V84">
+        <v>0.21</v>
+      </c>
+      <c r="W84">
+        <v>0.036103</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>13.20332906543359</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.0934771629327385</v>
+      </c>
+      <c r="C85">
+        <v>13.9513447186626</v>
+      </c>
+      <c r="D85">
+        <v>-4.856655281337414</v>
+      </c>
+      <c r="E85">
+        <v>62.29199999999999</v>
+      </c>
+      <c r="F85">
+        <v>68.392</v>
+      </c>
+      <c r="G85">
+        <v>87.2</v>
+      </c>
+      <c r="H85">
+        <v>76.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>45.1</v>
+      </c>
+      <c r="K85">
+        <v>4.33</v>
+      </c>
+      <c r="L85">
+        <v>40.77</v>
+      </c>
+      <c r="M85">
+        <v>3.1255144</v>
+      </c>
+      <c r="N85">
+        <v>37.6444856</v>
+      </c>
+      <c r="O85">
+        <v>7.905341975999999</v>
+      </c>
+      <c r="P85">
+        <v>29.739143624</v>
+      </c>
+      <c r="Q85">
+        <v>34.06914362400001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3735980760749325</v>
+      </c>
+      <c r="T85">
+        <v>3.638894877519637</v>
+      </c>
+      <c r="U85">
+        <v>0.0457</v>
+      </c>
+      <c r="V85">
+        <v>0.21</v>
+      </c>
+      <c r="W85">
+        <v>0.036103</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>13.04425281163318</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.09436719949546256</v>
+      </c>
+      <c r="C86">
+        <v>13.13076921903723</v>
+      </c>
+      <c r="D86">
+        <v>-4.853230780962769</v>
+      </c>
+      <c r="E86">
+        <v>63.11599999999999</v>
+      </c>
+      <c r="F86">
+        <v>69.21599999999999</v>
+      </c>
+      <c r="G86">
+        <v>87.2</v>
+      </c>
+      <c r="H86">
+        <v>76.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>45.1</v>
+      </c>
+      <c r="K86">
+        <v>4.33</v>
+      </c>
+      <c r="L86">
+        <v>40.77</v>
+      </c>
+      <c r="M86">
+        <v>3.2739168</v>
+      </c>
+      <c r="N86">
+        <v>37.4960832</v>
+      </c>
+      <c r="O86">
+        <v>7.874177471999999</v>
+      </c>
+      <c r="P86">
+        <v>29.621905728</v>
+      </c>
+      <c r="Q86">
+        <v>33.951905728</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3936182468466409</v>
+      </c>
+      <c r="T86">
+        <v>3.856492594096517</v>
+      </c>
+      <c r="U86">
+        <v>0.0473</v>
+      </c>
+      <c r="V86">
+        <v>0.21</v>
+      </c>
+      <c r="W86">
+        <v>0.037367</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>12.45297375913768</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.09420811605818662</v>
+      </c>
+      <c r="C87">
+        <v>12.30615748486876</v>
+      </c>
+      <c r="D87">
+        <v>-4.853842515131254</v>
+      </c>
+      <c r="E87">
+        <v>63.93999999999999</v>
+      </c>
+      <c r="F87">
+        <v>70.03999999999999</v>
+      </c>
+      <c r="G87">
+        <v>87.2</v>
+      </c>
+      <c r="H87">
+        <v>76.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>45.1</v>
+      </c>
+      <c r="K87">
+        <v>4.33</v>
+      </c>
+      <c r="L87">
+        <v>40.77</v>
+      </c>
+      <c r="M87">
+        <v>3.312892</v>
+      </c>
+      <c r="N87">
+        <v>37.45710800000001</v>
+      </c>
+      <c r="O87">
+        <v>7.86599268</v>
+      </c>
+      <c r="P87">
+        <v>29.59111532000001</v>
+      </c>
+      <c r="Q87">
+        <v>33.92111532000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.416307773721244</v>
+      </c>
+      <c r="T87">
+        <v>4.103103339550318</v>
+      </c>
+      <c r="U87">
+        <v>0.0473</v>
+      </c>
+      <c r="V87">
+        <v>0.21</v>
+      </c>
+      <c r="W87">
+        <v>0.037367</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>12.30646818550077</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.09404903262091066</v>
+      </c>
+      <c r="C88">
+        <v>11.48154559646657</v>
+      </c>
+      <c r="D88">
+        <v>-4.854454403533438</v>
+      </c>
+      <c r="E88">
+        <v>64.764</v>
+      </c>
+      <c r="F88">
+        <v>70.86399999999999</v>
+      </c>
+      <c r="G88">
+        <v>87.2</v>
+      </c>
+      <c r="H88">
+        <v>76.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>45.1</v>
+      </c>
+      <c r="K88">
+        <v>4.33</v>
+      </c>
+      <c r="L88">
+        <v>40.77</v>
+      </c>
+      <c r="M88">
+        <v>3.3518672</v>
+      </c>
+      <c r="N88">
+        <v>37.4181328</v>
+      </c>
+      <c r="O88">
+        <v>7.857807887999999</v>
+      </c>
+      <c r="P88">
+        <v>29.560324912</v>
+      </c>
+      <c r="Q88">
+        <v>33.890324912</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4422386615779332</v>
+      </c>
+      <c r="T88">
+        <v>4.384944191497518</v>
+      </c>
+      <c r="U88">
+        <v>0.0473</v>
+      </c>
+      <c r="V88">
+        <v>0.21</v>
+      </c>
+      <c r="W88">
+        <v>0.037367</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>12.1633697182275</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.0938899491836347</v>
+      </c>
+      <c r="C89">
+        <v>10.65693355377236</v>
+      </c>
+      <c r="D89">
+        <v>-4.855066446227658</v>
+      </c>
+      <c r="E89">
+        <v>65.58799999999999</v>
+      </c>
+      <c r="F89">
+        <v>71.68799999999999</v>
+      </c>
+      <c r="G89">
+        <v>87.2</v>
+      </c>
+      <c r="H89">
+        <v>76.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>45.1</v>
+      </c>
+      <c r="K89">
+        <v>4.33</v>
+      </c>
+      <c r="L89">
+        <v>40.77</v>
+      </c>
+      <c r="M89">
+        <v>3.390842399999999</v>
+      </c>
+      <c r="N89">
+        <v>37.37915760000001</v>
+      </c>
+      <c r="O89">
+        <v>7.849623096</v>
+      </c>
+      <c r="P89">
+        <v>29.529534504</v>
+      </c>
+      <c r="Q89">
+        <v>33.859534504</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.47215891679719</v>
+      </c>
+      <c r="T89">
+        <v>4.710145174513519</v>
+      </c>
+      <c r="U89">
+        <v>0.0473</v>
+      </c>
+      <c r="V89">
+        <v>0.21</v>
+      </c>
+      <c r="W89">
+        <v>0.037367</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>12.02356087089156</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.09373086574635876</v>
+      </c>
+      <c r="C90">
+        <v>9.832321356727732</v>
+      </c>
+      <c r="D90">
+        <v>-4.85567864327228</v>
+      </c>
+      <c r="E90">
+        <v>66.41199999999999</v>
+      </c>
+      <c r="F90">
+        <v>72.51199999999999</v>
+      </c>
+      <c r="G90">
+        <v>87.2</v>
+      </c>
+      <c r="H90">
+        <v>76.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>45.1</v>
+      </c>
+      <c r="K90">
+        <v>4.33</v>
+      </c>
+      <c r="L90">
+        <v>40.77</v>
+      </c>
+      <c r="M90">
+        <v>3.429817599999999</v>
+      </c>
+      <c r="N90">
+        <v>37.3401824</v>
+      </c>
+      <c r="O90">
+        <v>7.841438304</v>
+      </c>
+      <c r="P90">
+        <v>29.498744096</v>
+      </c>
+      <c r="Q90">
+        <v>33.828744096</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5070658812196563</v>
+      </c>
+      <c r="T90">
+        <v>5.08954632136552</v>
+      </c>
+      <c r="U90">
+        <v>0.0473</v>
+      </c>
+      <c r="V90">
+        <v>0.21</v>
+      </c>
+      <c r="W90">
+        <v>0.037367</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>11.8869294973587</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.09357178230908282</v>
+      </c>
+      <c r="C91">
+        <v>9.007709005274307</v>
+      </c>
+      <c r="D91">
+        <v>-4.8562909947257</v>
+      </c>
+      <c r="E91">
+        <v>67.236</v>
+      </c>
+      <c r="F91">
+        <v>73.336</v>
+      </c>
+      <c r="G91">
+        <v>87.2</v>
+      </c>
+      <c r="H91">
+        <v>76.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>45.1</v>
+      </c>
+      <c r="K91">
+        <v>4.33</v>
+      </c>
+      <c r="L91">
+        <v>40.77</v>
+      </c>
+      <c r="M91">
+        <v>3.4687928</v>
+      </c>
+      <c r="N91">
+        <v>37.3012072</v>
+      </c>
+      <c r="O91">
+        <v>7.833253511999999</v>
+      </c>
+      <c r="P91">
+        <v>29.467953688</v>
+      </c>
+      <c r="Q91">
+        <v>33.797953688</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5483195664462075</v>
+      </c>
+      <c r="T91">
+        <v>5.537929494917885</v>
+      </c>
+      <c r="U91">
+        <v>0.0473</v>
+      </c>
+      <c r="V91">
+        <v>0.21</v>
+      </c>
+      <c r="W91">
+        <v>0.037367</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>11.75336849177039</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.09341269887180687</v>
+      </c>
+      <c r="C92">
+        <v>8.183096499353667</v>
+      </c>
+      <c r="D92">
+        <v>-4.856903500646341</v>
+      </c>
+      <c r="E92">
+        <v>68.06</v>
+      </c>
+      <c r="F92">
+        <v>74.16</v>
+      </c>
+      <c r="G92">
+        <v>87.2</v>
+      </c>
+      <c r="H92">
+        <v>76.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>45.1</v>
+      </c>
+      <c r="K92">
+        <v>4.33</v>
+      </c>
+      <c r="L92">
+        <v>40.77</v>
+      </c>
+      <c r="M92">
+        <v>3.507768</v>
+      </c>
+      <c r="N92">
+        <v>37.262232</v>
+      </c>
+      <c r="O92">
+        <v>7.82506872</v>
+      </c>
+      <c r="P92">
+        <v>29.43716328</v>
+      </c>
+      <c r="Q92">
+        <v>33.76716328000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5978239887180687</v>
+      </c>
+      <c r="T92">
+        <v>6.075989303180723</v>
+      </c>
+      <c r="U92">
+        <v>0.0473</v>
+      </c>
+      <c r="V92">
+        <v>0.21</v>
+      </c>
+      <c r="W92">
+        <v>0.037367</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>11.6227755085285</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.09325361543453091</v>
+      </c>
+      <c r="C93">
+        <v>7.358483838907347</v>
+      </c>
+      <c r="D93">
+        <v>-4.85751616109266</v>
+      </c>
+      <c r="E93">
+        <v>68.884</v>
+      </c>
+      <c r="F93">
+        <v>74.98399999999999</v>
+      </c>
+      <c r="G93">
+        <v>87.2</v>
+      </c>
+      <c r="H93">
+        <v>76.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>45.1</v>
+      </c>
+      <c r="K93">
+        <v>4.33</v>
+      </c>
+      <c r="L93">
+        <v>40.77</v>
+      </c>
+      <c r="M93">
+        <v>3.5467432</v>
+      </c>
+      <c r="N93">
+        <v>37.2232568</v>
+      </c>
+      <c r="O93">
+        <v>7.816883927999999</v>
+      </c>
+      <c r="P93">
+        <v>29.406372872</v>
+      </c>
+      <c r="Q93">
+        <v>33.736372872</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6583293937170103</v>
+      </c>
+      <c r="T93">
+        <v>6.733617957724189</v>
+      </c>
+      <c r="U93">
+        <v>0.0473</v>
+      </c>
+      <c r="V93">
+        <v>0.21</v>
+      </c>
+      <c r="W93">
+        <v>0.037367</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>11.49505270074247</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.09309453199725498</v>
+      </c>
+      <c r="C94">
+        <v>6.53387102387687</v>
+      </c>
+      <c r="D94">
+        <v>-4.858128976123139</v>
+      </c>
+      <c r="E94">
+        <v>69.708</v>
+      </c>
+      <c r="F94">
+        <v>75.80799999999999</v>
+      </c>
+      <c r="G94">
+        <v>87.2</v>
+      </c>
+      <c r="H94">
+        <v>76.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>45.1</v>
+      </c>
+      <c r="K94">
+        <v>4.33</v>
+      </c>
+      <c r="L94">
+        <v>40.77</v>
+      </c>
+      <c r="M94">
+        <v>3.5857184</v>
+      </c>
+      <c r="N94">
+        <v>37.18428160000001</v>
+      </c>
+      <c r="O94">
+        <v>7.808699136</v>
+      </c>
+      <c r="P94">
+        <v>29.375582464</v>
+      </c>
+      <c r="Q94">
+        <v>33.705582464</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7339611499656875</v>
+      </c>
+      <c r="T94">
+        <v>7.555653775903528</v>
+      </c>
+      <c r="U94">
+        <v>0.0473</v>
+      </c>
+      <c r="V94">
+        <v>0.21</v>
+      </c>
+      <c r="W94">
+        <v>0.037367</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>11.3701064757344</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.09293544855997901</v>
+      </c>
+      <c r="C95">
+        <v>5.709258054203715</v>
+      </c>
+      <c r="D95">
+        <v>-4.858741945796294</v>
+      </c>
+      <c r="E95">
+        <v>70.532</v>
+      </c>
+      <c r="F95">
+        <v>76.63199999999999</v>
+      </c>
+      <c r="G95">
+        <v>87.2</v>
+      </c>
+      <c r="H95">
+        <v>76.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>45.1</v>
+      </c>
+      <c r="K95">
+        <v>4.33</v>
+      </c>
+      <c r="L95">
+        <v>40.77</v>
+      </c>
+      <c r="M95">
+        <v>3.6246936</v>
+      </c>
+      <c r="N95">
+        <v>37.1453064</v>
+      </c>
+      <c r="O95">
+        <v>7.800514343999999</v>
+      </c>
+      <c r="P95">
+        <v>29.344792056</v>
+      </c>
+      <c r="Q95">
+        <v>33.674792056</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8312019794282721</v>
+      </c>
+      <c r="T95">
+        <v>8.61255697070553</v>
+      </c>
+      <c r="U95">
+        <v>0.0473</v>
+      </c>
+      <c r="V95">
+        <v>0.21</v>
+      </c>
+      <c r="W95">
+        <v>0.037367</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>11.2478472663179</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.09277636512270307</v>
+      </c>
+      <c r="C96">
+        <v>4.884644929829335</v>
+      </c>
+      <c r="D96">
+        <v>-4.859355070170666</v>
+      </c>
+      <c r="E96">
+        <v>71.35600000000001</v>
+      </c>
+      <c r="F96">
+        <v>77.456</v>
+      </c>
+      <c r="G96">
+        <v>87.2</v>
+      </c>
+      <c r="H96">
+        <v>76.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>45.1</v>
+      </c>
+      <c r="K96">
+        <v>4.33</v>
+      </c>
+      <c r="L96">
+        <v>40.77</v>
+      </c>
+      <c r="M96">
+        <v>3.6636688</v>
+      </c>
+      <c r="N96">
+        <v>37.1063312</v>
+      </c>
+      <c r="O96">
+        <v>7.792329551999998</v>
+      </c>
+      <c r="P96">
+        <v>29.314001648</v>
+      </c>
+      <c r="Q96">
+        <v>33.644001648</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9608564187117186</v>
+      </c>
+      <c r="T96">
+        <v>10.02176123044154</v>
+      </c>
+      <c r="U96">
+        <v>0.0473</v>
+      </c>
+      <c r="V96">
+        <v>0.21</v>
+      </c>
+      <c r="W96">
+        <v>0.037367</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>11.12818931667622</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.09261728168542713</v>
+      </c>
+      <c r="C97">
+        <v>4.06003165069518</v>
+      </c>
+      <c r="D97">
+        <v>-4.859968349304826</v>
+      </c>
+      <c r="E97">
+        <v>72.18000000000001</v>
+      </c>
+      <c r="F97">
+        <v>78.28</v>
+      </c>
+      <c r="G97">
+        <v>87.2</v>
+      </c>
+      <c r="H97">
+        <v>76.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>45.1</v>
+      </c>
+      <c r="K97">
+        <v>4.33</v>
+      </c>
+      <c r="L97">
+        <v>40.77</v>
+      </c>
+      <c r="M97">
+        <v>3.702644</v>
+      </c>
+      <c r="N97">
+        <v>37.067356</v>
+      </c>
+      <c r="O97">
+        <v>7.784144759999999</v>
+      </c>
+      <c r="P97">
+        <v>29.28321124</v>
+      </c>
+      <c r="Q97">
+        <v>33.61321124000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.142372633708544</v>
+      </c>
+      <c r="T97">
+        <v>11.99464719407194</v>
+      </c>
+      <c r="U97">
+        <v>0.0473</v>
+      </c>
+      <c r="V97">
+        <v>0.21</v>
+      </c>
+      <c r="W97">
+        <v>0.037367</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>11.01105048176384</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.09245819824815119</v>
+      </c>
+      <c r="C98">
+        <v>3.23541821674263</v>
+      </c>
+      <c r="D98">
+        <v>-4.860581783257381</v>
+      </c>
+      <c r="E98">
+        <v>73.00399999999999</v>
+      </c>
+      <c r="F98">
+        <v>79.10399999999998</v>
+      </c>
+      <c r="G98">
+        <v>87.2</v>
+      </c>
+      <c r="H98">
+        <v>76.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>45.1</v>
+      </c>
+      <c r="K98">
+        <v>4.33</v>
+      </c>
+      <c r="L98">
+        <v>40.77</v>
+      </c>
+      <c r="M98">
+        <v>3.741619199999999</v>
+      </c>
+      <c r="N98">
+        <v>37.0283808</v>
+      </c>
+      <c r="O98">
+        <v>7.775959967999999</v>
+      </c>
+      <c r="P98">
+        <v>29.252420832</v>
+      </c>
+      <c r="Q98">
+        <v>33.582420832</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.414646956203778</v>
+      </c>
+      <c r="T98">
+        <v>14.95397613951752</v>
+      </c>
+      <c r="U98">
+        <v>0.0473</v>
+      </c>
+      <c r="V98">
+        <v>0.21</v>
+      </c>
+      <c r="W98">
+        <v>0.037367</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>10.89635203924547</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.09229911481087523</v>
+      </c>
+      <c r="C99">
+        <v>2.410804627913066</v>
+      </c>
+      <c r="D99">
+        <v>-4.86119537208696</v>
+      </c>
+      <c r="E99">
+        <v>73.82799999999999</v>
+      </c>
+      <c r="F99">
+        <v>79.92799999999998</v>
+      </c>
+      <c r="G99">
+        <v>87.2</v>
+      </c>
+      <c r="H99">
+        <v>76.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>45.1</v>
+      </c>
+      <c r="K99">
+        <v>4.33</v>
+      </c>
+      <c r="L99">
+        <v>40.77</v>
+      </c>
+      <c r="M99">
+        <v>3.780594399999999</v>
+      </c>
+      <c r="N99">
+        <v>36.9894056</v>
+      </c>
+      <c r="O99">
+        <v>7.767775176</v>
+      </c>
+      <c r="P99">
+        <v>29.221630424</v>
+      </c>
+      <c r="Q99">
+        <v>33.551630424</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.868437493695839</v>
+      </c>
+      <c r="T99">
+        <v>19.88619104859352</v>
+      </c>
+      <c r="U99">
+        <v>0.0473</v>
+      </c>
+      <c r="V99">
+        <v>0.21</v>
+      </c>
+      <c r="W99">
+        <v>0.037367</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>10.78401851306768</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.09214003137359927</v>
+      </c>
+      <c r="C100">
+        <v>1.586190884147783</v>
+      </c>
+      <c r="D100">
+        <v>-4.861809115852223</v>
+      </c>
+      <c r="E100">
+        <v>74.652</v>
+      </c>
+      <c r="F100">
+        <v>80.752</v>
+      </c>
+      <c r="G100">
+        <v>87.2</v>
+      </c>
+      <c r="H100">
+        <v>76.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>45.1</v>
+      </c>
+      <c r="K100">
+        <v>4.33</v>
+      </c>
+      <c r="L100">
+        <v>40.77</v>
+      </c>
+      <c r="M100">
+        <v>3.8195696</v>
+      </c>
+      <c r="N100">
+        <v>36.9504304</v>
+      </c>
+      <c r="O100">
+        <v>7.759590383999999</v>
+      </c>
+      <c r="P100">
+        <v>29.190840016</v>
+      </c>
+      <c r="Q100">
+        <v>33.520840016</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.776018568679961</v>
+      </c>
+      <c r="T100">
+        <v>29.75062086674552</v>
+      </c>
+      <c r="U100">
+        <v>0.0473</v>
+      </c>
+      <c r="V100">
+        <v>0.21</v>
+      </c>
+      <c r="W100">
+        <v>0.037367</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>10.6739775078323</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.09198094793632333</v>
+      </c>
+      <c r="C101">
+        <v>0.761576985388146</v>
+      </c>
+      <c r="D101">
+        <v>-4.862423014611863</v>
+      </c>
+      <c r="E101">
+        <v>75.476</v>
+      </c>
+      <c r="F101">
+        <v>81.57599999999999</v>
+      </c>
+      <c r="G101">
+        <v>87.2</v>
+      </c>
+      <c r="H101">
+        <v>76.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>45.1</v>
+      </c>
+      <c r="K101">
+        <v>4.33</v>
+      </c>
+      <c r="L101">
+        <v>40.77</v>
+      </c>
+      <c r="M101">
+        <v>3.8585448</v>
+      </c>
+      <c r="N101">
+        <v>36.91145520000001</v>
+      </c>
+      <c r="O101">
+        <v>7.751405592</v>
+      </c>
+      <c r="P101">
+        <v>29.160049608</v>
+      </c>
+      <c r="Q101">
+        <v>33.49004960800001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.498761793632328</v>
+      </c>
+      <c r="T101">
+        <v>59.34391032120154</v>
+      </c>
+      <c r="U101">
+        <v>0.0473</v>
+      </c>
+      <c r="V101">
+        <v>0.21</v>
+      </c>
+      <c r="W101">
+        <v>0.037367</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>10.56615955320773</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/portugal/portugal_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_hotel_gaming.xlsx
@@ -1127,43 +1127,43 @@
         <v>54.054054054054</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>504.641585162845</v>
       </c>
       <c r="G2">
         <v>0.0172585669781931</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0171819314641745</v>
       </c>
       <c r="I2">
         <v>0.0100446023860463</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>54.6</v>
       </c>
       <c r="L2">
-        <v>55.1540013133742</v>
+        <v>54.6021920156162</v>
       </c>
       <c r="M2">
         <v>-18.846</v>
       </c>
       <c r="N2">
-        <v>-18.8459986866258</v>
+        <v>-18.8462679843838</v>
       </c>
       <c r="O2">
         <v>0.554</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.55154</v>
       </c>
       <c r="Q2">
         <v>0.0901636728066991</v>
       </c>
       <c r="R2">
-        <v>0.09016442288214339</v>
+        <v>0.09001062759409099</v>
       </c>
       <c r="S2">
         <v>0.0550418543268039</v>
@@ -1185,13 +1185,13 @@
         <v>0.09052003704548781</v>
       </c>
       <c r="X2">
-        <v>0.09016442288214339</v>
+        <v>0.0905184420142333</v>
       </c>
       <c r="Y2">
         <v>0.754044070358493</v>
       </c>
       <c r="Z2">
-        <v>0.7480479046815171</v>
+        <v>0.754017175840087</v>
       </c>
       <c r="AA2">
         <v>0.554</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09016442288214344</v>
+        <v>0.09001062759409095</v>
       </c>
       <c r="C2">
-        <v>55.1540013133742</v>
+        <v>54.60219201561623</v>
       </c>
       <c r="D2">
-        <v>-18.8459986866258</v>
+        <v>-18.84626798438378</v>
       </c>
       <c r="E2">
-        <v>-0.554</v>
+        <v>-0.002460000000000018</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.55154</v>
       </c>
       <c r="G2">
         <v>74</v>
@@ -1445,28 +1445,28 @@
         <v>14</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.027742462</v>
       </c>
       <c r="N2">
-        <v>14</v>
+        <v>13.972257538</v>
       </c>
       <c r="O2">
-        <v>2.94</v>
+        <v>2.93417408298</v>
       </c>
       <c r="P2">
-        <v>11.06</v>
+        <v>11.03808345502</v>
       </c>
       <c r="Q2">
-        <v>29.16</v>
+        <v>29.13808345502</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09016442288214344</v>
+        <v>0.09051844201423329</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815168</v>
+        <v>0.7540171758400865</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>504.6415851628453</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09001062759409095</v>
+        <v>0.08985683230603844</v>
       </c>
       <c r="C3">
-        <v>54.60219201561623</v>
+        <v>54.05038271016195</v>
       </c>
       <c r="D3">
-        <v>-18.84626798438378</v>
+        <v>-18.84653728983806</v>
       </c>
       <c r="E3">
-        <v>-0.002460000000000018</v>
+        <v>0.54908</v>
       </c>
       <c r="F3">
-        <v>0.55154</v>
+        <v>1.10308</v>
       </c>
       <c r="G3">
         <v>74</v>
@@ -1527,28 +1527,28 @@
         <v>14</v>
       </c>
       <c r="M3">
-        <v>0.027742462</v>
+        <v>0.055484924</v>
       </c>
       <c r="N3">
-        <v>13.972257538</v>
+        <v>13.944515076</v>
       </c>
       <c r="O3">
-        <v>2.93417408298</v>
+        <v>2.92834816596</v>
       </c>
       <c r="P3">
-        <v>11.03808345502</v>
+        <v>11.01616691004</v>
       </c>
       <c r="Q3">
-        <v>29.13808345502</v>
+        <v>29.11616691004</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09051844201423329</v>
+        <v>0.09087968602656984</v>
       </c>
       <c r="T3">
-        <v>0.7540171758400865</v>
+        <v>0.7601082688590353</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>504.6415851628453</v>
+        <v>252.3207925814227</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08985683230603844</v>
+        <v>0.08970303701798593</v>
       </c>
       <c r="C4">
-        <v>54.05038271016195</v>
+        <v>53.49857339701102</v>
       </c>
       <c r="D4">
-        <v>-18.84653728983806</v>
+        <v>-18.84680660298898</v>
       </c>
       <c r="E4">
-        <v>0.54908</v>
+        <v>1.10062</v>
       </c>
       <c r="F4">
-        <v>1.10308</v>
+        <v>1.65462</v>
       </c>
       <c r="G4">
         <v>74</v>
@@ -1609,28 +1609,28 @@
         <v>14</v>
       </c>
       <c r="M4">
-        <v>0.055484924</v>
+        <v>0.083227386</v>
       </c>
       <c r="N4">
-        <v>13.944515076</v>
+        <v>13.916772614</v>
       </c>
       <c r="O4">
-        <v>2.92834816596</v>
+        <v>2.92252224894</v>
       </c>
       <c r="P4">
-        <v>11.01616691004</v>
+        <v>10.99425036506</v>
       </c>
       <c r="Q4">
-        <v>29.11616691004</v>
+        <v>29.09425036506</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09087968602656984</v>
+        <v>0.09124837836905766</v>
       </c>
       <c r="T4">
-        <v>0.7601082688590353</v>
+        <v>0.7663249514247662</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>252.3207925814227</v>
+        <v>168.2138617209484</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08970303701798593</v>
+        <v>0.08954924172993345</v>
       </c>
       <c r="C5">
-        <v>53.49857339701102</v>
+        <v>52.94676407616313</v>
       </c>
       <c r="D5">
-        <v>-18.84680660298898</v>
+        <v>-18.84707592383687</v>
       </c>
       <c r="E5">
-        <v>1.10062</v>
+        <v>1.65216</v>
       </c>
       <c r="F5">
-        <v>1.65462</v>
+        <v>2.20616</v>
       </c>
       <c r="G5">
         <v>74</v>
@@ -1691,28 +1691,28 @@
         <v>14</v>
       </c>
       <c r="M5">
-        <v>0.083227386</v>
+        <v>0.110969848</v>
       </c>
       <c r="N5">
-        <v>13.916772614</v>
+        <v>13.889030152</v>
       </c>
       <c r="O5">
-        <v>2.92252224894</v>
+        <v>2.91669633192</v>
       </c>
       <c r="P5">
-        <v>10.99425036506</v>
+        <v>10.97233382008</v>
       </c>
       <c r="Q5">
-        <v>29.09425036506</v>
+        <v>29.07233382008</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09124837836905766</v>
+        <v>0.091624751802014</v>
       </c>
       <c r="T5">
-        <v>0.7663249514247662</v>
+        <v>0.7726711482106168</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>168.2138617209484</v>
+        <v>126.1603962907113</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08954924172993345</v>
+        <v>0.08939544644188094</v>
       </c>
       <c r="C6">
-        <v>52.94676407616313</v>
+        <v>52.39495474761793</v>
       </c>
       <c r="D6">
-        <v>-18.84707592383687</v>
+        <v>-18.84734525238207</v>
       </c>
       <c r="E6">
-        <v>1.65216</v>
+        <v>2.2037</v>
       </c>
       <c r="F6">
-        <v>2.20616</v>
+        <v>2.7577</v>
       </c>
       <c r="G6">
         <v>74</v>
@@ -1773,28 +1773,28 @@
         <v>14</v>
       </c>
       <c r="M6">
-        <v>0.110969848</v>
+        <v>0.13871231</v>
       </c>
       <c r="N6">
-        <v>13.889030152</v>
+        <v>13.86128769</v>
       </c>
       <c r="O6">
-        <v>2.91669633192</v>
+        <v>2.9108704149</v>
       </c>
       <c r="P6">
-        <v>10.97233382008</v>
+        <v>10.9504172751</v>
       </c>
       <c r="Q6">
-        <v>29.07233382008</v>
+        <v>29.0504172751</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.091624751802014</v>
+        <v>0.09200904888619046</v>
       </c>
       <c r="T6">
-        <v>0.7726711482106168</v>
+        <v>0.7791509491393274</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>126.1603962907113</v>
+        <v>100.9283170325691</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08939544644188094</v>
+        <v>0.08924165115382844</v>
       </c>
       <c r="C7">
-        <v>52.39495474761793</v>
+        <v>51.8431454113751</v>
       </c>
       <c r="D7">
-        <v>-18.84734525238207</v>
+        <v>-18.84761458862489</v>
       </c>
       <c r="E7">
-        <v>2.2037</v>
+        <v>2.755240000000001</v>
       </c>
       <c r="F7">
-        <v>2.7577</v>
+        <v>3.30924</v>
       </c>
       <c r="G7">
         <v>74</v>
@@ -1855,28 +1855,28 @@
         <v>14</v>
       </c>
       <c r="M7">
-        <v>0.13871231</v>
+        <v>0.166454772</v>
       </c>
       <c r="N7">
-        <v>13.86128769</v>
+        <v>13.833545228</v>
       </c>
       <c r="O7">
-        <v>2.9108704149</v>
+        <v>2.90504449788</v>
       </c>
       <c r="P7">
-        <v>10.9504172751</v>
+        <v>10.92850073012</v>
       </c>
       <c r="Q7">
-        <v>29.0504172751</v>
+        <v>29.02850073012</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09200904888619046</v>
+        <v>0.09240152250407281</v>
       </c>
       <c r="T7">
-        <v>0.7791509491393274</v>
+        <v>0.785768618172904</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>100.9283170325691</v>
+        <v>84.10693086047422</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08924165115382844</v>
+        <v>0.08908785586577594</v>
       </c>
       <c r="C8">
-        <v>51.8431454113751</v>
+        <v>51.29133606743434</v>
       </c>
       <c r="D8">
-        <v>-18.84761458862489</v>
+        <v>-18.84788393256567</v>
       </c>
       <c r="E8">
-        <v>2.75524</v>
+        <v>3.30678</v>
       </c>
       <c r="F8">
-        <v>3.30924</v>
+        <v>3.86078</v>
       </c>
       <c r="G8">
         <v>74</v>
@@ -1937,28 +1937,28 @@
         <v>14</v>
       </c>
       <c r="M8">
-        <v>0.166454772</v>
+        <v>0.194197234</v>
       </c>
       <c r="N8">
-        <v>13.833545228</v>
+        <v>13.805802766</v>
       </c>
       <c r="O8">
-        <v>2.90504449788</v>
+        <v>2.89921858086</v>
       </c>
       <c r="P8">
-        <v>10.92850073012</v>
+        <v>10.90658418514</v>
       </c>
       <c r="Q8">
-        <v>29.02850073012</v>
+        <v>29.00658418514</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09240152250407281</v>
+        <v>0.09280243641481284</v>
       </c>
       <c r="T8">
-        <v>0.785768618172904</v>
+        <v>0.7925286026695684</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>84.10693086047422</v>
+        <v>72.09165502326363</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08908785586577593</v>
+        <v>0.08893406057772343</v>
       </c>
       <c r="C9">
-        <v>51.29133606743434</v>
+        <v>50.73952671579526</v>
       </c>
       <c r="D9">
-        <v>-18.84788393256567</v>
+        <v>-18.84815328420474</v>
       </c>
       <c r="E9">
-        <v>3.306780000000001</v>
+        <v>3.85832</v>
       </c>
       <c r="F9">
-        <v>3.860780000000001</v>
+        <v>4.41232</v>
       </c>
       <c r="G9">
         <v>74</v>
@@ -2019,28 +2019,28 @@
         <v>14</v>
       </c>
       <c r="M9">
-        <v>0.194197234</v>
+        <v>0.221939696</v>
       </c>
       <c r="N9">
-        <v>13.805802766</v>
+        <v>13.778060304</v>
       </c>
       <c r="O9">
-        <v>2.89921858086</v>
+        <v>2.89339266384</v>
       </c>
       <c r="P9">
-        <v>10.90658418514</v>
+        <v>10.88466764016</v>
       </c>
       <c r="Q9">
-        <v>29.00658418514</v>
+        <v>28.98466764016</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09280243641481284</v>
+        <v>0.09321206584535156</v>
       </c>
       <c r="T9">
-        <v>0.7925286026695684</v>
+        <v>0.7994355433509428</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>72.0916550232636</v>
+        <v>63.08019814535567</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08893406057772343</v>
+        <v>0.08878026528967094</v>
       </c>
       <c r="C10">
-        <v>50.73952671579526</v>
+        <v>50.18771735645757</v>
       </c>
       <c r="D10">
-        <v>-18.84815328420474</v>
+        <v>-18.84842264354243</v>
       </c>
       <c r="E10">
-        <v>3.85832</v>
+        <v>4.40986</v>
       </c>
       <c r="F10">
-        <v>4.41232</v>
+        <v>4.96386</v>
       </c>
       <c r="G10">
         <v>74</v>
@@ -2101,28 +2101,28 @@
         <v>14</v>
       </c>
       <c r="M10">
-        <v>0.221939696</v>
+        <v>0.249682158</v>
       </c>
       <c r="N10">
-        <v>13.778060304</v>
+        <v>13.750317842</v>
       </c>
       <c r="O10">
-        <v>2.89339266384</v>
+        <v>2.88756674682</v>
       </c>
       <c r="P10">
-        <v>10.88466764016</v>
+        <v>10.86275109518</v>
       </c>
       <c r="Q10">
-        <v>28.98466764016</v>
+        <v>28.96275109518</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09321206584535156</v>
+        <v>0.09363069812051751</v>
       </c>
       <c r="T10">
-        <v>0.7994355433509428</v>
+        <v>0.8064942849264134</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>63.08019814535567</v>
+        <v>56.07128724031614</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08878026528967094</v>
+        <v>0.08862647000161843</v>
       </c>
       <c r="C11">
-        <v>50.18771735645757</v>
+        <v>49.63590798942094</v>
       </c>
       <c r="D11">
-        <v>-18.84842264354243</v>
+        <v>-18.84869201057906</v>
       </c>
       <c r="E11">
-        <v>4.40986</v>
+        <v>4.961399999999999</v>
       </c>
       <c r="F11">
-        <v>4.96386</v>
+        <v>5.5154</v>
       </c>
       <c r="G11">
         <v>74</v>
@@ -2183,28 +2183,28 @@
         <v>14</v>
       </c>
       <c r="M11">
-        <v>0.249682158</v>
+        <v>0.27742462</v>
       </c>
       <c r="N11">
-        <v>13.750317842</v>
+        <v>13.72257538</v>
       </c>
       <c r="O11">
-        <v>2.88756674682</v>
+        <v>2.8817408298</v>
       </c>
       <c r="P11">
-        <v>10.86275109518</v>
+        <v>10.8408345502</v>
       </c>
       <c r="Q11">
-        <v>28.96275109518</v>
+        <v>28.9408345502</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09363069812051751</v>
+        <v>0.09405863333513159</v>
       </c>
       <c r="T11">
-        <v>0.8064942849264134</v>
+        <v>0.8137098874257833</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>56.07128724031614</v>
+        <v>50.46415851628454</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08862647000161843</v>
+        <v>0.08847267471356593</v>
       </c>
       <c r="C12">
-        <v>49.63590798942094</v>
+        <v>49.08409861468502</v>
       </c>
       <c r="D12">
-        <v>-18.84869201057906</v>
+        <v>-18.84896138531498</v>
       </c>
       <c r="E12">
-        <v>4.9614</v>
+        <v>5.51294</v>
       </c>
       <c r="F12">
-        <v>5.515400000000001</v>
+        <v>6.066940000000001</v>
       </c>
       <c r="G12">
         <v>74</v>
@@ -2265,28 +2265,28 @@
         <v>14</v>
       </c>
       <c r="M12">
-        <v>0.27742462</v>
+        <v>0.305167082</v>
       </c>
       <c r="N12">
-        <v>13.72257538</v>
+        <v>13.694832918</v>
       </c>
       <c r="O12">
-        <v>2.8817408298</v>
+        <v>2.87591491278</v>
       </c>
       <c r="P12">
-        <v>10.8408345502</v>
+        <v>10.81891800522</v>
       </c>
       <c r="Q12">
-        <v>28.9408345502</v>
+        <v>28.91891800522</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09405863333513159</v>
+        <v>0.09449618507142239</v>
       </c>
       <c r="T12">
-        <v>0.8137098874257833</v>
+        <v>0.8210876382959256</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>50.46415851628453</v>
+        <v>45.87650774207684</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08847267471356593</v>
+        <v>0.08831887942551343</v>
       </c>
       <c r="C13">
-        <v>49.08409861468502</v>
+        <v>48.53228923224949</v>
       </c>
       <c r="D13">
-        <v>-18.84896138531498</v>
+        <v>-18.84923076775051</v>
       </c>
       <c r="E13">
-        <v>5.51294</v>
+        <v>6.06448</v>
       </c>
       <c r="F13">
-        <v>6.066940000000001</v>
+        <v>6.61848</v>
       </c>
       <c r="G13">
         <v>74</v>
@@ -2347,28 +2347,28 @@
         <v>14</v>
       </c>
       <c r="M13">
-        <v>0.305167082</v>
+        <v>0.332909544</v>
       </c>
       <c r="N13">
-        <v>13.694832918</v>
+        <v>13.667090456</v>
       </c>
       <c r="O13">
-        <v>2.87591491278</v>
+        <v>2.87008899576</v>
       </c>
       <c r="P13">
-        <v>10.81891800522</v>
+        <v>10.79700146024</v>
       </c>
       <c r="Q13">
-        <v>28.91891800522</v>
+        <v>28.89700146024</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09449618507142239</v>
+        <v>0.09494368116535618</v>
       </c>
       <c r="T13">
-        <v>0.8210876382959256</v>
+        <v>0.8286330653222075</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>45.87650774207684</v>
+        <v>42.05346543023711</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08831887942551343</v>
+        <v>0.08816508413746094</v>
       </c>
       <c r="C14">
-        <v>48.53228923224949</v>
+        <v>47.98047984211401</v>
       </c>
       <c r="D14">
-        <v>-18.84923076775051</v>
+        <v>-18.84950015788598</v>
       </c>
       <c r="E14">
-        <v>6.06448</v>
+        <v>6.616020000000001</v>
       </c>
       <c r="F14">
-        <v>6.61848</v>
+        <v>7.170020000000001</v>
       </c>
       <c r="G14">
         <v>74</v>
@@ -2429,28 +2429,28 @@
         <v>14</v>
       </c>
       <c r="M14">
-        <v>0.332909544</v>
+        <v>0.360652006</v>
       </c>
       <c r="N14">
-        <v>13.667090456</v>
+        <v>13.639347994</v>
       </c>
       <c r="O14">
-        <v>2.87008899576</v>
+        <v>2.86426307874</v>
       </c>
       <c r="P14">
-        <v>10.79700146024</v>
+        <v>10.77508491526</v>
       </c>
       <c r="Q14">
-        <v>28.89700146024</v>
+        <v>28.87508491526</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09494368116535618</v>
+        <v>0.09540146452581716</v>
       </c>
       <c r="T14">
-        <v>0.8286330653222075</v>
+        <v>0.8363519504410477</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>42.05346543023711</v>
+        <v>38.81858347406502</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08816508413746094</v>
+        <v>0.08801128884940843</v>
       </c>
       <c r="C15">
-        <v>47.98047984211401</v>
+        <v>47.42867044427828</v>
       </c>
       <c r="D15">
-        <v>-18.84950015788598</v>
+        <v>-18.84976955572171</v>
       </c>
       <c r="E15">
-        <v>6.616020000000001</v>
+        <v>7.167560000000001</v>
       </c>
       <c r="F15">
-        <v>7.170020000000001</v>
+        <v>7.721560000000001</v>
       </c>
       <c r="G15">
         <v>74</v>
@@ -2511,28 +2511,28 @@
         <v>14</v>
       </c>
       <c r="M15">
-        <v>0.360652006</v>
+        <v>0.388394468</v>
       </c>
       <c r="N15">
-        <v>13.639347994</v>
+        <v>13.611605532</v>
       </c>
       <c r="O15">
-        <v>2.86426307874</v>
+        <v>2.85843716172</v>
       </c>
       <c r="P15">
-        <v>10.77508491526</v>
+        <v>10.75316837028</v>
       </c>
       <c r="Q15">
-        <v>28.87508491526</v>
+        <v>28.85316837028</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09540146452581716</v>
+        <v>0.09586989401094004</v>
       </c>
       <c r="T15">
-        <v>0.8363519504410477</v>
+        <v>0.8442503445161398</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>38.81858347406502</v>
+        <v>36.04582751163181</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08801128884940843</v>
+        <v>0.08785749356135591</v>
       </c>
       <c r="C16">
-        <v>47.42867044427828</v>
+        <v>46.87686103874195</v>
       </c>
       <c r="D16">
-        <v>-18.84976955572171</v>
+        <v>-18.85003896125805</v>
       </c>
       <c r="E16">
-        <v>7.167560000000001</v>
+        <v>7.719100000000001</v>
       </c>
       <c r="F16">
-        <v>7.721560000000001</v>
+        <v>8.273100000000001</v>
       </c>
       <c r="G16">
         <v>74</v>
@@ -2593,28 +2593,28 @@
         <v>14</v>
       </c>
       <c r="M16">
-        <v>0.388394468</v>
+        <v>0.41613693</v>
       </c>
       <c r="N16">
-        <v>13.611605532</v>
+        <v>13.58386307</v>
       </c>
       <c r="O16">
-        <v>2.85843716172</v>
+        <v>2.8526112447</v>
       </c>
       <c r="P16">
-        <v>10.75316837028</v>
+        <v>10.7312518253</v>
       </c>
       <c r="Q16">
-        <v>28.85316837028</v>
+        <v>28.8312518253</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09586989401094004</v>
+        <v>0.09634934536630109</v>
       </c>
       <c r="T16">
-        <v>0.8442503445161398</v>
+        <v>0.8523345831577047</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>36.04582751163181</v>
+        <v>33.64277234418969</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08785749356135591</v>
+        <v>0.08770369827330342</v>
       </c>
       <c r="C17">
-        <v>46.87686103874195</v>
+        <v>46.32505162550467</v>
       </c>
       <c r="D17">
-        <v>-18.85003896125805</v>
+        <v>-18.85030837449532</v>
       </c>
       <c r="E17">
-        <v>7.719099999999999</v>
+        <v>8.27064</v>
       </c>
       <c r="F17">
-        <v>8.273099999999999</v>
+        <v>8.82464</v>
       </c>
       <c r="G17">
         <v>74</v>
@@ -2675,28 +2675,28 @@
         <v>14</v>
       </c>
       <c r="M17">
-        <v>0.41613693</v>
+        <v>0.443879392</v>
       </c>
       <c r="N17">
-        <v>13.58386307</v>
+        <v>13.556120608</v>
       </c>
       <c r="O17">
-        <v>2.8526112447</v>
+        <v>2.84678532768</v>
       </c>
       <c r="P17">
-        <v>10.7312518253</v>
+        <v>10.70933528032</v>
       </c>
       <c r="Q17">
-        <v>28.8312518253</v>
+        <v>28.80933528032</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09634934536630109</v>
+        <v>0.09684021223012312</v>
       </c>
       <c r="T17">
-        <v>0.8523345831577047</v>
+        <v>0.8606113036716879</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>33.64277234418969</v>
+        <v>31.54009907267783</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08770369827330342</v>
+        <v>0.08754990298525092</v>
       </c>
       <c r="C18">
-        <v>46.32505162550467</v>
+        <v>45.77324220456615</v>
       </c>
       <c r="D18">
-        <v>-18.85030837449532</v>
+        <v>-18.85057779543385</v>
       </c>
       <c r="E18">
-        <v>8.27064</v>
+        <v>8.822180000000001</v>
       </c>
       <c r="F18">
-        <v>8.82464</v>
+        <v>9.376180000000002</v>
       </c>
       <c r="G18">
         <v>74</v>
@@ -2757,28 +2757,28 @@
         <v>14</v>
       </c>
       <c r="M18">
-        <v>0.443879392</v>
+        <v>0.4716218540000001</v>
       </c>
       <c r="N18">
-        <v>13.556120608</v>
+        <v>13.528378146</v>
       </c>
       <c r="O18">
-        <v>2.84678532768</v>
+        <v>2.84095941066</v>
       </c>
       <c r="P18">
-        <v>10.70933528032</v>
+        <v>10.68741873534</v>
       </c>
       <c r="Q18">
-        <v>28.80933528032</v>
+        <v>28.78741873534</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09684021223012312</v>
+        <v>0.09734290721114569</v>
       </c>
       <c r="T18">
-        <v>0.8606113036716879</v>
+        <v>0.8690874632342008</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>31.54009907267783</v>
+        <v>29.68479912722619</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08754990298525092</v>
+        <v>0.08739610769719842</v>
       </c>
       <c r="C19">
-        <v>45.77324220456615</v>
+        <v>45.22143277592603</v>
       </c>
       <c r="D19">
-        <v>-18.85057779543385</v>
+        <v>-18.85084722407397</v>
       </c>
       <c r="E19">
-        <v>8.822180000000001</v>
+        <v>9.373720000000002</v>
       </c>
       <c r="F19">
-        <v>9.376180000000002</v>
+        <v>9.927720000000003</v>
       </c>
       <c r="G19">
         <v>74</v>
@@ -2839,28 +2839,28 @@
         <v>14</v>
       </c>
       <c r="M19">
-        <v>0.4716218540000001</v>
+        <v>0.4993643160000001</v>
       </c>
       <c r="N19">
-        <v>13.528378146</v>
+        <v>13.500635684</v>
       </c>
       <c r="O19">
-        <v>2.84095941066</v>
+        <v>2.83513349364</v>
       </c>
       <c r="P19">
-        <v>10.68741873534</v>
+        <v>10.66550219036</v>
       </c>
       <c r="Q19">
-        <v>28.78741873534</v>
+        <v>28.76550219036</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09734290721114569</v>
+        <v>0.09785786304536392</v>
       </c>
       <c r="T19">
-        <v>0.8690874632342008</v>
+        <v>0.8777703583957993</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.68479912722619</v>
+        <v>28.03564362015807</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08739610769719842</v>
+        <v>0.08724231240914593</v>
       </c>
       <c r="C20">
-        <v>45.22143277592603</v>
+        <v>44.66962333958399</v>
       </c>
       <c r="D20">
-        <v>-18.85084722407397</v>
+        <v>-18.85111666041601</v>
       </c>
       <c r="E20">
-        <v>9.37372</v>
+        <v>9.92526</v>
       </c>
       <c r="F20">
-        <v>9.927720000000001</v>
+        <v>10.47926</v>
       </c>
       <c r="G20">
         <v>74</v>
@@ -2921,28 +2921,28 @@
         <v>14</v>
       </c>
       <c r="M20">
-        <v>0.499364316</v>
+        <v>0.5271067779999999</v>
       </c>
       <c r="N20">
-        <v>13.500635684</v>
+        <v>13.472893222</v>
       </c>
       <c r="O20">
-        <v>2.83513349364</v>
+        <v>2.82930757662</v>
       </c>
       <c r="P20">
-        <v>10.66550219036</v>
+        <v>10.64358564538</v>
       </c>
       <c r="Q20">
-        <v>28.76550219036</v>
+        <v>28.74358564538</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09785786304536392</v>
+        <v>0.09838553383845176</v>
       </c>
       <c r="T20">
-        <v>0.8777703583957993</v>
+        <v>0.8866676460305239</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>28.03564362015807</v>
+        <v>26.56008342962344</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08724231240914593</v>
+        <v>0.08708851712109342</v>
       </c>
       <c r="C21">
-        <v>44.66962333958399</v>
+        <v>44.1178138955397</v>
       </c>
       <c r="D21">
-        <v>-18.85111666041601</v>
+        <v>-18.8513861044603</v>
       </c>
       <c r="E21">
-        <v>9.92526</v>
+        <v>10.4768</v>
       </c>
       <c r="F21">
-        <v>10.47926</v>
+        <v>11.0308</v>
       </c>
       <c r="G21">
         <v>74</v>
@@ -3003,28 +3003,28 @@
         <v>14</v>
       </c>
       <c r="M21">
-        <v>0.5271067779999999</v>
+        <v>0.55484924</v>
       </c>
       <c r="N21">
-        <v>13.472893222</v>
+        <v>13.44515076</v>
       </c>
       <c r="O21">
-        <v>2.82930757662</v>
+        <v>2.8234816596</v>
       </c>
       <c r="P21">
-        <v>10.64358564538</v>
+        <v>10.6216691004</v>
       </c>
       <c r="Q21">
-        <v>28.74358564538</v>
+        <v>28.7216691004</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09838553383845176</v>
+        <v>0.09892639640136677</v>
       </c>
       <c r="T21">
-        <v>0.8866676460305239</v>
+        <v>0.8957873658561164</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.56008342962344</v>
+        <v>25.23207925814227</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08708851712109342</v>
+        <v>0.08693472183304092</v>
       </c>
       <c r="C22">
-        <v>44.1178138955397</v>
+        <v>43.56600444379282</v>
       </c>
       <c r="D22">
-        <v>-18.8513861044603</v>
+        <v>-18.85165555620718</v>
       </c>
       <c r="E22">
-        <v>10.4768</v>
+        <v>11.02834</v>
       </c>
       <c r="F22">
-        <v>11.0308</v>
+        <v>11.58234</v>
       </c>
       <c r="G22">
         <v>74</v>
@@ -3085,28 +3085,28 @@
         <v>14</v>
       </c>
       <c r="M22">
-        <v>0.55484924</v>
+        <v>0.5825917020000001</v>
       </c>
       <c r="N22">
-        <v>13.44515076</v>
+        <v>13.417408298</v>
       </c>
       <c r="O22">
-        <v>2.8234816596</v>
+        <v>2.81765574258</v>
       </c>
       <c r="P22">
-        <v>10.6216691004</v>
+        <v>10.59975255542</v>
       </c>
       <c r="Q22">
-        <v>28.7216691004</v>
+        <v>28.69975255542</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09892639640136677</v>
+        <v>0.09948095168739357</v>
       </c>
       <c r="T22">
-        <v>0.8957873658561164</v>
+        <v>0.9051379646646354</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>25.23207925814227</v>
+        <v>24.0305516744212</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08693472183304092</v>
+        <v>0.08678092654498841</v>
       </c>
       <c r="C23">
-        <v>43.56600444379282</v>
+        <v>43.01419498434304</v>
       </c>
       <c r="D23">
-        <v>-18.85165555620718</v>
+        <v>-18.85192501565696</v>
       </c>
       <c r="E23">
-        <v>11.02834</v>
+        <v>11.57988</v>
       </c>
       <c r="F23">
-        <v>11.58234</v>
+        <v>12.13388</v>
       </c>
       <c r="G23">
         <v>74</v>
@@ -3167,28 +3167,28 @@
         <v>14</v>
       </c>
       <c r="M23">
-        <v>0.582591702</v>
+        <v>0.6103341640000001</v>
       </c>
       <c r="N23">
-        <v>13.417408298</v>
+        <v>13.389665836</v>
       </c>
       <c r="O23">
-        <v>2.81765574258</v>
+        <v>2.81182982556</v>
       </c>
       <c r="P23">
-        <v>10.59975255542</v>
+        <v>10.57783601044</v>
       </c>
       <c r="Q23">
-        <v>28.69975255542</v>
+        <v>28.67783601044</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09948095168739357</v>
+        <v>0.1000497263397287</v>
       </c>
       <c r="T23">
-        <v>0.9051379646646354</v>
+        <v>0.9147283224169624</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>24.0305516744212</v>
+        <v>22.93825387103842</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08678092654498841</v>
+        <v>0.08662713125693593</v>
       </c>
       <c r="C24">
-        <v>43.01419498434304</v>
+        <v>42.46238551719001</v>
       </c>
       <c r="D24">
-        <v>-18.85192501565696</v>
+        <v>-18.85219448280998</v>
       </c>
       <c r="E24">
-        <v>11.57988</v>
+        <v>12.13142</v>
       </c>
       <c r="F24">
-        <v>12.13388</v>
+        <v>12.68542</v>
       </c>
       <c r="G24">
         <v>74</v>
@@ -3249,28 +3249,28 @@
         <v>14</v>
       </c>
       <c r="M24">
-        <v>0.6103341640000001</v>
+        <v>0.638076626</v>
       </c>
       <c r="N24">
-        <v>13.389665836</v>
+        <v>13.361923374</v>
       </c>
       <c r="O24">
-        <v>2.81182982556</v>
+        <v>2.80600390854</v>
       </c>
       <c r="P24">
-        <v>10.57783601044</v>
+        <v>10.55591946546</v>
       </c>
       <c r="Q24">
-        <v>28.67783601044</v>
+        <v>28.65591946546</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1000497263397287</v>
+        <v>0.100633274359657</v>
       </c>
       <c r="T24">
-        <v>0.9147283224169624</v>
+        <v>0.9245677803706488</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.93825387103842</v>
+        <v>21.9409384853411</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08662713125693593</v>
+        <v>0.08647333596888342</v>
       </c>
       <c r="C25">
-        <v>42.46238551719001</v>
+        <v>41.91057604233341</v>
       </c>
       <c r="D25">
-        <v>-18.85219448280998</v>
+        <v>-18.85246395766658</v>
       </c>
       <c r="E25">
-        <v>12.13142</v>
+        <v>12.68296</v>
       </c>
       <c r="F25">
-        <v>12.68542</v>
+        <v>13.23696</v>
       </c>
       <c r="G25">
         <v>74</v>
@@ -3331,28 +3331,28 @@
         <v>14</v>
       </c>
       <c r="M25">
-        <v>0.638076626</v>
+        <v>0.665819088</v>
       </c>
       <c r="N25">
-        <v>13.361923374</v>
+        <v>13.334180912</v>
       </c>
       <c r="O25">
-        <v>2.80600390854</v>
+        <v>2.80017799152</v>
       </c>
       <c r="P25">
-        <v>10.55591946546</v>
+        <v>10.53400292048</v>
       </c>
       <c r="Q25">
-        <v>28.65591946546</v>
+        <v>28.63400292048</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.100633274359657</v>
+        <v>0.1012321789064256</v>
       </c>
       <c r="T25">
-        <v>0.9245677803706488</v>
+        <v>0.9346661714283794</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.9409384853411</v>
+        <v>21.02673271511856</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08647333596888342</v>
+        <v>0.08631954068083092</v>
       </c>
       <c r="C26">
-        <v>41.91057604233342</v>
+        <v>41.35876655977292</v>
       </c>
       <c r="D26">
-        <v>-18.85246395766658</v>
+        <v>-18.85273344022708</v>
       </c>
       <c r="E26">
-        <v>12.68296</v>
+        <v>13.2345</v>
       </c>
       <c r="F26">
-        <v>13.23696</v>
+        <v>13.7885</v>
       </c>
       <c r="G26">
         <v>74</v>
@@ -3413,28 +3413,28 @@
         <v>14</v>
       </c>
       <c r="M26">
-        <v>0.665819088</v>
+        <v>0.69356155</v>
       </c>
       <c r="N26">
-        <v>13.334180912</v>
+        <v>13.30643845</v>
       </c>
       <c r="O26">
-        <v>2.80017799152</v>
+        <v>2.7943520745</v>
       </c>
       <c r="P26">
-        <v>10.53400292048</v>
+        <v>10.5120863755</v>
       </c>
       <c r="Q26">
-        <v>28.63400292048</v>
+        <v>28.6120863755</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1012321789064256</v>
+        <v>0.1018470542411079</v>
       </c>
       <c r="T26">
-        <v>0.9346661714283794</v>
+        <v>0.9450338529143162</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>21.02673271511856</v>
+        <v>20.18566340651381</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08631954068083092</v>
+        <v>0.08616574539277841</v>
       </c>
       <c r="C27">
-        <v>41.35876655977292</v>
+        <v>40.80695706950818</v>
       </c>
       <c r="D27">
-        <v>-18.85273344022708</v>
+        <v>-18.85300293049182</v>
       </c>
       <c r="E27">
-        <v>13.2345</v>
+        <v>13.78604</v>
       </c>
       <c r="F27">
-        <v>13.7885</v>
+        <v>14.34004</v>
       </c>
       <c r="G27">
         <v>74</v>
@@ -3495,28 +3495,28 @@
         <v>14</v>
       </c>
       <c r="M27">
-        <v>0.69356155</v>
+        <v>0.721304012</v>
       </c>
       <c r="N27">
-        <v>13.30643845</v>
+        <v>13.278695988</v>
       </c>
       <c r="O27">
-        <v>2.7943520745</v>
+        <v>2.78852615748</v>
       </c>
       <c r="P27">
-        <v>10.5120863755</v>
+        <v>10.49016983052</v>
       </c>
       <c r="Q27">
-        <v>28.6120863755</v>
+        <v>28.59016983052</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1018470542411079</v>
+        <v>0.1024785478280789</v>
       </c>
       <c r="T27">
-        <v>0.9450338529143162</v>
+        <v>0.9556817420079811</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>20.18566340651381</v>
+        <v>19.40929173703251</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08616574539277841</v>
+        <v>0.0860119501047259</v>
       </c>
       <c r="C28">
-        <v>40.80695706950818</v>
+        <v>40.25514757153888</v>
       </c>
       <c r="D28">
-        <v>-18.85300293049182</v>
+        <v>-18.85327242846112</v>
       </c>
       <c r="E28">
-        <v>13.78604</v>
+        <v>14.33758</v>
       </c>
       <c r="F28">
-        <v>14.34004</v>
+        <v>14.89158</v>
       </c>
       <c r="G28">
         <v>74</v>
@@ -3577,28 +3577,28 @@
         <v>14</v>
       </c>
       <c r="M28">
-        <v>0.721304012</v>
+        <v>0.749046474</v>
       </c>
       <c r="N28">
-        <v>13.278695988</v>
+        <v>13.250953526</v>
       </c>
       <c r="O28">
-        <v>2.78852615748</v>
+        <v>2.78270024046</v>
       </c>
       <c r="P28">
-        <v>10.49016983052</v>
+        <v>10.46825328554</v>
       </c>
       <c r="Q28">
-        <v>28.59016983052</v>
+        <v>28.56825328554</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1024785478280789</v>
+        <v>0.1031273426092136</v>
       </c>
       <c r="T28">
-        <v>0.9556817420079811</v>
+        <v>0.9666213540905135</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.40929173703251</v>
+        <v>18.69042908010538</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0860119501047259</v>
+        <v>0.08585815481667342</v>
       </c>
       <c r="C29">
-        <v>40.25514757153888</v>
+        <v>39.70333806586469</v>
       </c>
       <c r="D29">
-        <v>-18.85327242846112</v>
+        <v>-18.85354193413531</v>
       </c>
       <c r="E29">
-        <v>14.33758</v>
+        <v>14.88912</v>
       </c>
       <c r="F29">
-        <v>14.89158</v>
+        <v>15.44312</v>
       </c>
       <c r="G29">
         <v>74</v>
@@ -3659,28 +3659,28 @@
         <v>14</v>
       </c>
       <c r="M29">
-        <v>0.749046474</v>
+        <v>0.7767889360000001</v>
       </c>
       <c r="N29">
-        <v>13.250953526</v>
+        <v>13.223211064</v>
       </c>
       <c r="O29">
-        <v>2.78270024046</v>
+        <v>2.77687432344</v>
       </c>
       <c r="P29">
-        <v>10.46825328554</v>
+        <v>10.44633674056</v>
       </c>
       <c r="Q29">
-        <v>28.56825328554</v>
+        <v>28.54633674056</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1031273426092136</v>
+        <v>0.103794159467602</v>
       </c>
       <c r="T29">
-        <v>0.9666213540905135</v>
+        <v>0.9778648442864496</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.69042908010538</v>
+        <v>18.0229137558159</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08585815481667342</v>
+        <v>0.0857043595286209</v>
       </c>
       <c r="C30">
-        <v>39.70333806586469</v>
+        <v>39.15152855248527</v>
       </c>
       <c r="D30">
-        <v>-18.85354193413531</v>
+        <v>-18.85381144751473</v>
       </c>
       <c r="E30">
-        <v>14.88912</v>
+        <v>15.44066</v>
       </c>
       <c r="F30">
-        <v>15.44312</v>
+        <v>15.99466</v>
       </c>
       <c r="G30">
         <v>74</v>
@@ -3741,28 +3741,28 @@
         <v>14</v>
       </c>
       <c r="M30">
-        <v>0.7767889360000001</v>
+        <v>0.8045313980000002</v>
       </c>
       <c r="N30">
-        <v>13.223211064</v>
+        <v>13.195468602</v>
       </c>
       <c r="O30">
-        <v>2.77687432344</v>
+        <v>2.77104840642</v>
       </c>
       <c r="P30">
-        <v>10.44633674056</v>
+        <v>10.42442019558</v>
       </c>
       <c r="Q30">
-        <v>28.54633674056</v>
+        <v>28.52442019558</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.103794159467602</v>
+        <v>0.1044797598994661</v>
       </c>
       <c r="T30">
-        <v>0.9778648442864496</v>
+        <v>0.9894250525160739</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>18.0229137558159</v>
+        <v>17.40143397113259</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0857043595286209</v>
+        <v>0.08555056424056841</v>
       </c>
       <c r="C31">
-        <v>39.15152855248527</v>
+        <v>38.5997190314003</v>
       </c>
       <c r="D31">
-        <v>-18.85381144751473</v>
+        <v>-18.8540809685997</v>
       </c>
       <c r="E31">
-        <v>15.44066</v>
+        <v>15.9922</v>
       </c>
       <c r="F31">
-        <v>15.99466</v>
+        <v>16.5462</v>
       </c>
       <c r="G31">
         <v>74</v>
@@ -3823,28 +3823,28 @@
         <v>14</v>
       </c>
       <c r="M31">
-        <v>0.804531398</v>
+        <v>0.8322738599999999</v>
       </c>
       <c r="N31">
-        <v>13.195468602</v>
+        <v>13.16772614</v>
       </c>
       <c r="O31">
-        <v>2.77104840642</v>
+        <v>2.7652224894</v>
       </c>
       <c r="P31">
-        <v>10.42442019558</v>
+        <v>10.4025036506</v>
       </c>
       <c r="Q31">
-        <v>28.52442019558</v>
+        <v>28.5025036506</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1044797598994661</v>
+        <v>0.1051849489150977</v>
       </c>
       <c r="T31">
-        <v>0.9894250525160739</v>
+        <v>1.001315552409402</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.4014339711326</v>
+        <v>16.82138617209484</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08555056424056841</v>
+        <v>0.0853967689525159</v>
       </c>
       <c r="C32">
-        <v>38.5997190314003</v>
+        <v>38.04790950260944</v>
       </c>
       <c r="D32">
-        <v>-18.8540809685997</v>
+        <v>-18.85435049739056</v>
       </c>
       <c r="E32">
-        <v>15.9922</v>
+        <v>16.54374</v>
       </c>
       <c r="F32">
-        <v>16.5462</v>
+        <v>17.09774</v>
       </c>
       <c r="G32">
         <v>74</v>
@@ -3905,28 +3905,28 @@
         <v>14</v>
       </c>
       <c r="M32">
-        <v>0.8322738599999999</v>
+        <v>0.860016322</v>
       </c>
       <c r="N32">
-        <v>13.16772614</v>
+        <v>13.139983678</v>
       </c>
       <c r="O32">
-        <v>2.7652224894</v>
+        <v>2.75939657238</v>
       </c>
       <c r="P32">
-        <v>10.4025036506</v>
+        <v>10.38058710562</v>
       </c>
       <c r="Q32">
-        <v>28.5025036506</v>
+        <v>28.48058710562</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1051849489150977</v>
+        <v>0.105910578192052</v>
       </c>
       <c r="T32">
-        <v>1.001315552409402</v>
+        <v>1.013550704473551</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.82138617209484</v>
+        <v>16.27876081170469</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0853967689525159</v>
+        <v>0.08524297366446341</v>
       </c>
       <c r="C33">
-        <v>38.04790950260944</v>
+        <v>37.49609996611237</v>
       </c>
       <c r="D33">
-        <v>-18.85435049739056</v>
+        <v>-18.85462003388763</v>
       </c>
       <c r="E33">
-        <v>16.54374</v>
+        <v>17.09528</v>
       </c>
       <c r="F33">
-        <v>17.09774</v>
+        <v>17.64928</v>
       </c>
       <c r="G33">
         <v>74</v>
@@ -3987,28 +3987,28 @@
         <v>14</v>
       </c>
       <c r="M33">
-        <v>0.860016322</v>
+        <v>0.887758784</v>
       </c>
       <c r="N33">
-        <v>13.139983678</v>
+        <v>13.112241216</v>
       </c>
       <c r="O33">
-        <v>2.75939657238</v>
+        <v>2.75357065536</v>
       </c>
       <c r="P33">
-        <v>10.38058710562</v>
+        <v>10.35867056064</v>
       </c>
       <c r="Q33">
-        <v>28.48058710562</v>
+        <v>28.45867056064</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.105910578192052</v>
+        <v>0.1066575495065638</v>
       </c>
       <c r="T33">
-        <v>1.013550704473551</v>
+        <v>1.026145713951351</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.27876081170469</v>
+        <v>15.77004953633892</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08524297366446341</v>
+        <v>0.08508917837641089</v>
       </c>
       <c r="C34">
-        <v>37.49609996611237</v>
+        <v>36.94429042190875</v>
       </c>
       <c r="D34">
-        <v>-18.85462003388763</v>
+        <v>-18.85488957809125</v>
       </c>
       <c r="E34">
-        <v>17.09528</v>
+        <v>17.64682000000001</v>
       </c>
       <c r="F34">
-        <v>17.64928</v>
+        <v>18.20082</v>
       </c>
       <c r="G34">
         <v>74</v>
@@ -4069,28 +4069,28 @@
         <v>14</v>
       </c>
       <c r="M34">
-        <v>0.887758784</v>
+        <v>0.9155012460000002</v>
       </c>
       <c r="N34">
-        <v>13.112241216</v>
+        <v>13.084498754</v>
       </c>
       <c r="O34">
-        <v>2.75357065536</v>
+        <v>2.74774473834</v>
       </c>
       <c r="P34">
-        <v>10.35867056064</v>
+        <v>10.33675401566</v>
       </c>
       <c r="Q34">
-        <v>28.45867056064</v>
+        <v>28.43675401566</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1066575495065638</v>
+        <v>0.1074268184722551</v>
       </c>
       <c r="T34">
-        <v>1.026145713951351</v>
+        <v>1.039116693861325</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.77004953633892</v>
+        <v>15.29216924735895</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08508917837641089</v>
+        <v>0.08493538308835841</v>
       </c>
       <c r="C35">
-        <v>36.94429042190875</v>
+        <v>36.39248086999826</v>
       </c>
       <c r="D35">
-        <v>-18.85488957809125</v>
+        <v>-18.85515913000174</v>
       </c>
       <c r="E35">
-        <v>17.64682000000001</v>
+        <v>18.19836</v>
       </c>
       <c r="F35">
-        <v>18.20082</v>
+        <v>18.75236</v>
       </c>
       <c r="G35">
         <v>74</v>
@@ -4151,28 +4151,28 @@
         <v>14</v>
       </c>
       <c r="M35">
-        <v>0.9155012460000002</v>
+        <v>0.9432437080000001</v>
       </c>
       <c r="N35">
-        <v>13.084498754</v>
+        <v>13.056756292</v>
       </c>
       <c r="O35">
-        <v>2.74774473834</v>
+        <v>2.74191882132</v>
       </c>
       <c r="P35">
-        <v>10.33675401566</v>
+        <v>10.31483747068</v>
       </c>
       <c r="Q35">
-        <v>28.43675401566</v>
+        <v>28.41483747068</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1074268184722551</v>
+        <v>0.1082193986187249</v>
       </c>
       <c r="T35">
-        <v>1.039116693861325</v>
+        <v>1.052480733768571</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.29216924735895</v>
+        <v>14.84239956361309</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08493538308835841</v>
+        <v>0.0847815878003059</v>
       </c>
       <c r="C36">
-        <v>36.39248086999826</v>
+        <v>35.84067131038056</v>
       </c>
       <c r="D36">
-        <v>-18.85515913000174</v>
+        <v>-18.85542868961944</v>
       </c>
       <c r="E36">
-        <v>18.19836</v>
+        <v>18.7499</v>
       </c>
       <c r="F36">
-        <v>18.75236</v>
+        <v>19.3039</v>
       </c>
       <c r="G36">
         <v>74</v>
@@ -4233,28 +4233,28 @@
         <v>14</v>
       </c>
       <c r="M36">
-        <v>0.9432437080000001</v>
+        <v>0.9709861700000001</v>
       </c>
       <c r="N36">
-        <v>13.056756292</v>
+        <v>13.02901383</v>
       </c>
       <c r="O36">
-        <v>2.74191882132</v>
+        <v>2.7360929043</v>
       </c>
       <c r="P36">
-        <v>10.31483747068</v>
+        <v>10.2929209257</v>
       </c>
       <c r="Q36">
-        <v>28.41483747068</v>
+        <v>28.3929209257</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1082193986187249</v>
+        <v>0.1090363658466245</v>
       </c>
       <c r="T36">
-        <v>1.052480733768571</v>
+        <v>1.066255974903731</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.84239956361309</v>
+        <v>14.41833100465272</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0847815878003059</v>
+        <v>0.0846277925122534</v>
       </c>
       <c r="C37">
-        <v>35.84067131038056</v>
+        <v>35.28886174305531</v>
       </c>
       <c r="D37">
-        <v>-18.85542868961944</v>
+        <v>-18.85569825694468</v>
       </c>
       <c r="E37">
-        <v>18.7499</v>
+        <v>19.30144000000001</v>
       </c>
       <c r="F37">
-        <v>19.3039</v>
+        <v>19.85544000000001</v>
       </c>
       <c r="G37">
         <v>74</v>
@@ -4315,28 +4315,28 @@
         <v>14</v>
       </c>
       <c r="M37">
-        <v>0.9709861700000001</v>
+        <v>0.9987286320000002</v>
       </c>
       <c r="N37">
-        <v>13.02901383</v>
+        <v>13.001271368</v>
       </c>
       <c r="O37">
-        <v>2.7360929043</v>
+        <v>2.73026698728</v>
       </c>
       <c r="P37">
-        <v>10.2929209257</v>
+        <v>10.27100438072</v>
       </c>
       <c r="Q37">
-        <v>28.3929209257</v>
+        <v>28.37100438072</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1090363658466245</v>
+        <v>0.109878863300396</v>
       </c>
       <c r="T37">
-        <v>1.066255974903731</v>
+        <v>1.080461692324366</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.41833100465272</v>
+        <v>14.01782181007903</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08462779251225341</v>
+        <v>0.0844739972242009</v>
       </c>
       <c r="C38">
-        <v>35.28886174305531</v>
+        <v>34.7370521680222</v>
       </c>
       <c r="D38">
-        <v>-18.85569825694468</v>
+        <v>-18.85596783197779</v>
       </c>
       <c r="E38">
-        <v>19.30144</v>
+        <v>19.85298</v>
       </c>
       <c r="F38">
-        <v>19.85544</v>
+        <v>20.40698</v>
       </c>
       <c r="G38">
         <v>74</v>
@@ -4397,28 +4397,28 @@
         <v>14</v>
       </c>
       <c r="M38">
-        <v>0.9987286320000001</v>
+        <v>1.026471094</v>
       </c>
       <c r="N38">
-        <v>13.001271368</v>
+        <v>12.973528906</v>
       </c>
       <c r="O38">
-        <v>2.73026698728</v>
+        <v>2.72444107026</v>
       </c>
       <c r="P38">
-        <v>10.27100438072</v>
+        <v>10.24908783574</v>
       </c>
       <c r="Q38">
-        <v>28.37100438072</v>
+        <v>28.34908783574</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.109878863300396</v>
+        <v>0.1107481067050808</v>
       </c>
       <c r="T38">
-        <v>1.080461692324366</v>
+        <v>1.095118384901211</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>14.01782181007903</v>
+        <v>13.63896176115798</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0844739972242009</v>
+        <v>0.08432020193614839</v>
       </c>
       <c r="C39">
-        <v>34.7370521680222</v>
+        <v>34.1852425852809</v>
       </c>
       <c r="D39">
-        <v>-18.85596783197779</v>
+        <v>-18.8562374147191</v>
       </c>
       <c r="E39">
-        <v>19.85298</v>
+        <v>20.40452</v>
       </c>
       <c r="F39">
-        <v>20.40698</v>
+        <v>20.95852</v>
       </c>
       <c r="G39">
         <v>74</v>
@@ -4479,28 +4479,28 @@
         <v>14</v>
       </c>
       <c r="M39">
-        <v>1.026471094</v>
+        <v>1.054213556</v>
       </c>
       <c r="N39">
-        <v>12.973528906</v>
+        <v>12.945786444</v>
       </c>
       <c r="O39">
-        <v>2.72444107026</v>
+        <v>2.71861515324</v>
       </c>
       <c r="P39">
-        <v>10.24908783574</v>
+        <v>10.22717129076</v>
       </c>
       <c r="Q39">
-        <v>28.34908783574</v>
+        <v>28.32717129076</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1107481067050808</v>
+        <v>0.1116453902195942</v>
       </c>
       <c r="T39">
-        <v>1.095118384901211</v>
+        <v>1.110247874012793</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.63896176115798</v>
+        <v>13.28004171481172</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08432020193614839</v>
+        <v>0.0841664066480959</v>
       </c>
       <c r="C40">
-        <v>34.1852425852809</v>
+        <v>33.63343299483106</v>
       </c>
       <c r="D40">
-        <v>-18.8562374147191</v>
+        <v>-18.85650700516894</v>
       </c>
       <c r="E40">
-        <v>20.40452</v>
+        <v>20.95606</v>
       </c>
       <c r="F40">
-        <v>20.95852</v>
+        <v>21.51006</v>
       </c>
       <c r="G40">
         <v>74</v>
@@ -4561,28 +4561,28 @@
         <v>14</v>
       </c>
       <c r="M40">
-        <v>1.054213556</v>
+        <v>1.081956018</v>
       </c>
       <c r="N40">
-        <v>12.945786444</v>
+        <v>12.918043982</v>
       </c>
       <c r="O40">
-        <v>2.71861515324</v>
+        <v>2.71278923622</v>
       </c>
       <c r="P40">
-        <v>10.22717129076</v>
+        <v>10.20525474578</v>
       </c>
       <c r="Q40">
-        <v>28.32717129076</v>
+        <v>28.30525474578</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1116453902195942</v>
+        <v>0.112572092865731</v>
       </c>
       <c r="T40">
-        <v>1.110247874012793</v>
+        <v>1.125873411947706</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>13.28004171481172</v>
+        <v>12.93952782468834</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0841664066480959</v>
+        <v>0.0844866113600434</v>
       </c>
       <c r="C41">
-        <v>33.63343299483106</v>
+        <v>33.08245427858722</v>
       </c>
       <c r="D41">
-        <v>-18.85650700516894</v>
+        <v>-18.85594572141278</v>
       </c>
       <c r="E41">
-        <v>20.95606</v>
+        <v>21.5076</v>
       </c>
       <c r="F41">
-        <v>21.51006</v>
+        <v>22.0616</v>
       </c>
       <c r="G41">
         <v>74</v>
@@ -4643,45 +4643,45 @@
         <v>14</v>
       </c>
       <c r="M41">
-        <v>1.081956018</v>
+        <v>1.14279088</v>
       </c>
       <c r="N41">
-        <v>12.918043982</v>
+        <v>12.85720912</v>
       </c>
       <c r="O41">
-        <v>2.71278923622</v>
+        <v>2.7000139152</v>
       </c>
       <c r="P41">
-        <v>10.20525474578</v>
+        <v>10.1571952048</v>
       </c>
       <c r="Q41">
-        <v>28.30525474578</v>
+        <v>28.2571952048</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.112572092865731</v>
+        <v>0.1135296856000723</v>
       </c>
       <c r="T41">
-        <v>1.125873411947706</v>
+        <v>1.142019801147116</v>
       </c>
       <c r="U41">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V41">
         <v>0.21</v>
       </c>
       <c r="W41">
-        <v>0.039737</v>
+        <v>0.040922</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y41">
-        <v>12.93952782468834</v>
+        <v>12.25071029618297</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0844866113600434</v>
+        <v>0.0843446660719909</v>
       </c>
       <c r="C42">
-        <v>33.08245427858722</v>
+        <v>32.53066546818179</v>
       </c>
       <c r="D42">
-        <v>-18.85594572141278</v>
+        <v>-18.85619453181821</v>
       </c>
       <c r="E42">
-        <v>21.5076</v>
+        <v>22.05914000000001</v>
       </c>
       <c r="F42">
-        <v>22.0616</v>
+        <v>22.61314</v>
       </c>
       <c r="G42">
         <v>74</v>
@@ -4725,28 +4725,28 @@
         <v>14</v>
       </c>
       <c r="M42">
-        <v>1.14279088</v>
+        <v>1.171360652</v>
       </c>
       <c r="N42">
-        <v>12.85720912</v>
+        <v>12.828639348</v>
       </c>
       <c r="O42">
-        <v>2.7000139152</v>
+        <v>2.69401426308</v>
       </c>
       <c r="P42">
-        <v>10.1571952048</v>
+        <v>10.13462508492</v>
       </c>
       <c r="Q42">
-        <v>28.2571952048</v>
+        <v>28.23462508492</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1135296856000723</v>
+        <v>0.1145197391050693</v>
       </c>
       <c r="T42">
-        <v>1.142019801147116</v>
+        <v>1.158713525573624</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.25071029618297</v>
+        <v>11.95191248408095</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0843446660719909</v>
+        <v>0.08420272078393841</v>
       </c>
       <c r="C43">
-        <v>32.53066546818179</v>
+        <v>31.97887665121</v>
       </c>
       <c r="D43">
-        <v>-18.85619453181821</v>
+        <v>-18.85644334878999</v>
       </c>
       <c r="E43">
-        <v>22.05914000000001</v>
+        <v>22.61068000000001</v>
       </c>
       <c r="F43">
-        <v>22.61314</v>
+        <v>23.16468</v>
       </c>
       <c r="G43">
         <v>74</v>
@@ -4807,28 +4807,28 @@
         <v>14</v>
       </c>
       <c r="M43">
-        <v>1.171360652</v>
+        <v>1.199930424</v>
       </c>
       <c r="N43">
-        <v>12.828639348</v>
+        <v>12.800069576</v>
       </c>
       <c r="O43">
-        <v>2.69401426308</v>
+        <v>2.68801461096</v>
       </c>
       <c r="P43">
-        <v>10.13462508492</v>
+        <v>10.11205496504</v>
       </c>
       <c r="Q43">
-        <v>28.23462508492</v>
+        <v>28.21205496504</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1145197391050693</v>
+        <v>0.1155439323861007</v>
       </c>
       <c r="T43">
-        <v>1.158713525573624</v>
+        <v>1.175982895670012</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.95191248408095</v>
+        <v>11.66734313922188</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0842027207839384</v>
+        <v>0.08406077549588589</v>
       </c>
       <c r="C44">
-        <v>31.97887665121</v>
+        <v>31.4270878276716</v>
       </c>
       <c r="D44">
-        <v>-18.85644334878999</v>
+        <v>-18.8566921723284</v>
       </c>
       <c r="E44">
-        <v>22.61068</v>
+        <v>23.16222</v>
       </c>
       <c r="F44">
-        <v>23.16468</v>
+        <v>23.71622</v>
       </c>
       <c r="G44">
         <v>74</v>
@@ -4889,28 +4889,28 @@
         <v>14</v>
       </c>
       <c r="M44">
-        <v>1.199930424</v>
+        <v>1.228500196</v>
       </c>
       <c r="N44">
-        <v>12.800069576</v>
+        <v>12.771499804</v>
       </c>
       <c r="O44">
-        <v>2.68801461096</v>
+        <v>2.68201495884</v>
       </c>
       <c r="P44">
-        <v>10.11205496504</v>
+        <v>10.08948484516</v>
       </c>
       <c r="Q44">
-        <v>28.21205496504</v>
+        <v>28.18948484516</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1155439323861007</v>
+        <v>0.116604062273484</v>
       </c>
       <c r="T44">
-        <v>1.175982895670012</v>
+        <v>1.1938582085768</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.66734313922188</v>
+        <v>11.39600957784463</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08406077549588589</v>
+        <v>0.08391883020783339</v>
       </c>
       <c r="C45">
-        <v>31.4270878276716</v>
+        <v>30.87529899756632</v>
       </c>
       <c r="D45">
-        <v>-18.8566921723284</v>
+        <v>-18.85694100243368</v>
       </c>
       <c r="E45">
-        <v>23.16222</v>
+        <v>23.71376</v>
       </c>
       <c r="F45">
-        <v>23.71622</v>
+        <v>24.26776</v>
       </c>
       <c r="G45">
         <v>74</v>
@@ -4971,28 +4971,28 @@
         <v>14</v>
       </c>
       <c r="M45">
-        <v>1.228500196</v>
+        <v>1.257069968</v>
       </c>
       <c r="N45">
-        <v>12.771499804</v>
+        <v>12.742930032</v>
       </c>
       <c r="O45">
-        <v>2.68201495884</v>
+        <v>2.67601530672</v>
       </c>
       <c r="P45">
-        <v>10.08948484516</v>
+        <v>10.06691472528</v>
       </c>
       <c r="Q45">
-        <v>28.18948484516</v>
+        <v>28.16691472528</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.116604062273484</v>
+        <v>0.1177020539425596</v>
       </c>
       <c r="T45">
-        <v>1.1938582085768</v>
+        <v>1.212371925515973</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.39600957784463</v>
+        <v>11.13700936016634</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08391883020783339</v>
+        <v>0.08377688491978089</v>
       </c>
       <c r="C46">
-        <v>30.87529899756632</v>
+        <v>30.3235101608939</v>
       </c>
       <c r="D46">
-        <v>-18.85694100243368</v>
+        <v>-18.85718983910609</v>
       </c>
       <c r="E46">
-        <v>23.71376</v>
+        <v>24.2653</v>
       </c>
       <c r="F46">
-        <v>24.26776</v>
+        <v>24.8193</v>
       </c>
       <c r="G46">
         <v>74</v>
@@ -5053,28 +5053,28 @@
         <v>14</v>
       </c>
       <c r="M46">
-        <v>1.257069968</v>
+        <v>1.28563974</v>
       </c>
       <c r="N46">
-        <v>12.742930032</v>
+        <v>12.71436026</v>
       </c>
       <c r="O46">
-        <v>2.67601530672</v>
+        <v>2.6700156546</v>
       </c>
       <c r="P46">
-        <v>10.06691472528</v>
+        <v>10.0443446054</v>
       </c>
       <c r="Q46">
-        <v>28.16691472528</v>
+        <v>28.1443446054</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1177020539425596</v>
+        <v>0.1188399725814198</v>
       </c>
       <c r="T46">
-        <v>1.212371925515973</v>
+        <v>1.231558868525661</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.13700936016634</v>
+        <v>10.88952026327375</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08377688491978089</v>
+        <v>0.0836349396317284</v>
       </c>
       <c r="C47">
-        <v>30.3235101608939</v>
+        <v>29.77172131765408</v>
       </c>
       <c r="D47">
-        <v>-18.85718983910609</v>
+        <v>-18.85743868234591</v>
       </c>
       <c r="E47">
-        <v>24.2653</v>
+        <v>24.81684</v>
       </c>
       <c r="F47">
-        <v>24.8193</v>
+        <v>25.37084</v>
       </c>
       <c r="G47">
         <v>74</v>
@@ -5135,28 +5135,28 @@
         <v>14</v>
       </c>
       <c r="M47">
-        <v>1.28563974</v>
+        <v>1.314209512</v>
       </c>
       <c r="N47">
-        <v>12.71436026</v>
+        <v>12.685790488</v>
       </c>
       <c r="O47">
-        <v>2.6700156546</v>
+        <v>2.66401600248</v>
       </c>
       <c r="P47">
-        <v>10.0443446054</v>
+        <v>10.02177448552</v>
       </c>
       <c r="Q47">
-        <v>28.1443446054</v>
+        <v>28.12177448552</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1188399725814198</v>
+        <v>0.1200200363550526</v>
       </c>
       <c r="T47">
-        <v>1.231558868525661</v>
+        <v>1.251456439054226</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.88952026327375</v>
+        <v>10.65279156189824</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0836349396317284</v>
+        <v>0.08349299434367588</v>
       </c>
       <c r="C48">
-        <v>29.77172131765408</v>
+        <v>29.21993246784662</v>
       </c>
       <c r="D48">
-        <v>-18.85743868234591</v>
+        <v>-18.85768753215338</v>
       </c>
       <c r="E48">
-        <v>24.81684</v>
+        <v>25.36838000000001</v>
       </c>
       <c r="F48">
-        <v>25.37084</v>
+        <v>25.92238</v>
       </c>
       <c r="G48">
         <v>74</v>
@@ -5217,28 +5217,28 @@
         <v>14</v>
       </c>
       <c r="M48">
-        <v>1.314209512</v>
+        <v>1.342779284</v>
       </c>
       <c r="N48">
-        <v>12.685790488</v>
+        <v>12.657220716</v>
       </c>
       <c r="O48">
-        <v>2.66401600248</v>
+        <v>2.65801635036</v>
       </c>
       <c r="P48">
-        <v>10.02177448552</v>
+        <v>9.999204365640001</v>
       </c>
       <c r="Q48">
-        <v>28.12177448552</v>
+        <v>28.09920436564</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1200200363550526</v>
+        <v>0.1212446308371243</v>
       </c>
       <c r="T48">
-        <v>1.251456439054226</v>
+        <v>1.272104861300851</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.65279156189824</v>
+        <v>10.42613642228338</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08349299434367588</v>
+        <v>0.08335104905562339</v>
       </c>
       <c r="C49">
-        <v>29.21993246784662</v>
+        <v>28.66814361147123</v>
       </c>
       <c r="D49">
-        <v>-18.85768753215338</v>
+        <v>-18.85793638852877</v>
       </c>
       <c r="E49">
-        <v>25.36838000000001</v>
+        <v>25.91992</v>
       </c>
       <c r="F49">
-        <v>25.92238</v>
+        <v>26.47392</v>
       </c>
       <c r="G49">
         <v>74</v>
@@ -5299,28 +5299,28 @@
         <v>14</v>
       </c>
       <c r="M49">
-        <v>1.342779284</v>
+        <v>1.371349056</v>
       </c>
       <c r="N49">
-        <v>12.657220716</v>
+        <v>12.628650944</v>
       </c>
       <c r="O49">
-        <v>2.65801635036</v>
+        <v>2.65201669824</v>
       </c>
       <c r="P49">
-        <v>9.999204365640001</v>
+        <v>9.97663424576</v>
       </c>
       <c r="Q49">
-        <v>28.09920436564</v>
+        <v>28.07663424576</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1212446308371243</v>
+        <v>0.1225163251069681</v>
       </c>
       <c r="T49">
-        <v>1.272104861300851</v>
+        <v>1.293547453633885</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.42613642228338</v>
+        <v>10.20892524681914</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08335104905562339</v>
+        <v>0.0832091037675709</v>
       </c>
       <c r="C50">
-        <v>28.66814361147123</v>
+        <v>28.11635474852766</v>
       </c>
       <c r="D50">
-        <v>-18.85793638852877</v>
+        <v>-18.85818525147233</v>
       </c>
       <c r="E50">
-        <v>25.91992</v>
+        <v>26.47146</v>
       </c>
       <c r="F50">
-        <v>26.47392</v>
+        <v>27.02546</v>
       </c>
       <c r="G50">
         <v>74</v>
@@ -5381,28 +5381,28 @@
         <v>14</v>
       </c>
       <c r="M50">
-        <v>1.371349056</v>
+        <v>1.399918828</v>
       </c>
       <c r="N50">
-        <v>12.628650944</v>
+        <v>12.600081172</v>
       </c>
       <c r="O50">
-        <v>2.65201669824</v>
+        <v>2.64601704612</v>
       </c>
       <c r="P50">
-        <v>9.97663424576</v>
+        <v>9.954064125879999</v>
       </c>
       <c r="Q50">
-        <v>28.07663424576</v>
+        <v>28.05406412588</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1225163251069681</v>
+        <v>0.1238378897403351</v>
       </c>
       <c r="T50">
-        <v>1.293547453633884</v>
+        <v>1.315830931940762</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.20892524681915</v>
+        <v>10.00057983361875</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0832091037675709</v>
+        <v>0.08373865847951839</v>
       </c>
       <c r="C51">
-        <v>28.11635474852766</v>
+        <v>27.56574314704899</v>
       </c>
       <c r="D51">
-        <v>-18.85818525147233</v>
+        <v>-18.85725685295101</v>
       </c>
       <c r="E51">
-        <v>26.47146</v>
+        <v>27.023</v>
       </c>
       <c r="F51">
-        <v>27.02546</v>
+        <v>27.577</v>
       </c>
       <c r="G51">
         <v>74</v>
@@ -5463,45 +5463,45 @@
         <v>14</v>
       </c>
       <c r="M51">
-        <v>1.399918828</v>
+        <v>1.4753695</v>
       </c>
       <c r="N51">
-        <v>12.600081172</v>
+        <v>12.5246305</v>
       </c>
       <c r="O51">
-        <v>2.64601704612</v>
+        <v>2.630172405</v>
       </c>
       <c r="P51">
-        <v>9.954064125879999</v>
+        <v>9.894458095000001</v>
       </c>
       <c r="Q51">
-        <v>28.05406412588</v>
+        <v>27.994458095</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1238378897403351</v>
+        <v>0.1252123169590368</v>
       </c>
       <c r="T51">
-        <v>1.315830931940762</v>
+        <v>1.339005749379915</v>
       </c>
       <c r="U51">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V51">
         <v>0.21</v>
       </c>
       <c r="W51">
-        <v>0.040922</v>
+        <v>0.042265</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>10.00057983361875</v>
+        <v>9.489148311660232</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08373865847951839</v>
+        <v>0.0836101431914659</v>
       </c>
       <c r="C52">
-        <v>27.56574314704899</v>
+        <v>27.0139778465233</v>
       </c>
       <c r="D52">
-        <v>-18.85725685295101</v>
+        <v>-18.8574821534767</v>
       </c>
       <c r="E52">
-        <v>27.023</v>
+        <v>27.57454</v>
       </c>
       <c r="F52">
-        <v>27.577</v>
+        <v>28.12854</v>
       </c>
       <c r="G52">
         <v>74</v>
@@ -5545,28 +5545,28 @@
         <v>14</v>
       </c>
       <c r="M52">
-        <v>1.4753695</v>
+        <v>1.50487689</v>
       </c>
       <c r="N52">
-        <v>12.5246305</v>
+        <v>12.49512311</v>
       </c>
       <c r="O52">
-        <v>2.630172405</v>
+        <v>2.6239758531</v>
       </c>
       <c r="P52">
-        <v>9.894458095000001</v>
+        <v>9.8711472569</v>
       </c>
       <c r="Q52">
-        <v>27.994458095</v>
+        <v>27.9711472569</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1252123169590368</v>
+        <v>0.1266428432478896</v>
       </c>
       <c r="T52">
-        <v>1.339005749379915</v>
+        <v>1.363126477734952</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.489148311660232</v>
+        <v>9.30308658005905</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0836101431914659</v>
+        <v>0.08348162790341339</v>
       </c>
       <c r="C53">
-        <v>27.0139778465233</v>
+        <v>26.4622125406139</v>
       </c>
       <c r="D53">
-        <v>-18.8574821534767</v>
+        <v>-18.85770745938609</v>
       </c>
       <c r="E53">
-        <v>27.57454</v>
+        <v>28.12608000000001</v>
       </c>
       <c r="F53">
-        <v>28.12854</v>
+        <v>28.68008</v>
       </c>
       <c r="G53">
         <v>74</v>
@@ -5627,28 +5627,28 @@
         <v>14</v>
       </c>
       <c r="M53">
-        <v>1.50487689</v>
+        <v>1.53438428</v>
       </c>
       <c r="N53">
-        <v>12.49512311</v>
+        <v>12.46561572</v>
       </c>
       <c r="O53">
-        <v>2.6239758531</v>
+        <v>2.6177793012</v>
       </c>
       <c r="P53">
-        <v>9.8711472569</v>
+        <v>9.8478364188</v>
       </c>
       <c r="Q53">
-        <v>27.9711472569</v>
+        <v>27.9478364188</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1266428432478896</v>
+        <v>0.1281329747987779</v>
       </c>
       <c r="T53">
-        <v>1.363126477734952</v>
+        <v>1.388252236438115</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.30308658005905</v>
+        <v>9.124181068904067</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08348162790341339</v>
+        <v>0.08335311261536088</v>
       </c>
       <c r="C54">
-        <v>26.4622125406139</v>
+        <v>25.91044722932063</v>
       </c>
       <c r="D54">
-        <v>-18.85770745938609</v>
+        <v>-18.85793277067937</v>
       </c>
       <c r="E54">
-        <v>28.12608000000001</v>
+        <v>28.67762</v>
       </c>
       <c r="F54">
-        <v>28.68008</v>
+        <v>29.23162</v>
       </c>
       <c r="G54">
         <v>74</v>
@@ -5709,28 +5709,28 @@
         <v>14</v>
       </c>
       <c r="M54">
-        <v>1.53438428</v>
+        <v>1.56389167</v>
       </c>
       <c r="N54">
-        <v>12.46561572</v>
+        <v>12.43610833</v>
       </c>
       <c r="O54">
-        <v>2.6177793012</v>
+        <v>2.6115827493</v>
       </c>
       <c r="P54">
-        <v>9.8478364188</v>
+        <v>9.8245255807</v>
       </c>
       <c r="Q54">
-        <v>27.9478364188</v>
+        <v>27.9245255807</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1281329747987779</v>
+        <v>0.1296865162028955</v>
       </c>
       <c r="T54">
-        <v>1.388252236438115</v>
+        <v>1.414447176362689</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.124181068904067</v>
+        <v>8.952026709113426</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08335311261536088</v>
+        <v>0.08322459732730837</v>
       </c>
       <c r="C55">
-        <v>25.91044722932063</v>
+        <v>25.35868191264326</v>
       </c>
       <c r="D55">
-        <v>-18.85793277067937</v>
+        <v>-18.85815808735675</v>
       </c>
       <c r="E55">
-        <v>28.67762</v>
+        <v>29.22916</v>
       </c>
       <c r="F55">
-        <v>29.23162</v>
+        <v>29.78316</v>
       </c>
       <c r="G55">
         <v>74</v>
@@ -5791,28 +5791,28 @@
         <v>14</v>
       </c>
       <c r="M55">
-        <v>1.56389167</v>
+        <v>1.59339906</v>
       </c>
       <c r="N55">
-        <v>12.43610833</v>
+        <v>12.40660094</v>
       </c>
       <c r="O55">
-        <v>2.6115827493</v>
+        <v>2.6053861974</v>
       </c>
       <c r="P55">
-        <v>9.8245255807</v>
+        <v>9.801214742600001</v>
       </c>
       <c r="Q55">
-        <v>27.9245255807</v>
+        <v>27.9012147426</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1296865162028955</v>
+        <v>0.131307602885453</v>
       </c>
       <c r="T55">
-        <v>1.414447176362689</v>
+        <v>1.441781026718767</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.952026709113426</v>
+        <v>8.786248436722436</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08322459732730837</v>
+        <v>0.08309608203925588</v>
       </c>
       <c r="C56">
-        <v>25.35868191264326</v>
+        <v>24.8069165905816</v>
       </c>
       <c r="D56">
-        <v>-18.85815808735675</v>
+        <v>-18.8583834094184</v>
       </c>
       <c r="E56">
-        <v>29.22916</v>
+        <v>29.78070000000001</v>
       </c>
       <c r="F56">
-        <v>29.78316</v>
+        <v>30.33470000000001</v>
       </c>
       <c r="G56">
         <v>74</v>
@@ -5873,28 +5873,28 @@
         <v>14</v>
       </c>
       <c r="M56">
-        <v>1.59339906</v>
+        <v>1.62290645</v>
       </c>
       <c r="N56">
-        <v>12.40660094</v>
+        <v>12.37709355</v>
       </c>
       <c r="O56">
-        <v>2.6053861974</v>
+        <v>2.5991896455</v>
       </c>
       <c r="P56">
-        <v>9.801214742600001</v>
+        <v>9.7779039045</v>
       </c>
       <c r="Q56">
-        <v>27.9012147426</v>
+        <v>27.8779039045</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.131307602885453</v>
+        <v>0.1330007378650131</v>
       </c>
       <c r="T56">
-        <v>1.441781026718767</v>
+        <v>1.470329714868448</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.786248436722436</v>
+        <v>8.626498465145662</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08309608203925588</v>
+        <v>0.08296756675120338</v>
       </c>
       <c r="C57">
-        <v>24.8069165905816</v>
+        <v>24.25515126313547</v>
       </c>
       <c r="D57">
-        <v>-18.8583834094184</v>
+        <v>-18.85860873686453</v>
       </c>
       <c r="E57">
-        <v>29.78070000000001</v>
+        <v>30.33224000000001</v>
       </c>
       <c r="F57">
-        <v>30.33470000000001</v>
+        <v>30.88624</v>
       </c>
       <c r="G57">
         <v>74</v>
@@ -5955,28 +5955,28 @@
         <v>14</v>
       </c>
       <c r="M57">
-        <v>1.62290645</v>
+        <v>1.65241384</v>
       </c>
       <c r="N57">
-        <v>12.37709355</v>
+        <v>12.34758616</v>
       </c>
       <c r="O57">
-        <v>2.5991896455</v>
+        <v>2.5929930936</v>
       </c>
       <c r="P57">
-        <v>9.7779039045</v>
+        <v>9.7545930664</v>
       </c>
       <c r="Q57">
-        <v>27.8779039045</v>
+        <v>27.8545930664</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1330007378650131</v>
+        <v>0.1347708335254622</v>
       </c>
       <c r="T57">
-        <v>1.470329714868448</v>
+        <v>1.500176070661297</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.626498465145662</v>
+        <v>8.472453849696635</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08296756675120338</v>
+        <v>0.08283905146315088</v>
       </c>
       <c r="C58">
-        <v>24.25515126313547</v>
+        <v>23.70338593030467</v>
       </c>
       <c r="D58">
-        <v>-18.85860873686453</v>
+        <v>-18.85883406969533</v>
       </c>
       <c r="E58">
-        <v>30.33224000000001</v>
+        <v>30.88378000000001</v>
       </c>
       <c r="F58">
-        <v>30.88624</v>
+        <v>31.43778000000001</v>
       </c>
       <c r="G58">
         <v>74</v>
@@ -6037,28 +6037,28 @@
         <v>14</v>
       </c>
       <c r="M58">
-        <v>1.65241384</v>
+        <v>1.68192123</v>
       </c>
       <c r="N58">
-        <v>12.34758616</v>
+        <v>12.31807877</v>
       </c>
       <c r="O58">
-        <v>2.5929930936</v>
+        <v>2.5867965417</v>
       </c>
       <c r="P58">
-        <v>9.7545930664</v>
+        <v>9.7312822283</v>
       </c>
       <c r="Q58">
-        <v>27.8545930664</v>
+        <v>27.8312822283</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1347708335254622</v>
+        <v>0.13662325921663</v>
       </c>
       <c r="T58">
-        <v>1.500176070661297</v>
+        <v>1.531410629049162</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.472453849696635</v>
+        <v>8.323814308473885</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08283905146315088</v>
+        <v>0.08271053617509838</v>
       </c>
       <c r="C59">
-        <v>23.70338593030467</v>
+        <v>23.15162059208901</v>
       </c>
       <c r="D59">
-        <v>-18.85883406969533</v>
+        <v>-18.85905940791098</v>
       </c>
       <c r="E59">
-        <v>30.88378000000001</v>
+        <v>31.43532000000001</v>
       </c>
       <c r="F59">
-        <v>31.43778000000001</v>
+        <v>31.98932000000001</v>
       </c>
       <c r="G59">
         <v>74</v>
@@ -6119,28 +6119,28 @@
         <v>14</v>
       </c>
       <c r="M59">
-        <v>1.68192123</v>
+        <v>1.71142862</v>
       </c>
       <c r="N59">
-        <v>12.31807877</v>
+        <v>12.28857138</v>
       </c>
       <c r="O59">
-        <v>2.5867965417</v>
+        <v>2.5805999898</v>
       </c>
       <c r="P59">
-        <v>9.7312822283</v>
+        <v>9.707971390200001</v>
       </c>
       <c r="Q59">
-        <v>27.8312822283</v>
+        <v>27.8079713902</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.13662325921663</v>
+        <v>0.1385638956549962</v>
       </c>
       <c r="T59">
-        <v>1.531410629049162</v>
+        <v>1.564132547360258</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.323814308473885</v>
+        <v>8.180300268672612</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08271053617509838</v>
+        <v>0.08258202088704587</v>
       </c>
       <c r="C60">
-        <v>23.15162059208902</v>
+        <v>22.5998552484883</v>
       </c>
       <c r="D60">
-        <v>-18.85905940791098</v>
+        <v>-18.85928475151169</v>
       </c>
       <c r="E60">
-        <v>31.43532</v>
+        <v>31.98686</v>
       </c>
       <c r="F60">
-        <v>31.98932</v>
+        <v>32.54086</v>
       </c>
       <c r="G60">
         <v>74</v>
@@ -6201,28 +6201,28 @@
         <v>14</v>
       </c>
       <c r="M60">
-        <v>1.71142862</v>
+        <v>1.74093601</v>
       </c>
       <c r="N60">
-        <v>12.28857138</v>
+        <v>12.25906399</v>
       </c>
       <c r="O60">
-        <v>2.5805999898</v>
+        <v>2.5744034379</v>
       </c>
       <c r="P60">
-        <v>9.707971390200001</v>
+        <v>9.684660552099999</v>
       </c>
       <c r="Q60">
-        <v>27.8079713902</v>
+        <v>27.7846605521</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1385638956549961</v>
+        <v>0.1405991972854777</v>
       </c>
       <c r="T60">
-        <v>1.564132547360257</v>
+        <v>1.59845065680848</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.180300268672614</v>
+        <v>8.041651111576467</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08258202088704587</v>
+        <v>0.08245350559899337</v>
       </c>
       <c r="C61">
-        <v>22.5998552484883</v>
+        <v>22.04808989950234</v>
       </c>
       <c r="D61">
-        <v>-18.85928475151169</v>
+        <v>-18.85951010049765</v>
       </c>
       <c r="E61">
-        <v>31.98686</v>
+        <v>32.5384</v>
       </c>
       <c r="F61">
-        <v>32.54086</v>
+        <v>33.0924</v>
       </c>
       <c r="G61">
         <v>74</v>
@@ -6283,28 +6283,28 @@
         <v>14</v>
       </c>
       <c r="M61">
-        <v>1.74093601</v>
+        <v>1.7704434</v>
       </c>
       <c r="N61">
-        <v>12.25906399</v>
+        <v>12.2295566</v>
       </c>
       <c r="O61">
-        <v>2.5744034379</v>
+        <v>2.568206886</v>
       </c>
       <c r="P61">
-        <v>9.684660552099999</v>
+        <v>9.661349714</v>
       </c>
       <c r="Q61">
-        <v>27.7846605521</v>
+        <v>27.761349714</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1405991972854777</v>
+        <v>0.1427362639974834</v>
       </c>
       <c r="T61">
-        <v>1.59845065680848</v>
+        <v>1.634484671729114</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.041651111576467</v>
+        <v>7.907623593050194</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08245350559899337</v>
+        <v>0.08232499031094087</v>
       </c>
       <c r="C62">
-        <v>22.04808989950234</v>
+        <v>21.49632454513095</v>
       </c>
       <c r="D62">
-        <v>-18.85951010049765</v>
+        <v>-18.85973545486905</v>
       </c>
       <c r="E62">
-        <v>32.5384</v>
+        <v>33.08994</v>
       </c>
       <c r="F62">
-        <v>33.0924</v>
+        <v>33.64394</v>
       </c>
       <c r="G62">
         <v>74</v>
@@ -6365,28 +6365,28 @@
         <v>14</v>
       </c>
       <c r="M62">
-        <v>1.7704434</v>
+        <v>1.79995079</v>
       </c>
       <c r="N62">
-        <v>12.2295566</v>
+        <v>12.20004921</v>
       </c>
       <c r="O62">
-        <v>2.568206886</v>
+        <v>2.5620103341</v>
       </c>
       <c r="P62">
-        <v>9.661349714</v>
+        <v>9.6380388759</v>
       </c>
       <c r="Q62">
-        <v>27.761349714</v>
+        <v>27.7380388759</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1427362639974834</v>
+        <v>0.1449829238742074</v>
       </c>
       <c r="T62">
-        <v>1.634484671729114</v>
+        <v>1.672366584850806</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.907623593050194</v>
+        <v>7.777990419393632</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08232499031094087</v>
+        <v>0.08219647502288836</v>
       </c>
       <c r="C63">
-        <v>21.49632454513095</v>
+        <v>20.94455918537391</v>
       </c>
       <c r="D63">
-        <v>-18.85973545486905</v>
+        <v>-18.85996081462608</v>
       </c>
       <c r="E63">
-        <v>33.08994</v>
+        <v>33.64148</v>
       </c>
       <c r="F63">
-        <v>33.64394</v>
+        <v>34.19548</v>
       </c>
       <c r="G63">
         <v>74</v>
@@ -6447,28 +6447,28 @@
         <v>14</v>
       </c>
       <c r="M63">
-        <v>1.79995079</v>
+        <v>1.82945818</v>
       </c>
       <c r="N63">
-        <v>12.20004921</v>
+        <v>12.17054182</v>
       </c>
       <c r="O63">
-        <v>2.5620103341</v>
+        <v>2.5558137822</v>
       </c>
       <c r="P63">
-        <v>9.6380388759</v>
+        <v>9.614728037800001</v>
       </c>
       <c r="Q63">
-        <v>27.7380388759</v>
+        <v>27.7147280378</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1449829238742074</v>
+        <v>0.147347829007601</v>
       </c>
       <c r="T63">
-        <v>1.672366584850806</v>
+        <v>1.71224228287364</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.777990419393632</v>
+        <v>7.652538961016316</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08219647502288836</v>
+        <v>0.08246611973483586</v>
       </c>
       <c r="C64">
-        <v>20.94455918537391</v>
+        <v>20.39349201837549</v>
       </c>
       <c r="D64">
-        <v>-18.85996081462608</v>
+        <v>-18.85948798162451</v>
       </c>
       <c r="E64">
-        <v>33.64148</v>
+        <v>34.19302</v>
       </c>
       <c r="F64">
-        <v>34.19548</v>
+        <v>34.74702</v>
       </c>
       <c r="G64">
         <v>74</v>
@@ -6529,45 +6529,45 @@
         <v>14</v>
       </c>
       <c r="M64">
-        <v>1.82945818</v>
+        <v>1.886763186</v>
       </c>
       <c r="N64">
-        <v>12.17054182</v>
+        <v>12.113236814</v>
       </c>
       <c r="O64">
-        <v>2.5558137822</v>
+        <v>2.54377973094</v>
       </c>
       <c r="P64">
-        <v>9.614728037800001</v>
+        <v>9.569457083060001</v>
       </c>
       <c r="Q64">
-        <v>27.7147280378</v>
+        <v>27.66945708306</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.147347829007601</v>
+        <v>0.1498405668509077</v>
       </c>
       <c r="T64">
-        <v>1.71224228287364</v>
+        <v>1.754273424032844</v>
       </c>
       <c r="U64">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V64">
         <v>0.21</v>
       </c>
       <c r="W64">
-        <v>0.042265</v>
+        <v>0.042897</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y64">
-        <v>7.652538961016316</v>
+        <v>7.420115096521711</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08246611973483586</v>
+        <v>0.08234392444678336</v>
       </c>
       <c r="C65">
-        <v>20.39349201837549</v>
+        <v>19.84173774689098</v>
       </c>
       <c r="D65">
-        <v>-18.85948798162451</v>
+        <v>-18.85970225310902</v>
       </c>
       <c r="E65">
-        <v>34.19302</v>
+        <v>34.74456</v>
       </c>
       <c r="F65">
-        <v>34.74702</v>
+        <v>35.29856</v>
       </c>
       <c r="G65">
         <v>74</v>
@@ -6611,28 +6611,28 @@
         <v>14</v>
       </c>
       <c r="M65">
-        <v>1.886763186</v>
+        <v>1.916711808</v>
       </c>
       <c r="N65">
-        <v>12.113236814</v>
+        <v>12.083288192</v>
       </c>
       <c r="O65">
-        <v>2.54377973094</v>
+        <v>2.53749052032</v>
       </c>
       <c r="P65">
-        <v>9.569457083060001</v>
+        <v>9.545797671679999</v>
       </c>
       <c r="Q65">
-        <v>27.66945708306</v>
+        <v>27.64579767168</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1498405668509077</v>
+        <v>0.1524717901299538</v>
       </c>
       <c r="T65">
-        <v>1.754273424032844</v>
+        <v>1.798639628589781</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.420115096521711</v>
+        <v>7.304175798138559</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08234392444678336</v>
+        <v>0.08222172915873087</v>
       </c>
       <c r="C66">
-        <v>19.84173774689098</v>
+        <v>19.28998347053754</v>
       </c>
       <c r="D66">
-        <v>-18.85970225310902</v>
+        <v>-18.85991652946246</v>
       </c>
       <c r="E66">
-        <v>34.74456</v>
+        <v>35.2961</v>
       </c>
       <c r="F66">
-        <v>35.29856</v>
+        <v>35.8501</v>
       </c>
       <c r="G66">
         <v>74</v>
@@ -6693,28 +6693,28 @@
         <v>14</v>
       </c>
       <c r="M66">
-        <v>1.916711808</v>
+        <v>1.94666043</v>
       </c>
       <c r="N66">
-        <v>12.083288192</v>
+        <v>12.05333957</v>
       </c>
       <c r="O66">
-        <v>2.53749052032</v>
+        <v>2.5312013097</v>
       </c>
       <c r="P66">
-        <v>9.545797671679999</v>
+        <v>9.5221382603</v>
       </c>
       <c r="Q66">
-        <v>27.64579767168</v>
+        <v>27.6221382603</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1524717901299538</v>
+        <v>0.1552533690249454</v>
       </c>
       <c r="T66">
-        <v>1.798639628589781</v>
+        <v>1.845541044835685</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.304175798138559</v>
+        <v>7.19180386278258</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08222172915873087</v>
+        <v>0.08209953387067837</v>
       </c>
       <c r="C67">
-        <v>19.28998347053754</v>
+        <v>18.738229189315</v>
       </c>
       <c r="D67">
-        <v>-18.85991652946246</v>
+        <v>-18.86013081068499</v>
       </c>
       <c r="E67">
-        <v>35.2961</v>
+        <v>35.84764000000001</v>
       </c>
       <c r="F67">
-        <v>35.8501</v>
+        <v>36.40164000000001</v>
       </c>
       <c r="G67">
         <v>74</v>
@@ -6775,28 +6775,28 @@
         <v>14</v>
       </c>
       <c r="M67">
-        <v>1.94666043</v>
+        <v>1.976609052</v>
       </c>
       <c r="N67">
-        <v>12.05333957</v>
+        <v>12.023390948</v>
       </c>
       <c r="O67">
-        <v>2.5312013097</v>
+        <v>2.52491209908</v>
       </c>
       <c r="P67">
-        <v>9.5221382603</v>
+        <v>9.49847884892</v>
       </c>
       <c r="Q67">
-        <v>27.6221382603</v>
+        <v>27.59847884892</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1552533690249454</v>
+        <v>0.1581985702078776</v>
       </c>
       <c r="T67">
-        <v>1.845541044835685</v>
+        <v>1.895201367919584</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.19180386278258</v>
+        <v>7.082837137588904</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08209953387067837</v>
+        <v>0.08197733858262586</v>
       </c>
       <c r="C68">
-        <v>18.738229189315</v>
+        <v>18.1864749032232</v>
       </c>
       <c r="D68">
-        <v>-18.86013081068499</v>
+        <v>-18.8603450967768</v>
       </c>
       <c r="E68">
-        <v>35.84764000000001</v>
+        <v>36.39918</v>
       </c>
       <c r="F68">
-        <v>36.40164000000001</v>
+        <v>36.95318</v>
       </c>
       <c r="G68">
         <v>74</v>
@@ -6857,28 +6857,28 @@
         <v>14</v>
       </c>
       <c r="M68">
-        <v>1.976609052</v>
+        <v>2.006557674</v>
       </c>
       <c r="N68">
-        <v>12.023390948</v>
+        <v>11.993442326</v>
       </c>
       <c r="O68">
-        <v>2.52491209908</v>
+        <v>2.51862288846</v>
       </c>
       <c r="P68">
-        <v>9.49847884892</v>
+        <v>9.474819437540001</v>
       </c>
       <c r="Q68">
-        <v>27.59847884892</v>
+        <v>27.57481943754</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1581985702078776</v>
+        <v>0.1613222684321996</v>
       </c>
       <c r="T68">
-        <v>1.895201367919584</v>
+        <v>1.947871407554023</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.082837137588904</v>
+        <v>6.977123150460712</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08197733858262586</v>
+        <v>0.08185514329457337</v>
       </c>
       <c r="C69">
-        <v>18.1864749032232</v>
+        <v>17.63472061226197</v>
       </c>
       <c r="D69">
-        <v>-18.8603450967768</v>
+        <v>-18.86055938773803</v>
       </c>
       <c r="E69">
-        <v>36.39918</v>
+        <v>36.95072</v>
       </c>
       <c r="F69">
-        <v>36.95318</v>
+        <v>37.50472000000001</v>
       </c>
       <c r="G69">
         <v>74</v>
@@ -6939,28 +6939,28 @@
         <v>14</v>
       </c>
       <c r="M69">
-        <v>2.006557674</v>
+        <v>2.036506296</v>
       </c>
       <c r="N69">
-        <v>11.993442326</v>
+        <v>11.963493704</v>
       </c>
       <c r="O69">
-        <v>2.51862288846</v>
+        <v>2.51233367784</v>
       </c>
       <c r="P69">
-        <v>9.474819437540001</v>
+        <v>9.45116002616</v>
       </c>
       <c r="Q69">
-        <v>27.57481943754</v>
+        <v>27.55116002616</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1613222684321996</v>
+        <v>0.1646411977955418</v>
       </c>
       <c r="T69">
-        <v>1.947871407554023</v>
+        <v>2.003833324665614</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.977123150460712</v>
+        <v>6.874518398248054</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08185514329457337</v>
+        <v>0.08173294800652087</v>
       </c>
       <c r="C70">
-        <v>17.63472061226197</v>
+        <v>17.08296631643114</v>
       </c>
       <c r="D70">
-        <v>-18.86055938773803</v>
+        <v>-18.86077368356885</v>
       </c>
       <c r="E70">
-        <v>36.95072</v>
+        <v>37.50226000000001</v>
       </c>
       <c r="F70">
-        <v>37.50472000000001</v>
+        <v>38.05626000000001</v>
       </c>
       <c r="G70">
         <v>74</v>
@@ -7021,28 +7021,28 @@
         <v>14</v>
       </c>
       <c r="M70">
-        <v>2.036506296</v>
+        <v>2.066454918000001</v>
       </c>
       <c r="N70">
-        <v>11.963493704</v>
+        <v>11.933545082</v>
       </c>
       <c r="O70">
-        <v>2.51233367784</v>
+        <v>2.50604446722</v>
       </c>
       <c r="P70">
-        <v>9.45116002616</v>
+        <v>9.427500614779998</v>
       </c>
       <c r="Q70">
-        <v>27.55116002616</v>
+        <v>27.52750061478</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1646411977955418</v>
+        <v>0.1681742516339383</v>
       </c>
       <c r="T70">
-        <v>2.003833324665614</v>
+        <v>2.063405688042468</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.874518398248054</v>
+        <v>6.774887696824168</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08173294800652087</v>
+        <v>0.08161075271846836</v>
       </c>
       <c r="C71">
-        <v>17.08296631643114</v>
+        <v>16.53121201573055</v>
       </c>
       <c r="D71">
-        <v>-18.86077368356885</v>
+        <v>-18.86098798426945</v>
       </c>
       <c r="E71">
-        <v>37.50226000000001</v>
+        <v>38.0538</v>
       </c>
       <c r="F71">
-        <v>38.05626000000001</v>
+        <v>38.6078</v>
       </c>
       <c r="G71">
         <v>74</v>
@@ -7103,28 +7103,28 @@
         <v>14</v>
       </c>
       <c r="M71">
-        <v>2.066454918000001</v>
+        <v>2.09640354</v>
       </c>
       <c r="N71">
-        <v>11.933545082</v>
+        <v>11.90359646</v>
       </c>
       <c r="O71">
-        <v>2.50604446722</v>
+        <v>2.4997552566</v>
       </c>
       <c r="P71">
-        <v>9.427500614779998</v>
+        <v>9.403841203399999</v>
       </c>
       <c r="Q71">
-        <v>27.52750061478</v>
+        <v>27.5038412034</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1681742516339383</v>
+        <v>0.1719428423948945</v>
       </c>
       <c r="T71">
-        <v>2.063405688042468</v>
+        <v>2.126949542311113</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.774887696824168</v>
+        <v>6.678103586869538</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08161075271846836</v>
+        <v>0.08148855743041587</v>
       </c>
       <c r="C72">
-        <v>16.53121201573055</v>
+        <v>15.97945771016003</v>
       </c>
       <c r="D72">
-        <v>-18.86098798426945</v>
+        <v>-18.86120228983997</v>
       </c>
       <c r="E72">
-        <v>38.0538</v>
+        <v>38.60534000000001</v>
       </c>
       <c r="F72">
-        <v>38.6078</v>
+        <v>39.15934000000001</v>
       </c>
       <c r="G72">
         <v>74</v>
@@ -7185,28 +7185,28 @@
         <v>14</v>
       </c>
       <c r="M72">
-        <v>2.09640354</v>
+        <v>2.126352162</v>
       </c>
       <c r="N72">
-        <v>11.90359646</v>
+        <v>11.873647838</v>
       </c>
       <c r="O72">
-        <v>2.4997552566</v>
+        <v>2.49346604598</v>
       </c>
       <c r="P72">
-        <v>9.403841203399999</v>
+        <v>9.38018179202</v>
       </c>
       <c r="Q72">
-        <v>27.5038412034</v>
+        <v>27.48018179202</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1719428423948945</v>
+        <v>0.1759713359669513</v>
       </c>
       <c r="T72">
-        <v>2.126949542311113</v>
+        <v>2.194875731356907</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.678103586869538</v>
+        <v>6.584045789871376</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08148855743041587</v>
+        <v>0.08136636214236337</v>
       </c>
       <c r="C73">
-        <v>15.97945771016003</v>
+        <v>15.42770339971941</v>
       </c>
       <c r="D73">
-        <v>-18.86120228983997</v>
+        <v>-18.86141660028058</v>
       </c>
       <c r="E73">
-        <v>38.60534</v>
+        <v>39.15688</v>
       </c>
       <c r="F73">
-        <v>39.15934</v>
+        <v>39.71088</v>
       </c>
       <c r="G73">
         <v>74</v>
@@ -7267,28 +7267,28 @@
         <v>14</v>
       </c>
       <c r="M73">
-        <v>2.126352162</v>
+        <v>2.156300784</v>
       </c>
       <c r="N73">
-        <v>11.873647838</v>
+        <v>11.843699216</v>
       </c>
       <c r="O73">
-        <v>2.49346604598</v>
+        <v>2.48717683536</v>
       </c>
       <c r="P73">
-        <v>9.38018179202</v>
+        <v>9.35652238064</v>
       </c>
       <c r="Q73">
-        <v>27.48018179202</v>
+        <v>27.45652238064</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1759713359669512</v>
+        <v>0.1802875790798691</v>
       </c>
       <c r="T73">
-        <v>2.194875731356906</v>
+        <v>2.267653791048827</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.584045789871377</v>
+        <v>6.492600709456496</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08136636214236337</v>
+        <v>0.08124416685431086</v>
       </c>
       <c r="C74">
-        <v>15.42770339971941</v>
+        <v>14.87594908440854</v>
       </c>
       <c r="D74">
-        <v>-18.86141660028058</v>
+        <v>-18.86163091559146</v>
       </c>
       <c r="E74">
-        <v>39.15688</v>
+        <v>39.70842</v>
       </c>
       <c r="F74">
-        <v>39.71088</v>
+        <v>40.26242</v>
       </c>
       <c r="G74">
         <v>74</v>
@@ -7349,28 +7349,28 @@
         <v>14</v>
       </c>
       <c r="M74">
-        <v>2.156300784</v>
+        <v>2.186249406</v>
       </c>
       <c r="N74">
-        <v>11.843699216</v>
+        <v>11.813750594</v>
       </c>
       <c r="O74">
-        <v>2.48717683536</v>
+        <v>2.48088762474</v>
       </c>
       <c r="P74">
-        <v>9.35652238064</v>
+        <v>9.332862969260001</v>
       </c>
       <c r="Q74">
-        <v>27.45652238064</v>
+        <v>27.43286296926</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1802875790798691</v>
+        <v>0.184923543904855</v>
       </c>
       <c r="T74">
-        <v>2.267653791048827</v>
+        <v>2.345822818125334</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.492600709456496</v>
+        <v>6.403660973710517</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08124416685431086</v>
+        <v>0.08112197156625836</v>
       </c>
       <c r="C75">
-        <v>14.87594908440854</v>
+        <v>14.32419476422724</v>
       </c>
       <c r="D75">
-        <v>-18.86163091559146</v>
+        <v>-18.86184523577276</v>
       </c>
       <c r="E75">
-        <v>39.70842</v>
+        <v>40.25996</v>
       </c>
       <c r="F75">
-        <v>40.26242</v>
+        <v>40.81396</v>
       </c>
       <c r="G75">
         <v>74</v>
@@ -7431,28 +7431,28 @@
         <v>14</v>
       </c>
       <c r="M75">
-        <v>2.186249406</v>
+        <v>2.216198028</v>
       </c>
       <c r="N75">
-        <v>11.813750594</v>
+        <v>11.783801972</v>
       </c>
       <c r="O75">
-        <v>2.48088762474</v>
+        <v>2.47459841412</v>
       </c>
       <c r="P75">
-        <v>9.332862969260001</v>
+        <v>9.30920355788</v>
       </c>
       <c r="Q75">
-        <v>27.43286296926</v>
+        <v>27.40920355788</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.184923543904855</v>
+        <v>0.189916121408686</v>
       </c>
       <c r="T75">
-        <v>2.345822818125334</v>
+        <v>2.43000484728465</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.403660973710517</v>
+        <v>6.31712501460632</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08112197156625836</v>
+        <v>0.08099977627820586</v>
       </c>
       <c r="C76">
-        <v>14.32419476422724</v>
+        <v>13.77244043917533</v>
       </c>
       <c r="D76">
-        <v>-18.86184523577276</v>
+        <v>-18.86205956082466</v>
       </c>
       <c r="E76">
-        <v>40.25996</v>
+        <v>40.8115</v>
       </c>
       <c r="F76">
-        <v>40.81396</v>
+        <v>41.3655</v>
       </c>
       <c r="G76">
         <v>74</v>
@@ -7513,28 +7513,28 @@
         <v>14</v>
       </c>
       <c r="M76">
-        <v>2.216198028</v>
+        <v>2.24614665</v>
       </c>
       <c r="N76">
-        <v>11.783801972</v>
+        <v>11.75385335</v>
       </c>
       <c r="O76">
-        <v>2.47459841412</v>
+        <v>2.4683092035</v>
       </c>
       <c r="P76">
-        <v>9.30920355788</v>
+        <v>9.285544146499999</v>
       </c>
       <c r="Q76">
-        <v>27.40920355788</v>
+        <v>27.3855441465</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.189916121408686</v>
+        <v>0.1953081051128234</v>
       </c>
       <c r="T76">
-        <v>2.43000484728465</v>
+        <v>2.520921438776712</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.31712501460632</v>
+        <v>6.232896681078236</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08099977627820586</v>
+        <v>0.08087758099015335</v>
       </c>
       <c r="C77">
-        <v>13.77244043917533</v>
+        <v>13.22068610925268</v>
       </c>
       <c r="D77">
-        <v>-18.86205956082466</v>
+        <v>-18.86227389074731</v>
       </c>
       <c r="E77">
-        <v>40.8115</v>
+        <v>41.36304</v>
       </c>
       <c r="F77">
-        <v>41.3655</v>
+        <v>41.91704</v>
       </c>
       <c r="G77">
         <v>74</v>
@@ -7595,28 +7595,28 @@
         <v>14</v>
       </c>
       <c r="M77">
-        <v>2.24614665</v>
+        <v>2.276095272</v>
       </c>
       <c r="N77">
-        <v>11.75385335</v>
+        <v>11.723904728</v>
       </c>
       <c r="O77">
-        <v>2.4683092035</v>
+        <v>2.46201999288</v>
       </c>
       <c r="P77">
-        <v>9.285544146499999</v>
+        <v>9.261884735120001</v>
       </c>
       <c r="Q77">
-        <v>27.3855441465</v>
+        <v>27.36188473512</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1953081051128234</v>
+        <v>0.2011494207923057</v>
       </c>
       <c r="T77">
-        <v>2.520921438776712</v>
+        <v>2.619414412893112</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.232896681078236</v>
+        <v>6.150884882642997</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08087758099015335</v>
+        <v>0.08136368570210084</v>
       </c>
       <c r="C78">
-        <v>13.22068610925268</v>
+        <v>12.66999870562882</v>
       </c>
       <c r="D78">
-        <v>-18.86227389074731</v>
+        <v>-18.86142129437118</v>
       </c>
       <c r="E78">
-        <v>41.36304</v>
+        <v>41.91458</v>
       </c>
       <c r="F78">
-        <v>41.91704</v>
+        <v>42.46858</v>
       </c>
       <c r="G78">
         <v>74</v>
@@ -7677,45 +7677,45 @@
         <v>14</v>
       </c>
       <c r="M78">
-        <v>2.276095272</v>
+        <v>2.348512474</v>
       </c>
       <c r="N78">
-        <v>11.723904728</v>
+        <v>11.651487526</v>
       </c>
       <c r="O78">
-        <v>2.46201999288</v>
+        <v>2.44681238046</v>
       </c>
       <c r="P78">
-        <v>9.261884735120001</v>
+        <v>9.204675145540001</v>
       </c>
       <c r="Q78">
-        <v>27.36188473512</v>
+        <v>27.30467514554</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2011494207923057</v>
+        <v>0.2074986769656559</v>
       </c>
       <c r="T78">
-        <v>2.619414412893112</v>
+        <v>2.726471993454416</v>
       </c>
       <c r="U78">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V78">
         <v>0.21</v>
       </c>
       <c r="W78">
-        <v>0.042897</v>
+        <v>0.043687</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>6.150884882642997</v>
+        <v>5.961220200016702</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08136368570210084</v>
+        <v>0.08124939041404836</v>
       </c>
       <c r="C79">
-        <v>12.66999870562882</v>
+        <v>12.11825824598115</v>
       </c>
       <c r="D79">
-        <v>-18.86142129437118</v>
+        <v>-18.86162175401884</v>
       </c>
       <c r="E79">
-        <v>41.91458</v>
+        <v>42.46612</v>
       </c>
       <c r="F79">
-        <v>42.46858</v>
+        <v>43.02012000000001</v>
       </c>
       <c r="G79">
         <v>74</v>
@@ -7759,28 +7759,28 @@
         <v>14</v>
       </c>
       <c r="M79">
-        <v>2.348512474</v>
+        <v>2.379012636000001</v>
       </c>
       <c r="N79">
-        <v>11.651487526</v>
+        <v>11.620987364</v>
       </c>
       <c r="O79">
-        <v>2.44681238046</v>
+        <v>2.44040734644</v>
       </c>
       <c r="P79">
-        <v>9.204675145540001</v>
+        <v>9.180580017560001</v>
       </c>
       <c r="Q79">
-        <v>27.30467514554</v>
+        <v>27.28058001756</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2074986769656559</v>
+        <v>0.2144251382456743</v>
       </c>
       <c r="T79">
-        <v>2.726471993454416</v>
+        <v>2.843262081339474</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.961220200016702</v>
+        <v>5.884794300016487</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08124939041404836</v>
+        <v>0.08113509512599586</v>
       </c>
       <c r="C80">
-        <v>12.11825824598115</v>
+        <v>11.56651778207247</v>
       </c>
       <c r="D80">
-        <v>-18.86162175401884</v>
+        <v>-18.86182221792753</v>
       </c>
       <c r="E80">
-        <v>42.46612</v>
+        <v>43.01766</v>
       </c>
       <c r="F80">
-        <v>43.02012000000001</v>
+        <v>43.57166</v>
       </c>
       <c r="G80">
         <v>74</v>
@@ -7841,28 +7841,28 @@
         <v>14</v>
       </c>
       <c r="M80">
-        <v>2.379012636000001</v>
+        <v>2.409512798</v>
       </c>
       <c r="N80">
-        <v>11.620987364</v>
+        <v>11.590487202</v>
       </c>
       <c r="O80">
-        <v>2.44040734644</v>
+        <v>2.43400231242</v>
       </c>
       <c r="P80">
-        <v>9.180580017560001</v>
+        <v>9.15648488958</v>
       </c>
       <c r="Q80">
-        <v>27.28058001756</v>
+        <v>27.25648488958</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2144251382456743</v>
+        <v>0.2220112625047422</v>
       </c>
       <c r="T80">
-        <v>2.843262081339474</v>
+        <v>2.971175034737397</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.884794300016487</v>
+        <v>5.810303232927671</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08113509512599586</v>
+        <v>0.08102079983794336</v>
       </c>
       <c r="C81">
-        <v>11.56651778207247</v>
+        <v>11.01477731390262</v>
       </c>
       <c r="D81">
-        <v>-18.86182221792753</v>
+        <v>-18.86202268609737</v>
       </c>
       <c r="E81">
-        <v>43.01766</v>
+        <v>43.5692</v>
       </c>
       <c r="F81">
-        <v>43.57166</v>
+        <v>44.1232</v>
       </c>
       <c r="G81">
         <v>74</v>
@@ -7923,28 +7923,28 @@
         <v>14</v>
       </c>
       <c r="M81">
-        <v>2.409512798</v>
+        <v>2.44001296</v>
       </c>
       <c r="N81">
-        <v>11.590487202</v>
+        <v>11.55998704</v>
       </c>
       <c r="O81">
-        <v>2.43400231242</v>
+        <v>2.4275972784</v>
       </c>
       <c r="P81">
-        <v>9.15648488958</v>
+        <v>9.132389761599999</v>
       </c>
       <c r="Q81">
-        <v>27.25648488958</v>
+        <v>27.2323897616</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2220112625047422</v>
+        <v>0.2303559991897168</v>
       </c>
       <c r="T81">
-        <v>2.971175034737397</v>
+        <v>3.111879283475111</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.810303232927671</v>
+        <v>5.737674442516076</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08102079983794336</v>
+        <v>0.08090650454989085</v>
       </c>
       <c r="C82">
-        <v>11.01477731390262</v>
+        <v>10.46303684147148</v>
       </c>
       <c r="D82">
-        <v>-18.86202268609737</v>
+        <v>-18.86222315852851</v>
       </c>
       <c r="E82">
-        <v>43.5692</v>
+        <v>44.12074</v>
       </c>
       <c r="F82">
-        <v>44.1232</v>
+        <v>44.67474000000001</v>
       </c>
       <c r="G82">
         <v>74</v>
@@ -8005,28 +8005,28 @@
         <v>14</v>
       </c>
       <c r="M82">
-        <v>2.44001296</v>
+        <v>2.470513122</v>
       </c>
       <c r="N82">
-        <v>11.55998704</v>
+        <v>11.529486878</v>
       </c>
       <c r="O82">
-        <v>2.4275972784</v>
+        <v>2.42119224438</v>
       </c>
       <c r="P82">
-        <v>9.132389761599999</v>
+        <v>9.10829463362</v>
       </c>
       <c r="Q82">
-        <v>27.2323897616</v>
+        <v>27.20829463362</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2303559991897168</v>
+        <v>0.2395791292099519</v>
       </c>
       <c r="T82">
-        <v>3.111879283475111</v>
+        <v>3.267394505764163</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.737674442516076</v>
+        <v>5.666838955571432</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08090650454989085</v>
+        <v>0.08079220926183835</v>
       </c>
       <c r="C83">
-        <v>10.46303684147148</v>
+        <v>9.911296364778899</v>
       </c>
       <c r="D83">
-        <v>-18.86222315852851</v>
+        <v>-18.86242363522109</v>
       </c>
       <c r="E83">
-        <v>44.12074</v>
+        <v>44.67228000000001</v>
       </c>
       <c r="F83">
-        <v>44.67474000000001</v>
+        <v>45.22628000000001</v>
       </c>
       <c r="G83">
         <v>74</v>
@@ -8087,28 +8087,28 @@
         <v>14</v>
       </c>
       <c r="M83">
-        <v>2.470513122</v>
+        <v>2.501013284000001</v>
       </c>
       <c r="N83">
-        <v>11.529486878</v>
+        <v>11.498986716</v>
       </c>
       <c r="O83">
-        <v>2.42119224438</v>
+        <v>2.41478721036</v>
       </c>
       <c r="P83">
-        <v>9.10829463362</v>
+        <v>9.084199505639999</v>
       </c>
       <c r="Q83">
-        <v>27.20829463362</v>
+        <v>27.18419950564</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2395791292099519</v>
+        <v>0.2498270514546575</v>
       </c>
       <c r="T83">
-        <v>3.267394505764163</v>
+        <v>3.440189197196443</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.666838955571432</v>
+        <v>5.597731163430316</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08079220926183835</v>
+        <v>0.08067791397378585</v>
       </c>
       <c r="C84">
-        <v>9.911296364778899</v>
+        <v>9.359555883824754</v>
       </c>
       <c r="D84">
-        <v>-18.86242363522109</v>
+        <v>-18.86262411617524</v>
       </c>
       <c r="E84">
-        <v>44.67228000000001</v>
+        <v>45.22382</v>
       </c>
       <c r="F84">
-        <v>45.22628000000001</v>
+        <v>45.77782000000001</v>
       </c>
       <c r="G84">
         <v>74</v>
@@ -8169,28 +8169,28 @@
         <v>14</v>
       </c>
       <c r="M84">
-        <v>2.501013284000001</v>
+        <v>2.531513446</v>
       </c>
       <c r="N84">
-        <v>11.498986716</v>
+        <v>11.468486554</v>
       </c>
       <c r="O84">
-        <v>2.41478721036</v>
+        <v>2.40838217634</v>
       </c>
       <c r="P84">
-        <v>9.084199505639999</v>
+        <v>9.06010437766</v>
       </c>
       <c r="Q84">
-        <v>27.18419950564</v>
+        <v>27.16010437766</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2498270514546575</v>
+        <v>0.261280611610505</v>
       </c>
       <c r="T84">
-        <v>3.440189197196443</v>
+        <v>3.633312675856051</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.597731163430316</v>
+        <v>5.530288619292603</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08067791397378585</v>
+        <v>0.08056361868573333</v>
       </c>
       <c r="C85">
-        <v>9.359555883824754</v>
+        <v>8.807815398608895</v>
       </c>
       <c r="D85">
-        <v>-18.86262411617524</v>
+        <v>-18.86282460139109</v>
       </c>
       <c r="E85">
-        <v>45.22382</v>
+        <v>45.77536000000001</v>
       </c>
       <c r="F85">
-        <v>45.77782000000001</v>
+        <v>46.32936000000001</v>
       </c>
       <c r="G85">
         <v>74</v>
@@ -8251,28 +8251,28 @@
         <v>14</v>
       </c>
       <c r="M85">
-        <v>2.531513446</v>
+        <v>2.562013608</v>
       </c>
       <c r="N85">
-        <v>11.468486554</v>
+        <v>11.437986392</v>
       </c>
       <c r="O85">
-        <v>2.40838217634</v>
+        <v>2.40197714232</v>
       </c>
       <c r="P85">
-        <v>9.06010437766</v>
+        <v>9.036009249679999</v>
       </c>
       <c r="Q85">
-        <v>27.16010437766</v>
+        <v>27.13600924968</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.261280611610505</v>
+        <v>0.2741658667858335</v>
       </c>
       <c r="T85">
-        <v>3.633312675856051</v>
+        <v>3.85057658934811</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.530288619292603</v>
+        <v>5.464451850015309</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08056361868573333</v>
+        <v>0.08044932339768085</v>
       </c>
       <c r="C86">
-        <v>8.807815398608902</v>
+        <v>8.256074909131208</v>
       </c>
       <c r="D86">
-        <v>-18.86282460139109</v>
+        <v>-18.86302509086878</v>
       </c>
       <c r="E86">
-        <v>45.77536</v>
+        <v>46.3269</v>
       </c>
       <c r="F86">
-        <v>46.32936</v>
+        <v>46.8809</v>
       </c>
       <c r="G86">
         <v>74</v>
@@ -8333,28 +8333,28 @@
         <v>14</v>
       </c>
       <c r="M86">
-        <v>2.562013608</v>
+        <v>2.59251377</v>
       </c>
       <c r="N86">
-        <v>11.437986392</v>
+        <v>11.40748623</v>
       </c>
       <c r="O86">
-        <v>2.40197714232</v>
+        <v>2.3955721083</v>
       </c>
       <c r="P86">
-        <v>9.036009249679999</v>
+        <v>9.0119141217</v>
       </c>
       <c r="Q86">
-        <v>27.13600924968</v>
+        <v>27.1119141217</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2741658667858333</v>
+        <v>0.2887691559845389</v>
       </c>
       <c r="T86">
-        <v>3.850576589348107</v>
+        <v>4.096809024639107</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.46445185001531</v>
+        <v>5.4001641811916</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08044932339768085</v>
+        <v>0.08033502810962834</v>
       </c>
       <c r="C87">
-        <v>8.256074909131208</v>
+        <v>7.704334415391543</v>
       </c>
       <c r="D87">
-        <v>-18.86302509086878</v>
+        <v>-18.86322558460845</v>
       </c>
       <c r="E87">
-        <v>46.3269</v>
+        <v>46.87844</v>
       </c>
       <c r="F87">
-        <v>46.8809</v>
+        <v>47.43244</v>
       </c>
       <c r="G87">
         <v>74</v>
@@ -8415,28 +8415,28 @@
         <v>14</v>
       </c>
       <c r="M87">
-        <v>2.59251377</v>
+        <v>2.623013932</v>
       </c>
       <c r="N87">
-        <v>11.40748623</v>
+        <v>11.376986068</v>
       </c>
       <c r="O87">
-        <v>2.3955721083</v>
+        <v>2.38916707428</v>
       </c>
       <c r="P87">
-        <v>9.0119141217</v>
+        <v>8.987818993720001</v>
       </c>
       <c r="Q87">
-        <v>27.1119141217</v>
+        <v>27.08781899372</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2887691559845389</v>
+        <v>0.3054586293544881</v>
       </c>
       <c r="T87">
-        <v>4.096809024639107</v>
+        <v>4.378217522114534</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.4001641811916</v>
+        <v>5.337371574433559</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08033502810962834</v>
+        <v>0.08022073282157585</v>
       </c>
       <c r="C88">
-        <v>7.704334415391543</v>
+        <v>7.152593917389765</v>
       </c>
       <c r="D88">
-        <v>-18.86322558460845</v>
+        <v>-18.86342608261024</v>
       </c>
       <c r="E88">
-        <v>46.87844</v>
+        <v>47.42998</v>
       </c>
       <c r="F88">
-        <v>47.43244</v>
+        <v>47.98398</v>
       </c>
       <c r="G88">
         <v>74</v>
@@ -8497,28 +8497,28 @@
         <v>14</v>
       </c>
       <c r="M88">
-        <v>2.623013932</v>
+        <v>2.653514094</v>
       </c>
       <c r="N88">
-        <v>11.376986068</v>
+        <v>11.346485906</v>
       </c>
       <c r="O88">
-        <v>2.38916707428</v>
+        <v>2.38276204026</v>
       </c>
       <c r="P88">
-        <v>8.987818993720001</v>
+        <v>8.96372386574</v>
       </c>
       <c r="Q88">
-        <v>27.08781899372</v>
+        <v>27.06372386574</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3054586293544881</v>
+        <v>0.3247157140121218</v>
       </c>
       <c r="T88">
-        <v>4.378217522114534</v>
+        <v>4.702919634586182</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.337371574433559</v>
+        <v>5.276022475876851</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08022073282157585</v>
+        <v>0.08010643753352334</v>
       </c>
       <c r="C89">
-        <v>7.152593917389765</v>
+        <v>6.600853415125727</v>
       </c>
       <c r="D89">
-        <v>-18.86342608261024</v>
+        <v>-18.86362658487426</v>
       </c>
       <c r="E89">
-        <v>47.42998</v>
+        <v>47.98152</v>
       </c>
       <c r="F89">
-        <v>47.98398</v>
+        <v>48.53552000000001</v>
       </c>
       <c r="G89">
         <v>74</v>
@@ -8579,28 +8579,28 @@
         <v>14</v>
       </c>
       <c r="M89">
-        <v>2.653514094</v>
+        <v>2.684014256</v>
       </c>
       <c r="N89">
-        <v>11.346485906</v>
+        <v>11.315985744</v>
       </c>
       <c r="O89">
-        <v>2.38276204026</v>
+        <v>2.37635700624</v>
       </c>
       <c r="P89">
-        <v>8.96372386574</v>
+        <v>8.93962873776</v>
       </c>
       <c r="Q89">
-        <v>27.06372386574</v>
+        <v>27.03962873776</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3247157140121218</v>
+        <v>0.3471823127793612</v>
       </c>
       <c r="T89">
-        <v>4.702919634586182</v>
+        <v>5.081738765803105</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.276022475876851</v>
+        <v>5.216067675014614</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08010643753352334</v>
+        <v>0.07999214224547083</v>
       </c>
       <c r="C90">
-        <v>6.600853415125727</v>
+        <v>6.049112908599319</v>
       </c>
       <c r="D90">
-        <v>-18.86362658487426</v>
+        <v>-18.86382709140068</v>
       </c>
       <c r="E90">
-        <v>47.98152</v>
+        <v>48.53306</v>
       </c>
       <c r="F90">
-        <v>48.53552000000001</v>
+        <v>49.08706</v>
       </c>
       <c r="G90">
         <v>74</v>
@@ -8661,28 +8661,28 @@
         <v>14</v>
       </c>
       <c r="M90">
-        <v>2.684014256</v>
+        <v>2.714514418</v>
       </c>
       <c r="N90">
-        <v>11.315985744</v>
+        <v>11.285485582</v>
       </c>
       <c r="O90">
-        <v>2.37635700624</v>
+        <v>2.36995197222</v>
       </c>
       <c r="P90">
-        <v>8.93962873776</v>
+        <v>8.915533609779999</v>
       </c>
       <c r="Q90">
-        <v>27.03962873776</v>
+        <v>27.01553360978</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3471823127793612</v>
+        <v>0.3737337476860985</v>
       </c>
       <c r="T90">
-        <v>5.081738765803105</v>
+        <v>5.529434102695831</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.216067675014614</v>
+        <v>5.157460173048158</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07999214224547083</v>
+        <v>0.07987784695741834</v>
       </c>
       <c r="C91">
-        <v>6.049112908599319</v>
+        <v>5.497372397810388</v>
       </c>
       <c r="D91">
-        <v>-18.86382709140068</v>
+        <v>-18.86402760218961</v>
       </c>
       <c r="E91">
-        <v>48.53306</v>
+        <v>49.0846</v>
       </c>
       <c r="F91">
-        <v>49.08706</v>
+        <v>49.6386</v>
       </c>
       <c r="G91">
         <v>74</v>
@@ -8743,28 +8743,28 @@
         <v>14</v>
       </c>
       <c r="M91">
-        <v>2.714514418</v>
+        <v>2.74501458</v>
       </c>
       <c r="N91">
-        <v>11.285485582</v>
+        <v>11.25498542</v>
       </c>
       <c r="O91">
-        <v>2.36995197222</v>
+        <v>2.3635469382</v>
       </c>
       <c r="P91">
-        <v>8.915533609779999</v>
+        <v>8.891438481800002</v>
       </c>
       <c r="Q91">
-        <v>27.01553360978</v>
+        <v>26.9914384818</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3737337476860985</v>
+        <v>0.4055954695741835</v>
       </c>
       <c r="T91">
-        <v>5.529434102695831</v>
+        <v>6.066668506967104</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.157460173048158</v>
+        <v>5.10015506001429</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07987784695741834</v>
+        <v>0.07976355166936583</v>
       </c>
       <c r="C92">
-        <v>5.497372397810388</v>
+        <v>4.945631882758796</v>
       </c>
       <c r="D92">
-        <v>-18.86402760218961</v>
+        <v>-18.8642281172412</v>
       </c>
       <c r="E92">
-        <v>49.0846</v>
+        <v>49.63614</v>
       </c>
       <c r="F92">
-        <v>49.6386</v>
+        <v>50.19014000000001</v>
       </c>
       <c r="G92">
         <v>74</v>
@@ -8825,28 +8825,28 @@
         <v>14</v>
       </c>
       <c r="M92">
-        <v>2.74501458</v>
+        <v>2.775514742</v>
       </c>
       <c r="N92">
-        <v>11.25498542</v>
+        <v>11.224485258</v>
       </c>
       <c r="O92">
-        <v>2.3635469382</v>
+        <v>2.35714190418</v>
       </c>
       <c r="P92">
-        <v>8.891438481800002</v>
+        <v>8.867343353820001</v>
       </c>
       <c r="Q92">
-        <v>26.9914384818</v>
+        <v>26.96734335382</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4055954695741835</v>
+        <v>0.4445375741040649</v>
       </c>
       <c r="T92">
-        <v>6.066668506967104</v>
+        <v>6.723288334409768</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.10015506001429</v>
+        <v>5.044109400014132</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07976355166936583</v>
+        <v>0.07964925638131334</v>
       </c>
       <c r="C93">
-        <v>4.945631882758796</v>
+        <v>4.393891363444411</v>
       </c>
       <c r="D93">
-        <v>-18.8642281172412</v>
+        <v>-18.86442863655558</v>
       </c>
       <c r="E93">
-        <v>49.63614</v>
+        <v>50.18768</v>
       </c>
       <c r="F93">
-        <v>50.19014000000001</v>
+        <v>50.74168</v>
       </c>
       <c r="G93">
         <v>74</v>
@@ -8907,28 +8907,28 @@
         <v>14</v>
       </c>
       <c r="M93">
-        <v>2.775514742</v>
+        <v>2.806014904</v>
       </c>
       <c r="N93">
-        <v>11.224485258</v>
+        <v>11.193985096</v>
       </c>
       <c r="O93">
-        <v>2.35714190418</v>
+        <v>2.35073687016</v>
       </c>
       <c r="P93">
-        <v>8.867343353820001</v>
+        <v>8.84324822584</v>
       </c>
       <c r="Q93">
-        <v>26.96734335382</v>
+        <v>26.94324822584</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4445375741040649</v>
+        <v>0.4932152047664169</v>
       </c>
       <c r="T93">
-        <v>6.723288334409768</v>
+        <v>7.544063118713102</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.044109400014132</v>
+        <v>4.989282123927021</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07964925638131334</v>
+        <v>0.07953496109326083</v>
       </c>
       <c r="C94">
-        <v>4.393891363444411</v>
+        <v>3.842150839867102</v>
       </c>
       <c r="D94">
-        <v>-18.86442863655558</v>
+        <v>-18.8646291601329</v>
       </c>
       <c r="E94">
-        <v>50.18768</v>
+        <v>50.73922</v>
       </c>
       <c r="F94">
-        <v>50.74168</v>
+        <v>51.29322000000001</v>
       </c>
       <c r="G94">
         <v>74</v>
@@ -8989,28 +8989,28 @@
         <v>14</v>
       </c>
       <c r="M94">
-        <v>2.806014904</v>
+        <v>2.836515066</v>
       </c>
       <c r="N94">
-        <v>11.193985096</v>
+        <v>11.163484934</v>
       </c>
       <c r="O94">
-        <v>2.35073687016</v>
+        <v>2.34433183614</v>
       </c>
       <c r="P94">
-        <v>8.84324822584</v>
+        <v>8.819153097859999</v>
       </c>
       <c r="Q94">
-        <v>26.94324822584</v>
+        <v>26.91915309786</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4932152047664169</v>
+        <v>0.5558007299037265</v>
       </c>
       <c r="T94">
-        <v>7.544063118713102</v>
+        <v>8.599344984245958</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.989282123927021</v>
+        <v>4.935633929046086</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07953496109326083</v>
+        <v>0.07942066580520833</v>
       </c>
       <c r="C95">
-        <v>3.842150839867102</v>
+        <v>3.290410312026722</v>
       </c>
       <c r="D95">
-        <v>-18.8646291601329</v>
+        <v>-18.86482968797327</v>
       </c>
       <c r="E95">
-        <v>50.73922</v>
+        <v>51.29076000000001</v>
       </c>
       <c r="F95">
-        <v>51.29322000000001</v>
+        <v>51.84476000000001</v>
       </c>
       <c r="G95">
         <v>74</v>
@@ -9071,28 +9071,28 @@
         <v>14</v>
       </c>
       <c r="M95">
-        <v>2.836515066</v>
+        <v>2.867015228000001</v>
       </c>
       <c r="N95">
-        <v>11.163484934</v>
+        <v>11.132984772</v>
       </c>
       <c r="O95">
-        <v>2.34433183614</v>
+        <v>2.33792680212</v>
       </c>
       <c r="P95">
-        <v>8.819153097859999</v>
+        <v>8.79505796988</v>
       </c>
       <c r="Q95">
-        <v>26.91915309786</v>
+        <v>26.89505796988</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5558007299037265</v>
+        <v>0.6392480967534727</v>
       </c>
       <c r="T95">
-        <v>8.599344984245958</v>
+        <v>10.0063874716231</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.935633929046086</v>
+        <v>4.883127185120063</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07942066580520833</v>
+        <v>0.07930637051715583</v>
       </c>
       <c r="C96">
-        <v>3.290410312026722</v>
+        <v>2.73866977992315</v>
       </c>
       <c r="D96">
-        <v>-18.86482968797327</v>
+        <v>-18.86503022007684</v>
       </c>
       <c r="E96">
-        <v>51.29076000000001</v>
+        <v>51.8423</v>
       </c>
       <c r="F96">
-        <v>51.84476000000001</v>
+        <v>52.3963</v>
       </c>
       <c r="G96">
         <v>74</v>
@@ -9153,28 +9153,28 @@
         <v>14</v>
       </c>
       <c r="M96">
-        <v>2.867015228000001</v>
+        <v>2.89751539</v>
       </c>
       <c r="N96">
-        <v>11.132984772</v>
+        <v>11.10248461</v>
       </c>
       <c r="O96">
-        <v>2.33792680212</v>
+        <v>2.3315217681</v>
       </c>
       <c r="P96">
-        <v>8.79505796988</v>
+        <v>8.770962841899999</v>
       </c>
       <c r="Q96">
-        <v>26.89505796988</v>
+        <v>26.8709628419</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6392480967534727</v>
+        <v>0.7560744103431175</v>
       </c>
       <c r="T96">
-        <v>10.0063874716231</v>
+        <v>11.9762469539511</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.883127185120063</v>
+        <v>4.831725846329327</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07930637051715583</v>
+        <v>0.07919207522910332</v>
       </c>
       <c r="C97">
-        <v>2.73866977992315</v>
+        <v>2.186929243556243</v>
       </c>
       <c r="D97">
-        <v>-18.86503022007684</v>
+        <v>-18.86523075644375</v>
       </c>
       <c r="E97">
-        <v>51.8423</v>
+        <v>52.39384</v>
       </c>
       <c r="F97">
-        <v>52.3963</v>
+        <v>52.94784000000001</v>
       </c>
       <c r="G97">
         <v>74</v>
@@ -9235,28 +9235,28 @@
         <v>14</v>
       </c>
       <c r="M97">
-        <v>2.89751539</v>
+        <v>2.928015552000001</v>
       </c>
       <c r="N97">
-        <v>11.10248461</v>
+        <v>11.071984448</v>
       </c>
       <c r="O97">
-        <v>2.3315217681</v>
+        <v>2.325116734079999</v>
       </c>
       <c r="P97">
-        <v>8.770962841899999</v>
+        <v>8.746867713919999</v>
       </c>
       <c r="Q97">
-        <v>26.8709628419</v>
+        <v>26.84686771392</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7560744103431175</v>
+        <v>0.9313138807275847</v>
       </c>
       <c r="T97">
-        <v>11.9762469539511</v>
+        <v>14.9310361774431</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.831725846329327</v>
+        <v>4.781395368763395</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07919207522910332</v>
+        <v>0.07907777994105084</v>
       </c>
       <c r="C98">
-        <v>2.18692924355625</v>
+        <v>1.635188702925859</v>
       </c>
       <c r="D98">
-        <v>-18.86523075644375</v>
+        <v>-18.86543129707414</v>
       </c>
       <c r="E98">
-        <v>52.39384</v>
+        <v>52.94538</v>
       </c>
       <c r="F98">
-        <v>52.94784</v>
+        <v>53.49938</v>
       </c>
       <c r="G98">
         <v>74</v>
@@ -9317,28 +9317,28 @@
         <v>14</v>
       </c>
       <c r="M98">
-        <v>2.928015552</v>
+        <v>2.958515714</v>
       </c>
       <c r="N98">
-        <v>11.071984448</v>
+        <v>11.041484286</v>
       </c>
       <c r="O98">
-        <v>2.32511673408</v>
+        <v>2.31871170006</v>
       </c>
       <c r="P98">
-        <v>8.74686771392</v>
+        <v>8.72277258594</v>
       </c>
       <c r="Q98">
-        <v>26.84686771392</v>
+        <v>26.82277258594</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9313138807275824</v>
+        <v>1.223379664701693</v>
       </c>
       <c r="T98">
-        <v>14.93103617744306</v>
+        <v>19.85568488326305</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.781395368763397</v>
+        <v>4.732102633002949</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07907777994105084</v>
+        <v>0.07896348465299834</v>
       </c>
       <c r="C99">
-        <v>1.635188702925859</v>
+        <v>1.083448158031871</v>
       </c>
       <c r="D99">
-        <v>-18.86543129707414</v>
+        <v>-18.86563184196812</v>
       </c>
       <c r="E99">
-        <v>52.94538</v>
+        <v>53.49692</v>
       </c>
       <c r="F99">
-        <v>53.49938</v>
+        <v>54.05092</v>
       </c>
       <c r="G99">
         <v>74</v>
@@ -9399,28 +9399,28 @@
         <v>14</v>
       </c>
       <c r="M99">
-        <v>2.958515714</v>
+        <v>2.989015876</v>
       </c>
       <c r="N99">
-        <v>11.041484286</v>
+        <v>11.010984124</v>
       </c>
       <c r="O99">
-        <v>2.31871170006</v>
+        <v>2.31230666604</v>
       </c>
       <c r="P99">
-        <v>8.72277258594</v>
+        <v>8.698677457960001</v>
       </c>
       <c r="Q99">
-        <v>26.82277258594</v>
+        <v>26.79867745796</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.223379664701693</v>
+        <v>1.807511232649915</v>
       </c>
       <c r="T99">
-        <v>19.85568488326305</v>
+        <v>29.70498229490301</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.732102633002949</v>
+        <v>4.683815871441695</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07896348465299834</v>
+        <v>0.07884918936494584</v>
       </c>
       <c r="C100">
-        <v>1.083448158031871</v>
+        <v>0.531707608874143</v>
       </c>
       <c r="D100">
-        <v>-18.86563184196812</v>
+        <v>-18.86583239112586</v>
       </c>
       <c r="E100">
-        <v>53.49692</v>
+        <v>54.04846</v>
       </c>
       <c r="F100">
-        <v>54.05092</v>
+        <v>54.60246</v>
       </c>
       <c r="G100">
         <v>74</v>
@@ -9481,28 +9481,28 @@
         <v>14</v>
       </c>
       <c r="M100">
-        <v>2.989015876</v>
+        <v>3.019516038</v>
       </c>
       <c r="N100">
-        <v>11.010984124</v>
+        <v>10.980483962</v>
       </c>
       <c r="O100">
-        <v>2.31230666604</v>
+        <v>2.30590163202</v>
       </c>
       <c r="P100">
-        <v>8.698677457960001</v>
+        <v>8.67458232998</v>
       </c>
       <c r="Q100">
-        <v>26.79867745796</v>
+        <v>26.77458232998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.807511232649915</v>
+        <v>3.55990593649458</v>
       </c>
       <c r="T100">
-        <v>29.70498229490301</v>
+        <v>59.2528745298229</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.683815871441695</v>
+        <v>4.63650460001299</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07884918936494584</v>
-      </c>
-      <c r="C101">
-        <v>0.531707608874143</v>
-      </c>
-      <c r="D101">
-        <v>-18.86583239112586</v>
-      </c>
-      <c r="E101">
-        <v>54.04846</v>
-      </c>
-      <c r="F101">
-        <v>54.60246</v>
-      </c>
-      <c r="G101">
-        <v>74</v>
-      </c>
-      <c r="H101">
-        <v>54.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>32.1</v>
-      </c>
-      <c r="K101">
-        <v>18.1</v>
-      </c>
-      <c r="L101">
-        <v>14</v>
-      </c>
-      <c r="M101">
-        <v>3.019516038</v>
-      </c>
-      <c r="N101">
-        <v>10.980483962</v>
-      </c>
-      <c r="O101">
-        <v>2.30590163202</v>
-      </c>
-      <c r="P101">
-        <v>8.67458232998</v>
-      </c>
-      <c r="Q101">
-        <v>26.77458232998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.55990593649458</v>
-      </c>
-      <c r="T101">
-        <v>59.2528745298229</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.21</v>
-      </c>
-      <c r="W101">
-        <v>0.043687</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.63650460001299</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
